--- a/Reporte_Consulta_Pendientes.xlsx
+++ b/Reporte_Consulta_Pendientes.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2526" uniqueCount="856">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2151" uniqueCount="734">
   <si>
     <t>REPORTE PENDIENTES</t>
   </si>
@@ -152,10 +152,10 @@
     <t>1</t>
   </si>
   <si>
-    <t>429</t>
-  </si>
-  <si>
-    <t>32</t>
+    <t>430</t>
+  </si>
+  <si>
+    <t>33</t>
   </si>
   <si>
     <t>2025</t>
@@ -194,10 +194,10 @@
     <t>MANUEL GUSTAVO QUILLATUPA VASQUEZ</t>
   </si>
   <si>
-    <t>371</t>
-  </si>
-  <si>
-    <t>37</t>
+    <t>372</t>
+  </si>
+  <si>
+    <t>38</t>
   </si>
   <si>
     <t>0352-2025-02-0000044</t>
@@ -236,10 +236,10 @@
     <t>RICHARD MANUEL FLORES CABELLO</t>
   </si>
   <si>
-    <t>343</t>
-  </si>
-  <si>
-    <t>96</t>
+    <t>344</t>
+  </si>
+  <si>
+    <t>97</t>
   </si>
   <si>
     <t>0349-2025-02-0000029</t>
@@ -269,10 +269,10 @@
     <t>KARLA STHEPANIE CHUNGA HUANCA</t>
   </si>
   <si>
-    <t>341</t>
-  </si>
-  <si>
-    <t>2</t>
+    <t>342</t>
+  </si>
+  <si>
+    <t>3</t>
   </si>
   <si>
     <t>0335-2025-02-0001908</t>
@@ -299,10 +299,10 @@
     <t>28/04/2026 10:34</t>
   </si>
   <si>
-    <t>223</t>
-  </si>
-  <si>
-    <t>58</t>
+    <t>224</t>
+  </si>
+  <si>
+    <t>59</t>
   </si>
   <si>
     <t>0302-2025-02-0056199</t>
@@ -329,10 +329,10 @@
     <t>11/06/2026 09:47</t>
   </si>
   <si>
-    <t>215</t>
-  </si>
-  <si>
-    <t>27</t>
+    <t>216</t>
+  </si>
+  <si>
+    <t>28</t>
   </si>
   <si>
     <t>2026</t>
@@ -362,10 +362,10 @@
     <t>23/06/2026 17:00</t>
   </si>
   <si>
-    <t>134</t>
-  </si>
-  <si>
-    <t>19</t>
+    <t>135</t>
+  </si>
+  <si>
+    <t>20</t>
   </si>
   <si>
     <t>0302-2026-02-0003774</t>
@@ -401,10 +401,10 @@
     <t>NAYLAMP MARTIN LOPEZ GUERRERO</t>
   </si>
   <si>
-    <t>127</t>
-  </si>
-  <si>
-    <t>59</t>
+    <t>128</t>
+  </si>
+  <si>
+    <t>60</t>
   </si>
   <si>
     <t>0355-2026-02-0000068</t>
@@ -434,7 +434,7 @@
     <t>MARIA GIULLIANA VILLANUEVA RIVERA</t>
   </si>
   <si>
-    <t>86</t>
+    <t>87</t>
   </si>
   <si>
     <t>0364-2026-02-0001925</t>
@@ -464,10 +464,10 @@
     <t>26</t>
   </si>
   <si>
-    <t>79</t>
-  </si>
-  <si>
-    <t>75</t>
+    <t>80</t>
+  </si>
+  <si>
+    <t>76</t>
   </si>
   <si>
     <t>0355-2026-02-0000088</t>
@@ -486,192 +486,219 @@
     <t>09/06/2026 12:47</t>
   </si>
   <si>
-    <t>64</t>
+    <t>65</t>
+  </si>
+  <si>
+    <t>0355-2026-02-0000100</t>
+  </si>
+  <si>
+    <t>08/05/2026 14:49</t>
+  </si>
+  <si>
+    <t>08/05/2026 14:48</t>
+  </si>
+  <si>
+    <t>19/06/2026</t>
+  </si>
+  <si>
+    <t>40027186</t>
+  </si>
+  <si>
+    <t>LLANOS GUILLEN ENRIQUE GUILLERMO</t>
+  </si>
+  <si>
+    <t>Sustento técnico para la conformación de un Comité Especial encargado de conducir el Concurso Público para la contratación de servicios fiduciarios para la administración del Fideicomiso Maestro del Sistema de Recaudo Único de Lima y Callao.</t>
+  </si>
+  <si>
+    <t>08/06/2026 12:03</t>
+  </si>
+  <si>
+    <t>9</t>
+  </si>
+  <si>
+    <t>52</t>
+  </si>
+  <si>
+    <t>31</t>
+  </si>
+  <si>
+    <t>0355-2026-02-0000102</t>
+  </si>
+  <si>
+    <t>15/05/2026 15:55</t>
+  </si>
+  <si>
+    <t>26/06/2026</t>
+  </si>
+  <si>
+    <t>Revisión del Entregable N° 4 del Servicio de Asistencia Técnica para la Estructuración del Fideicomiso Maestro del Sistema de Recaudo Único y para la incorporación de los Sistemas de Recaudo Existentes.</t>
+  </si>
+  <si>
+    <t>ELLANOS</t>
+  </si>
+  <si>
+    <t>ENRIQUE GUILLERMO LLANOS GUILLEN</t>
+  </si>
+  <si>
+    <t>47</t>
+  </si>
+  <si>
+    <t>0342-2026-02-0003785</t>
+  </si>
+  <si>
+    <t>22/05/2026 17:20</t>
+  </si>
+  <si>
+    <t>22/05/2026 16:53</t>
+  </si>
+  <si>
+    <t>06/07/2026</t>
+  </si>
+  <si>
+    <t>43040434</t>
+  </si>
+  <si>
+    <t>CHAMBIO HERMOSA JENNIFFER ELIZABETH</t>
+  </si>
+  <si>
+    <t>Sobre la configuración de la causal para la declaratoria de nulidad de oficio del procedimiento de selección no competitivo Procedimiento de Selección No Competitivo N° 4-2026-ATU-1 – Contratación de Situación de Emergencia “Sistema Integral de un Sistema Integral de un Sistema de Videovigilancia para el Servicio de Transporte Regular autorizado de la Autoridad de Transporte Urbano para Lima y Callao – ATU”</t>
+  </si>
+  <si>
+    <t>21/07/2026 17:11</t>
+  </si>
+  <si>
+    <t>42</t>
+  </si>
+  <si>
+    <t>0355-2026-02-0000122</t>
+  </si>
+  <si>
+    <t>28/05/2026 12:13</t>
+  </si>
+  <si>
+    <t>10/07/2026</t>
+  </si>
+  <si>
+    <t>Invitación a participar en el Concurso Público para la selección de la Empresa Fiduciaria del Fideicomiso Maestro de la ATU.</t>
+  </si>
+  <si>
+    <t>04/06/2026 14:35</t>
+  </si>
+  <si>
+    <t>25</t>
+  </si>
+  <si>
+    <t>0302-2026-02-0038465</t>
+  </si>
+  <si>
+    <t>FEFZCQA</t>
+  </si>
+  <si>
+    <t>29/05/2026 18:58</t>
+  </si>
+  <si>
+    <t>16/07/2026</t>
+  </si>
+  <si>
+    <t>20159479855</t>
+  </si>
+  <si>
+    <t>CENTRO DE INVESTIGACION Y ASESORIA DE TR</t>
+  </si>
+  <si>
+    <t>La presente tiene el propósito de hacer entrega y compartir la versión borrador para la revisión del Libro de Casos ITS (Sistemas Inteligentes de Transporte, en proceso de edición por parte de ITS España e Iberoamérica(RUC 20159479855)</t>
+  </si>
+  <si>
+    <t>06/07/2026 14:15</t>
+  </si>
+  <si>
+    <t>DITU122</t>
+  </si>
+  <si>
+    <t>HECTOR LUIS TORRES FUERO</t>
+  </si>
+  <si>
+    <t>8</t>
+  </si>
+  <si>
+    <t>37</t>
+  </si>
+  <si>
+    <t>12</t>
+  </si>
+  <si>
+    <t>0302-2026-02-0038304</t>
+  </si>
+  <si>
+    <t>9QMYIAY</t>
+  </si>
+  <si>
+    <t>31/05/2026 20:41</t>
+  </si>
+  <si>
+    <t>01/06/2026 08:30</t>
+  </si>
+  <si>
+    <t>14/07/2026</t>
+  </si>
+  <si>
+    <t>07247084</t>
+  </si>
+  <si>
+    <t>QUINTANA ARELLANODAVID JESUS</t>
+  </si>
+  <si>
+    <t>Solicitamos Información sobre el modelo de fideicomisos.</t>
+  </si>
+  <si>
+    <t>016</t>
+  </si>
+  <si>
+    <t>03/06/2026 10:57</t>
+  </si>
+  <si>
+    <t>36</t>
+  </si>
+  <si>
+    <t>34</t>
+  </si>
+  <si>
+    <t>0302-2026-02-0038469</t>
+  </si>
+  <si>
+    <t>9NTA0YF</t>
+  </si>
+  <si>
+    <t>01/06/2026 10:40</t>
+  </si>
+  <si>
+    <t>20503758114</t>
+  </si>
+  <si>
+    <t>GAS NATURAL DE LIMA Y CALLAO S.A.</t>
+  </si>
+  <si>
+    <t>Solicitamos reunión de trabajo</t>
+  </si>
+  <si>
+    <t>2026-130447</t>
+  </si>
+  <si>
+    <t>02/06/2026 11:19</t>
+  </si>
+  <si>
+    <t>DITU179</t>
+  </si>
+  <si>
+    <t>FRANK WALTER CONDOR CARHUAS</t>
   </si>
   <si>
     <t>29</t>
   </si>
   <si>
-    <t>0355-2026-02-0000100</t>
-  </si>
-  <si>
-    <t>08/05/2026 14:49</t>
-  </si>
-  <si>
-    <t>08/05/2026 14:48</t>
-  </si>
-  <si>
-    <t>19/06/2026</t>
-  </si>
-  <si>
-    <t>40027186</t>
-  </si>
-  <si>
-    <t>LLANOS GUILLEN ENRIQUE GUILLERMO</t>
-  </si>
-  <si>
-    <t>Sustento técnico para la conformación de un Comité Especial encargado de conducir el Concurso Público para la contratación de servicios fiduciarios para la administración del Fideicomiso Maestro del Sistema de Recaudo Único de Lima y Callao.</t>
-  </si>
-  <si>
-    <t>08/06/2026 12:03</t>
-  </si>
-  <si>
-    <t>9</t>
-  </si>
-  <si>
-    <t>51</t>
-  </si>
-  <si>
-    <t>0355-2026-02-0000102</t>
-  </si>
-  <si>
-    <t>15/05/2026 15:55</t>
-  </si>
-  <si>
-    <t>26/06/2026</t>
-  </si>
-  <si>
-    <t>Revisión del Entregable N° 4 del Servicio de Asistencia Técnica para la Estructuración del Fideicomiso Maestro del Sistema de Recaudo Único y para la incorporación de los Sistemas de Recaudo Existentes.</t>
-  </si>
-  <si>
-    <t>ELLANOS</t>
-  </si>
-  <si>
-    <t>ENRIQUE GUILLERMO LLANOS GUILLEN</t>
-  </si>
-  <si>
-    <t>46</t>
-  </si>
-  <si>
-    <t>0355-2026-02-0000122</t>
-  </si>
-  <si>
-    <t>28/05/2026 12:13</t>
-  </si>
-  <si>
-    <t>10/07/2026</t>
-  </si>
-  <si>
-    <t>Invitación a participar en el Concurso Público para la selección de la Empresa Fiduciaria del Fideicomiso Maestro de la ATU.</t>
-  </si>
-  <si>
-    <t>04/06/2026 14:35</t>
-  </si>
-  <si>
-    <t>25</t>
-  </si>
-  <si>
-    <t>0302-2026-02-0038465</t>
-  </si>
-  <si>
-    <t>FEFZCQA</t>
-  </si>
-  <si>
-    <t>29/05/2026 18:58</t>
-  </si>
-  <si>
-    <t>16/07/2026</t>
-  </si>
-  <si>
-    <t>20159479855</t>
-  </si>
-  <si>
-    <t>CENTRO DE INVESTIGACION Y ASESORIA DE TR</t>
-  </si>
-  <si>
-    <t>La presente tiene el propósito de hacer entrega y compartir la versión borrador para la revisión del Libro de Casos ITS (Sistemas Inteligentes de Transporte, en proceso de edición por parte de ITS España e Iberoamérica(RUC 20159479855)</t>
-  </si>
-  <si>
-    <t>06/07/2026 14:15</t>
-  </si>
-  <si>
-    <t>DITU122</t>
-  </si>
-  <si>
-    <t>HECTOR LUIS TORRES FUERO</t>
-  </si>
-  <si>
-    <t>8</t>
-  </si>
-  <si>
-    <t>36</t>
-  </si>
-  <si>
-    <t>11</t>
-  </si>
-  <si>
-    <t>0302-2026-02-0038304</t>
-  </si>
-  <si>
-    <t>9QMYIAY</t>
-  </si>
-  <si>
-    <t>31/05/2026 20:41</t>
-  </si>
-  <si>
-    <t>01/06/2026 08:30</t>
-  </si>
-  <si>
-    <t>14/07/2026</t>
-  </si>
-  <si>
-    <t>07247084</t>
-  </si>
-  <si>
-    <t>QUINTANA ARELLANODAVID JESUS</t>
-  </si>
-  <si>
-    <t>Solicitamos Información sobre el modelo de fideicomisos.</t>
-  </si>
-  <si>
-    <t>016</t>
-  </si>
-  <si>
-    <t>03/06/2026 10:57</t>
-  </si>
-  <si>
-    <t>28</t>
-  </si>
-  <si>
     <t>35</t>
   </si>
   <si>
-    <t>33</t>
-  </si>
-  <si>
-    <t>0302-2026-02-0038469</t>
-  </si>
-  <si>
-    <t>9NTA0YF</t>
-  </si>
-  <si>
-    <t>01/06/2026 10:40</t>
-  </si>
-  <si>
-    <t>20503758114</t>
-  </si>
-  <si>
-    <t>GAS NATURAL DE LIMA Y CALLAO S.A.</t>
-  </si>
-  <si>
-    <t>Solicitamos reunión de trabajo</t>
-  </si>
-  <si>
-    <t>2026-130447</t>
-  </si>
-  <si>
-    <t>02/06/2026 11:19</t>
-  </si>
-  <si>
-    <t>DITU179</t>
-  </si>
-  <si>
-    <t>FRANK WALTER CONDOR CARHUAS</t>
-  </si>
-  <si>
-    <t>34</t>
-  </si>
-  <si>
     <t>0352-2026-02-0000151</t>
   </si>
   <si>
@@ -702,7 +729,7 @@
     <t>15/07/2026 20:33</t>
   </si>
   <si>
-    <t>4</t>
+    <t>5</t>
   </si>
   <si>
     <t>0342-2026-02-0004034</t>
@@ -721,6 +748,9 @@
   </si>
   <si>
     <t>20/07/2026 16:23</t>
+  </si>
+  <si>
+    <t>2</t>
   </si>
   <si>
     <t>0302-2026-02-0039647</t>
@@ -748,49 +778,19 @@
     <t>08/06/2026 10:39</t>
   </si>
   <si>
-    <t>31</t>
-  </si>
-  <si>
-    <t>0354-2026-02-0000079</t>
-  </si>
-  <si>
-    <t>08/06/2026 15:19</t>
+    <t>32</t>
+  </si>
+  <si>
+    <t>0302-2026-02-0040064</t>
+  </si>
+  <si>
+    <t>VMCT0UL</t>
+  </si>
+  <si>
+    <t>08/06/2026 20:03</t>
   </si>
   <si>
     <t>21/07/2026</t>
-  </si>
-  <si>
-    <t>44503150</t>
-  </si>
-  <si>
-    <t>ZAGAL MALAGA PATRICIA VIRGINIA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Solicitud de información para la implementación, validación, verificación y control posterior del subsidio económico regulado por el Decreto de Urgencia N.º 004-2026 </t>
-  </si>
-  <si>
-    <t>16/07/2026 16:21</t>
-  </si>
-  <si>
-    <t>Por vencer</t>
-  </si>
-  <si>
-    <t>CARAMBULO</t>
-  </si>
-  <si>
-    <t>CARLO MARTIN ARAMBULO CRUZ</t>
-  </si>
-  <si>
-    <t>3</t>
-  </si>
-  <si>
-    <t>0302-2026-02-0040064</t>
-  </si>
-  <si>
-    <t>VMCT0UL</t>
-  </si>
-  <si>
-    <t>08/06/2026 20:03</t>
   </si>
   <si>
     <t>Adjunta documento</t>
@@ -810,6 +810,12 @@
   </si>
   <si>
     <t>09/06/2026 15:04</t>
+  </si>
+  <si>
+    <t>CARAMBULO</t>
+  </si>
+  <si>
+    <t>CARLO MARTIN ARAMBULO CRUZ</t>
   </si>
   <si>
     <t>0302-2026-02-0040929</t>
@@ -845,10 +851,10 @@
     <t>En plazo</t>
   </si>
   <si>
-    <t>17</t>
-  </si>
-  <si>
-    <t>13</t>
+    <t>27</t>
+  </si>
+  <si>
+    <t>14</t>
   </si>
   <si>
     <t>0302-2026-02-0042277</t>
@@ -878,7 +884,7 @@
     <t>23/06/2026 09:16</t>
   </si>
   <si>
-    <t>22</t>
+    <t>23</t>
   </si>
   <si>
     <t>0302-2026-02-0042683</t>
@@ -915,10 +921,7 @@
     <t>WILLIAM CUBAS ALEGRIA</t>
   </si>
   <si>
-    <t>14</t>
-  </si>
-  <si>
-    <t>6</t>
+    <t>7</t>
   </si>
   <si>
     <t>4950-2026-02-0008307</t>
@@ -954,42 +957,15 @@
     <t>GAMIO RAFAEL TAPIA MUÑOZ</t>
   </si>
   <si>
-    <t>0362-2026-02-0000605</t>
-  </si>
-  <si>
-    <t>23/06/2026 12:53</t>
-  </si>
-  <si>
-    <t>23/06/2026 12:44</t>
+    <t>0355-2026-02-0000152</t>
+  </si>
+  <si>
+    <t>23/06/2026 12:54</t>
   </si>
   <si>
     <t>11/08/2026</t>
   </si>
   <si>
-    <t>71318927</t>
-  </si>
-  <si>
-    <t>AGUILAR FLORESBREYSY BLANCA</t>
-  </si>
-  <si>
-    <t>Capacitación "Gestión del Riesgo de Desastres", dirigida a brigadistas de la Autoridad de Transporte Urbano para Lima y Callao – ATU."</t>
-  </si>
-  <si>
-    <t>Memorando Múltiple N D-000027-2026-ATU_-GTGRD ATU</t>
-  </si>
-  <si>
-    <t>07/07/2026 18:03</t>
-  </si>
-  <si>
-    <t>21</t>
-  </si>
-  <si>
-    <t>0355-2026-02-0000152</t>
-  </si>
-  <si>
-    <t>23/06/2026 12:54</t>
-  </si>
-  <si>
     <t>Servicio de consultoría de revisión normativa y desarrollo de propuestas contractuales para el  Sistema de Recaudo Único de la Autoridad de Transporte Urbano de Lima y Callao - ATU</t>
   </si>
   <si>
@@ -1017,12 +993,12 @@
     <t>30/06/2026 15:58</t>
   </si>
   <si>
+    <t>17</t>
+  </si>
+  <si>
     <t>16</t>
   </si>
   <si>
-    <t>15</t>
-  </si>
-  <si>
     <t>0302-2026-02-0045789</t>
   </si>
   <si>
@@ -1051,6 +1027,9 @@
   </si>
   <si>
     <t>18</t>
+  </si>
+  <si>
+    <t>4</t>
   </si>
   <si>
     <t>0347-2026-02-0000378</t>
@@ -1108,34 +1087,19 @@
     <t>02/07/2026 09:10</t>
   </si>
   <si>
-    <t>0342-2026-02-0004773</t>
-  </si>
-  <si>
-    <t>02/07/2026 15:28</t>
+    <t>15</t>
+  </si>
+  <si>
+    <t>0352-2026-02-0000179</t>
+  </si>
+  <si>
+    <t>02/07/2026 17:21</t>
+  </si>
+  <si>
+    <t>02/07/2026 17:20</t>
   </si>
   <si>
     <t>19/08/2026</t>
-  </si>
-  <si>
-    <t>43040434</t>
-  </si>
-  <si>
-    <t>CHAMBIO HERMOSA JENNIFFER ELIZABETH</t>
-  </si>
-  <si>
-    <t>Sobre el cumplimiento de las disposiciones para las contrataciones cuyos montos sean iguales o inferiores a ocho (8) unidades impositivas tributarias (UIT) en la ATU</t>
-  </si>
-  <si>
-    <t>17/07/2026 10:37</t>
-  </si>
-  <si>
-    <t>0352-2026-02-0000179</t>
-  </si>
-  <si>
-    <t>02/07/2026 17:21</t>
-  </si>
-  <si>
-    <t>02/07/2026 17:20</t>
   </si>
   <si>
     <t>41473605</t>
@@ -1151,7 +1115,7 @@
     <t>03/07/2026 09:17</t>
   </si>
   <si>
-    <t>12</t>
+    <t>13</t>
   </si>
   <si>
     <t>0352-2026-02-0000180</t>
@@ -1205,6 +1169,9 @@
     <t>15/07/2026 16:28</t>
   </si>
   <si>
+    <t>22</t>
+  </si>
+  <si>
     <t>0339-2026-02-0000883</t>
   </si>
   <si>
@@ -1221,9 +1188,6 @@
   </si>
   <si>
     <t>10/07/2026 16:38</t>
-  </si>
-  <si>
-    <t>7</t>
   </si>
   <si>
     <t>0302-2026-02-0046601</t>
@@ -1267,6 +1231,9 @@
   </si>
   <si>
     <t>07/07/2026 10:46</t>
+  </si>
+  <si>
+    <t>11</t>
   </si>
   <si>
     <t>0302-2026-02-0046817</t>
@@ -1296,6 +1263,21 @@
     <t>07/07/2026 10:31</t>
   </si>
   <si>
+    <t>0355-2026-02-0000163</t>
+  </si>
+  <si>
+    <t>06/07/2026 17:01</t>
+  </si>
+  <si>
+    <t>Diagnostico técnico mapping ATU</t>
+  </si>
+  <si>
+    <t>21/07/2026 18:00</t>
+  </si>
+  <si>
+    <t>19</t>
+  </si>
+  <si>
     <t>0362-2026-02-0000664</t>
   </si>
   <si>
@@ -1342,7 +1324,7 @@
     <t>14/07/2026 12:26</t>
   </si>
   <si>
-    <t>5</t>
+    <t>6</t>
   </si>
   <si>
     <t>0362-2026-02-0000671</t>
@@ -1410,6 +1392,9 @@
     <t>15/07/2026 10:36</t>
   </si>
   <si>
+    <t>Por vencer</t>
+  </si>
+  <si>
     <t>0302-2026-02-0047220</t>
   </si>
   <si>
@@ -1525,30 +1510,6 @@
     <t>10/07/2026 16:31</t>
   </si>
   <si>
-    <t>0335-2026-02-0002702</t>
-  </si>
-  <si>
-    <t>09/07/2026 10:03</t>
-  </si>
-  <si>
-    <t>09/07/2026 10:00</t>
-  </si>
-  <si>
-    <t>40905957</t>
-  </si>
-  <si>
-    <t>DELGADO RUIZROSA MARIBEL</t>
-  </si>
-  <si>
-    <t>Remisión de información sobre acciones de preparación y medidas de mitigación frente al posible Fenómeno El Niño.</t>
-  </si>
-  <si>
-    <t>Memorando Múltiple N D-000146-2026-ATU_GG</t>
-  </si>
-  <si>
-    <t>13/07/2026 09:31</t>
-  </si>
-  <si>
     <t>8900-2026-02-0000153</t>
   </si>
   <si>
@@ -1579,10 +1540,7 @@
     <t>Se reitera solicitud de información para la implementación, validación, verificación y control posterior del subsidio económico regulado por el Decreto de Urgencia N.º 004-2026.</t>
   </si>
   <si>
-    <t>17/07/2026 10:39</t>
-  </si>
-  <si>
-    <t>24</t>
+    <t>21/07/2026 15:31</t>
   </si>
   <si>
     <t>0302-2026-02-0047421</t>
@@ -1613,53 +1571,19 @@
     <t>10/07/2026 15:32</t>
   </si>
   <si>
-    <t>0338-2026-02-0001598</t>
-  </si>
-  <si>
-    <t>09/07/2026 13:38</t>
+    <t>0335-2026-02-0002729</t>
+  </si>
+  <si>
+    <t>09/07/2026 17:45</t>
   </si>
   <si>
     <t>08/07/2026 19:00</t>
   </si>
   <si>
-    <t>24/07/2026</t>
-  </si>
-  <si>
-    <t>Solicitudes de información provenientes de otras entidades</t>
-  </si>
-  <si>
     <t>20131378972</t>
   </si>
   <si>
     <t>CONTRALORIA GENERAL DE LA REPUBLICA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[PLATAFORMA PIDE] Respuesta sobre acciones adoptadas para la corrección de la situación adversa comunicada en el Informe de Orientación de Oficio n.º 003-2026-OCI/6402-SOO.  (Fec. Reg. PIDE: 09/07/2026)
-</t>
-  </si>
-  <si>
-    <t>000224-2026-CG/OC6402</t>
-  </si>
-  <si>
-    <t>14/07/2026 13:04</t>
-  </si>
-  <si>
-    <t>0355-2026-02-0000167</t>
-  </si>
-  <si>
-    <t>09/07/2026 15:14</t>
-  </si>
-  <si>
-    <t>Solicitud de información sobre el historial de acceso a casillero de seguridad de la ATU.</t>
-  </si>
-  <si>
-    <t>15/07/2026 14:53</t>
-  </si>
-  <si>
-    <t>0335-2026-02-0002729</t>
-  </si>
-  <si>
-    <t>09/07/2026 17:45</t>
   </si>
   <si>
     <t xml:space="preserve">[PLATAFORMA PIDE] Remisión del Informe de Servicio Relacionado n.° 015-2026-OCI/6402-SR.  (Fec. Reg. PIDE: 09/07/2026)
@@ -1715,6 +1639,9 @@
     <t>20/07/2026 12:12</t>
   </si>
   <si>
+    <t>24</t>
+  </si>
+  <si>
     <t>0302-2026-02-0047736</t>
   </si>
   <si>
@@ -1822,28 +1749,25 @@
     <t>15/07/2026 12:27</t>
   </si>
   <si>
-    <t>0335-2026-02-0002748</t>
-  </si>
-  <si>
-    <t>13/07/2026 14:33</t>
-  </si>
-  <si>
-    <t>13/07/2026 14:19</t>
-  </si>
-  <si>
-    <t>48017778</t>
-  </si>
-  <si>
-    <t>MOREANO SAYRIFIORELA</t>
-  </si>
-  <si>
-    <t>Difusión de la propuesta del número de integrantes del Comité de Seguridad y Salud en el Trabajo para el periodo 2026–2028</t>
-  </si>
-  <si>
-    <t>Memorando Múltiple N D-000089-2026-ATU_GG-OGRH</t>
-  </si>
-  <si>
-    <t>14/07/2026 18:06</t>
+    <t>0302-2026-02-0048084</t>
+  </si>
+  <si>
+    <t>4EMX3RH</t>
+  </si>
+  <si>
+    <t>13/07/2026 15:13</t>
+  </si>
+  <si>
+    <t>09572511</t>
+  </si>
+  <si>
+    <t>AGUIRRE VALENCIAMARCOANTONIO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Señor:  David Hernández Salazar Carta:101/07/2026/GTLGRETCAPP-UGTRANM Presidente de Directorio de la Autoridad de Transporte Urbano para Lima y Callao – ATU. </t>
+  </si>
+  <si>
+    <t>21/07/2026 14:10</t>
   </si>
   <si>
     <t>0364-2026-02-0004122</t>
@@ -1972,6 +1896,9 @@
   </si>
   <si>
     <t>14/07/2026 11:55</t>
+  </si>
+  <si>
+    <t>07/09/2026</t>
   </si>
   <si>
     <t>20419026809</t>
@@ -1990,67 +1917,22 @@
     <t>486</t>
   </si>
   <si>
-    <t>20/07/2026 09:24</t>
-  </si>
-  <si>
-    <t>0302-2026-02-0048446</t>
-  </si>
-  <si>
-    <t>WD6OGQH</t>
-  </si>
-  <si>
-    <t>15/07/2026 11:39</t>
+    <t>21/07/2026 11:51</t>
+  </si>
+  <si>
+    <t>21/07/2026 11:07</t>
+  </si>
+  <si>
+    <t>0302-2026-02-0048520</t>
+  </si>
+  <si>
+    <t>5B6J02M</t>
+  </si>
+  <si>
+    <t>15/07/2026 16:55</t>
   </si>
   <si>
     <t>01/09/2026</t>
-  </si>
-  <si>
-    <t>01705195</t>
-  </si>
-  <si>
-    <t>HUAMAN CONDORIBARI LEONCIO</t>
-  </si>
-  <si>
-    <t>Remisión de información para la implementación del subsidio económico temporal (D.U. N.° 004-2026</t>
-  </si>
-  <si>
-    <t>227</t>
-  </si>
-  <si>
-    <t>16/07/2026 12:10</t>
-  </si>
-  <si>
-    <t>0340-2026-02-0001161</t>
-  </si>
-  <si>
-    <t>15/07/2026 14:47</t>
-  </si>
-  <si>
-    <t>15/07/2026 14:30</t>
-  </si>
-  <si>
-    <t>47857365</t>
-  </si>
-  <si>
-    <t>CHOQUE HILAQUITA TIFFANIBRILLIT</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Difusión de la Directiva que regula las Normas para la implementación y Funcionamiento del Lactario Institucional de La Autoridad de Transporte Urbano para Lima y Callao – ATU. </t>
-  </si>
-  <si>
-    <t>Memorando Múltiple N D-000091-2026-ATU_GG-OGRH</t>
-  </si>
-  <si>
-    <t>15/07/2026 14:57</t>
-  </si>
-  <si>
-    <t>0302-2026-02-0048520</t>
-  </si>
-  <si>
-    <t>5B6J02M</t>
-  </si>
-  <si>
-    <t>15/07/2026 16:55</t>
   </si>
   <si>
     <t xml:space="preserve">3251: REMISION DE COMUNICACION RECIBIDA DE BARCODE RFID S.A.C. CON RESPECTO A OBSERVACIONES TECNICAS VINCULADAS A LAS TARJETAS INTEROPERABLES DE TRANSPORTE (TIT)
@@ -2096,30 +1978,18 @@
     <t>20/07/2026 09:42</t>
   </si>
   <si>
-    <t>0355-2026-02-0000174</t>
-  </si>
-  <si>
-    <t>17/07/2026 09:12</t>
+    <t>0302-2026-02-0049309</t>
+  </si>
+  <si>
+    <t>2RL95Q6</t>
+  </si>
+  <si>
+    <t>17/07/2026 10:37</t>
   </si>
   <si>
     <t>03/09/2026</t>
   </si>
   <si>
-    <t>21/07/2026 08:46</t>
-  </si>
-  <si>
-    <t>Hoy</t>
-  </si>
-  <si>
-    <t>Devolver</t>
-  </si>
-  <si>
-    <t>0302-2026-02-0049309</t>
-  </si>
-  <si>
-    <t>2RL95Q6</t>
-  </si>
-  <si>
     <t>44637009</t>
   </si>
   <si>
@@ -2169,62 +2039,6 @@
   </si>
   <si>
     <t>17/07/2026 18:43</t>
-  </si>
-  <si>
-    <t>0302-2026-02-0049005</t>
-  </si>
-  <si>
-    <t>RVJEUNL</t>
-  </si>
-  <si>
-    <t>17/07/2026 15:02</t>
-  </si>
-  <si>
-    <t>20393066386</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GOBIERNO REGIONAL DE UCAYALI                                                                        </t>
-  </si>
-  <si>
-    <t>ATENCION DE REQUERIMIENTO DE INFORMACION
-Ref. : a) Oficio N° 434-2026-GRU-DRTC-DR
-b) Oficio N° D-0004-2026-ATU/DIR
-c) Oficio N° D-0001-2026-ATU/DIR</t>
-  </si>
-  <si>
-    <t>307-2026-GRU-GR-GGR</t>
-  </si>
-  <si>
-    <t>21/07/2026 08:41</t>
-  </si>
-  <si>
-    <t>0302-2026-02-0049035</t>
-  </si>
-  <si>
-    <t>W3RRODK</t>
-  </si>
-  <si>
-    <t>17/07/2026 15:49</t>
-  </si>
-  <si>
-    <t>46109701</t>
-  </si>
-  <si>
-    <t>BETETA ESPINOZAOSCAR GUALBERTO</t>
-  </si>
-  <si>
-    <t>Comunicación de atención y subsanación de la información requerida para la 
-implementación, validación, verificación y control posterior del subsidio 
-económico regulado por el Decreto de Urgencia N.° 004-2026. 
- : - Oficio Circular N.° D-000005-2026-ATU/DIR.
- - Oficio N.° 000062-2026-MPY/O2.20.
- - Oficio N.° 000064-2026-O2.20-MPY</t>
-  </si>
-  <si>
-    <t>000095-2026-O2.20-MPY</t>
-  </si>
-  <si>
-    <t>17/07/2026 16:59</t>
   </si>
   <si>
     <t>0302-2026-02-0049210</t>
@@ -2249,131 +2063,6 @@
     <t>Conocimiento y fines</t>
   </si>
   <si>
-    <t>0302-2026-02-0049276</t>
-  </si>
-  <si>
-    <t>7RW8H94</t>
-  </si>
-  <si>
-    <t>17/07/2026 17:01</t>
-  </si>
-  <si>
-    <t>41730658</t>
-  </si>
-  <si>
-    <t>ABREGU HUAYLLAWILFREDO</t>
-  </si>
-  <si>
-    <t>SEGUNDO ENTREGABLE, ORDEN DE SERVICIO N° 6605 PARA LA SIGT</t>
-  </si>
-  <si>
-    <t>007-WAH-2026</t>
-  </si>
-  <si>
-    <t>20/07/2026 10:02</t>
-  </si>
-  <si>
-    <t>0302-2026-02-0049382</t>
-  </si>
-  <si>
-    <t>6BPSVS4</t>
-  </si>
-  <si>
-    <t>17/07/2026 17:14</t>
-  </si>
-  <si>
-    <t>75704077</t>
-  </si>
-  <si>
-    <t>CONDOR  RAYMUNDOJHOJAN SCOTH</t>
-  </si>
-  <si>
-    <t>Segundo entregable del orden de servicio Nro 0007736</t>
-  </si>
-  <si>
-    <t>04-2026-JSCR</t>
-  </si>
-  <si>
-    <t>20/07/2026 10:01</t>
-  </si>
-  <si>
-    <t>0302-2026-02-0049448</t>
-  </si>
-  <si>
-    <t>IO4XDX3</t>
-  </si>
-  <si>
-    <t>17/07/2026 17:39</t>
-  </si>
-  <si>
-    <t>74091543</t>
-  </si>
-  <si>
-    <t>ROJAS PALOMINOOSCAR DANIEL</t>
-  </si>
-  <si>
-    <t>SEGUNDO ENTREGABLE PARA LA ORDEN DE SERVICIO 0006608</t>
-  </si>
-  <si>
-    <t>07-2026</t>
-  </si>
-  <si>
-    <t>20/07/2026 09:52</t>
-  </si>
-  <si>
-    <t>0302-2026-02-0049566</t>
-  </si>
-  <si>
-    <t>IO5X39G</t>
-  </si>
-  <si>
-    <t>17/07/2026 18:06</t>
-  </si>
-  <si>
-    <t>46393958</t>
-  </si>
-  <si>
-    <t>CUBAS ALEGRIAWILLIAM ALMILCAR</t>
-  </si>
-  <si>
-    <t>Se adjunta informe de actividades correspondientes al primer entregable Julio.</t>
-  </si>
-  <si>
-    <t>WACA-07-2026</t>
-  </si>
-  <si>
-    <t>20/07/2026 18:17</t>
-  </si>
-  <si>
-    <t>0302-2026-02-0050747</t>
-  </si>
-  <si>
-    <t>I4G2NIZ</t>
-  </si>
-  <si>
-    <t>17/07/2026 20:05</t>
-  </si>
-  <si>
-    <t>20426820120</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TRANSPORTECHNICK S.A.                                                                               </t>
-  </si>
-  <si>
-    <t xml:space="preserve">DECRETO DE URGENCIA Nº 004-2026  
-QUE ESTABLECE MEDIDAS EXTRAORDINARIAS EN MATERIA 
-ECONÓMICA Y FINANCIERA PARA TRANSPORTISTAS DEL 
-SERVICIO PÚBLICO DE TRANSPORTE TERRESTRE REGULAR DE 
-PERSONAS Y DEL SERVICIO DE TRANSPORTE PÚBLICO 
-TERRESTRE DE MERCANCÍAS EN EL TERRITORIO NACIONAL </t>
-  </si>
-  <si>
-    <t>001-TPK</t>
-  </si>
-  <si>
-    <t>20/07/2026 18:57</t>
-  </si>
-  <si>
     <t>0302-2026-02-0049757</t>
   </si>
   <si>
@@ -2402,238 +2091,170 @@
     <t>20/07/2026 18:19</t>
   </si>
   <si>
-    <t>0302-2026-02-0050081</t>
-  </si>
-  <si>
-    <t>V7U7UVZ</t>
-  </si>
-  <si>
-    <t>20/07/2026 00:09</t>
-  </si>
-  <si>
-    <t>09851164</t>
-  </si>
-  <si>
-    <t>LOPEZ GUERRERO NAYLAMP MARTIN</t>
-  </si>
-  <si>
-    <t>Se presenta el segundo entregable de la Orden de Servicio 6601</t>
-  </si>
-  <si>
-    <t>20/07/2026 18:37</t>
-  </si>
-  <si>
-    <t>0302-2026-02-0050267</t>
-  </si>
-  <si>
-    <t>EVHNI9R</t>
-  </si>
-  <si>
-    <t>20/07/2026 09:05</t>
-  </si>
-  <si>
-    <t>47623721</t>
-  </si>
-  <si>
-    <t>CONTRERAS MARTINEZFELIX RAFAEL</t>
-  </si>
-  <si>
-    <t>Único entregable de la orden de servicio N°0008491</t>
-  </si>
-  <si>
-    <t>004-2026</t>
-  </si>
-  <si>
-    <t>21/07/2026 08:39</t>
-  </si>
-  <si>
-    <t>0302-2026-02-0050305</t>
-  </si>
-  <si>
-    <t>71QYZB9</t>
-  </si>
-  <si>
-    <t>20/07/2026 10:15</t>
-  </si>
-  <si>
-    <t>70300875</t>
-  </si>
-  <si>
-    <t>BAUTISTA ABANTO ERICK</t>
-  </si>
-  <si>
-    <t>PRIMER INFORME DEL SERVICIO ESPECIALIZADO ECONÓMICO-FINANCIERO EN PROYECTOS BAJO LA MODALIDAD DE ASOCIACIONES PÚBLICO - PRIVADAS, SISTEMAS DE RECAUDO Y TECNOLOGÍA</t>
-  </si>
-  <si>
-    <t>007-2026-EABA</t>
+    <t>0345-2026-02-0000443</t>
+  </si>
+  <si>
+    <t>20/07/2026 16:31</t>
+  </si>
+  <si>
+    <t>20/07/2026 16:25</t>
+  </si>
+  <si>
+    <t>71667398</t>
+  </si>
+  <si>
+    <t>QUESQUEN GONZALEZEMMA STEPHANIE</t>
+  </si>
+  <si>
+    <t>Solicitud de pases a producción de emergencia Subsidio Nacional</t>
+  </si>
+  <si>
+    <t>Informe N D-000088-2026-ATU_GG-OA-UTI-ESQG</t>
+  </si>
+  <si>
+    <t>21/07/2026 17:42</t>
+  </si>
+  <si>
+    <t>0355-2026-02-0000183</t>
+  </si>
+  <si>
+    <t>20/07/2026 18:29</t>
+  </si>
+  <si>
+    <t>Informe de la participación en actividades de trabajo interinstitucional preparatorias para la presentación y desarrollo de un plan piloto de recaudo electrónico en el actual sistema del servicio de transporte público regular de personas de la provincia de Trujillo</t>
+  </si>
+  <si>
+    <t>0302-2026-02-0050972</t>
+  </si>
+  <si>
+    <t>YZ0MQXT</t>
   </si>
   <si>
     <t>21/07/2026 08:40</t>
   </si>
   <si>
-    <t>0355-2026-02-0000177</t>
-  </si>
-  <si>
-    <t>20/07/2026 11:41</t>
-  </si>
-  <si>
-    <t>20/07/2026 11:37</t>
-  </si>
-  <si>
-    <t>10473155864</t>
-  </si>
-  <si>
-    <t>DEL CARPIO CALDERON RAISA CLAUDIA</t>
-  </si>
-  <si>
-    <t>PRESENTA ENTREGABLE EN REF. A LA OS 006610-2026</t>
-  </si>
-  <si>
-    <t>07-2026-RDCC</t>
-  </si>
-  <si>
-    <t>20/07/2026 18:18</t>
-  </si>
-  <si>
-    <t>0355-2026-02-0000178</t>
-  </si>
-  <si>
-    <t>20/07/2026 12:46</t>
-  </si>
-  <si>
-    <t>20/07/2026 12:44</t>
-  </si>
-  <si>
-    <t>10101307480</t>
-  </si>
-  <si>
-    <t>FLORES CABELLO RICHARD MANUEL</t>
-  </si>
-  <si>
-    <t>PRESENTA ENTREGABLE EN REF. ORDEN DE SERVICIO  N° 7735-2026</t>
-  </si>
-  <si>
-    <t>06-2026-RMFC</t>
-  </si>
-  <si>
-    <t>20/07/2026 18:20</t>
-  </si>
-  <si>
-    <t>0355-2026-02-0000179</t>
-  </si>
-  <si>
-    <t>20/07/2026 13:15</t>
-  </si>
-  <si>
-    <t>20/07/2026 13:14</t>
-  </si>
-  <si>
-    <t>10730069095</t>
-  </si>
-  <si>
-    <t>TORRES FUERO HECTOR LUIS</t>
-  </si>
-  <si>
-    <t>PRESENTA ENTREGABLE EN REF. ORDEN DE SERVICIO  N°  0006602</t>
-  </si>
-  <si>
-    <t>007-2026-HLTF</t>
-  </si>
-  <si>
-    <t>20/07/2026 18:21</t>
-  </si>
-  <si>
-    <t>0302-2026-02-0050599</t>
-  </si>
-  <si>
-    <t>QUMDN89</t>
-  </si>
-  <si>
-    <t>20/07/2026 15:28</t>
-  </si>
-  <si>
-    <t>20159308708</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MUNICIPALIDAD PROVINCIAL DE PARURO                                                                  </t>
-  </si>
-  <si>
-    <t>En Provincia de Paruro no existen empresas de transportes de pasajeros ni de carga</t>
-  </si>
-  <si>
-    <t>517-2026-MPP/A</t>
-  </si>
-  <si>
-    <t>21/07/2026 08:55</t>
-  </si>
-  <si>
-    <t>0355-2026-02-0000181</t>
-  </si>
-  <si>
-    <t>20/07/2026 15:35</t>
-  </si>
-  <si>
-    <t>20/07/2026 15:32</t>
-  </si>
-  <si>
-    <t>10098263140</t>
-  </si>
-  <si>
-    <t>VILLANUEVA RIVERA MARIA GIULLIANA</t>
-  </si>
-  <si>
-    <t>REMITE SEGUNDO ENTREGABLE EN REFERENCIA A LA ORDEN DE SERVICIO Nº 660-2026</t>
-  </si>
-  <si>
-    <t>007-2026-MGVR</t>
-  </si>
-  <si>
-    <t>20/07/2026 18:36</t>
-  </si>
-  <si>
-    <t>0345-2026-02-0000443</t>
-  </si>
-  <si>
-    <t>20/07/2026 16:31</t>
-  </si>
-  <si>
-    <t>20/07/2026 16:25</t>
-  </si>
-  <si>
-    <t>71667398</t>
-  </si>
-  <si>
-    <t>QUESQUEN GONZALEZEMMA STEPHANIE</t>
-  </si>
-  <si>
-    <t>Solicitud de pases a producción de emergencia Subsidio Nacional</t>
-  </si>
-  <si>
-    <t>Informe N D-000088-2026-ATU_GG-OA-UTI-ESQG</t>
-  </si>
-  <si>
-    <t>21/07/2026 08:49</t>
-  </si>
-  <si>
-    <t>0355-2026-02-0000182</t>
-  </si>
-  <si>
-    <t>20/07/2026 18:03</t>
-  </si>
-  <si>
-    <t>20/07/2026 18:02</t>
-  </si>
-  <si>
-    <t>Solicitud de contratación de dos (02) locadores de servicio para la Subdirección de Integración y Gestión Tecnológica</t>
-  </si>
-  <si>
-    <t>0355-2026-02-0000183</t>
-  </si>
-  <si>
-    <t>20/07/2026 18:29</t>
-  </si>
-  <si>
-    <t>Informe de la participación en actividades de trabajo interinstitucional preparatorias para la presentación y desarrollo de un plan piloto de recaudo electrónico en el actual sistema del servicio de transporte público regular de personas de la provincia de Trujillo</t>
+    <t>20200557159</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MUNICIPALIDAD PROVINCIAL DE PAUCARTAMBO                                                             </t>
+  </si>
+  <si>
+    <t>Se remite información solicitada.</t>
+  </si>
+  <si>
+    <t>033-2026-GM-MPP/DCA</t>
+  </si>
+  <si>
+    <t>21/07/2026 16:03</t>
+  </si>
+  <si>
+    <t>0352-2026-02-0000202</t>
+  </si>
+  <si>
+    <t>21/07/2026 09:41</t>
+  </si>
+  <si>
+    <t>20/07/2026 19:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[PLATAFORMA PIDE] Habilitación del Servicio Web que permita obtener el detalle de los comprobantes de pago electrónicos para efectos de la implementación del subsidio económico regulado por el DU N.° 004-2026(Fec. Reg. PIDE: 21/07/2026)
+</t>
+  </si>
+  <si>
+    <t>OFICIO 000041-2026-SUNAT-7B1000</t>
+  </si>
+  <si>
+    <t>21/07/2026 15:34</t>
+  </si>
+  <si>
+    <t>0352-2026-02-0000203</t>
+  </si>
+  <si>
+    <t>21/07/2026 09:52</t>
+  </si>
+  <si>
+    <t>21/07/2026 09:50</t>
+  </si>
+  <si>
+    <t>20610065792</t>
+  </si>
+  <si>
+    <t>BARCODE RFID S.A.C</t>
+  </si>
+  <si>
+    <t>PRESENTA CONSULTA SOBRE PROCEDIMIENTO Y BORMATIVA APLICABLE PARA EL ACCESO A LOS ARCHIVOS DE DISEÑO DE LA TARJETA INTEROPERABLE DE TRANSPORTE (TIT)</t>
+  </si>
+  <si>
+    <t>21/07/2026 15:42</t>
+  </si>
+  <si>
+    <t>0355-2026-02-0000185</t>
+  </si>
+  <si>
+    <t>21/07/2026 10:33</t>
+  </si>
+  <si>
+    <t>21/07/2026 10:29</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SOLICITAN ACCESO A LA LIBRERIA DE VALIDACION DE LA TIT </t>
+  </si>
+  <si>
+    <t>21/07/2026 18:13</t>
+  </si>
+  <si>
+    <t>0352-2026-02-0000204</t>
+  </si>
+  <si>
+    <t>21/07/2026 12:16</t>
+  </si>
+  <si>
+    <t>21/07/2026 12:13</t>
+  </si>
+  <si>
+    <t>20408632146</t>
+  </si>
+  <si>
+    <t>DIRECCIÓN REGIONAL DE TRANSPORTES Y COMUNICACIONES  - LORETO</t>
+  </si>
+  <si>
+    <t>REMITEN INFORMACION SOLICITADA EN REF. AL OFICIO D-000004-2026-ATU/DIR</t>
+  </si>
+  <si>
+    <t>0641-2026-GRL/32-DRTC</t>
+  </si>
+  <si>
+    <t>21/07/2026 15:29</t>
+  </si>
+  <si>
+    <t>0355-2026-02-0000186</t>
+  </si>
+  <si>
+    <t>21/07/2026 13:04</t>
+  </si>
+  <si>
+    <t>21/07/2026 13:01</t>
+  </si>
+  <si>
+    <t>10610370</t>
+  </si>
+  <si>
+    <t>QUILLATUPA VASQUEZ MANUEL GUSTAVO</t>
+  </si>
+  <si>
+    <t>Informe N D-000001-2026-ATU_DIR-SIGT-MGQV</t>
+  </si>
+  <si>
+    <t>8900-2026-02-0000170</t>
+  </si>
+  <si>
+    <t>21/07/2026 14:40</t>
+  </si>
+  <si>
+    <t>Conformidad de resultados de pruebas MIFARE de Nivel 2 y listado de TIT inicializadas, entregadas por ENOTRIA S.A. correspondiente a las199,130 TIT en proceso de reposición.</t>
+  </si>
+  <si>
+    <t>21/07/2026 16:40</t>
   </si>
 </sst>
 </file>
@@ -2753,7 +2374,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="105">
+  <cellXfs count="90">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFill="true" applyFont="true">
       <alignment horizontal="center"/>
@@ -2787,8 +2408,8 @@
     <xf numFmtId="0" fontId="0" fillId="9" borderId="4" xfId="0" applyBorder="true" applyFill="true"/>
     <xf numFmtId="0" fontId="0" fillId="9" borderId="4" xfId="0" applyBorder="true" applyFill="true"/>
     <xf numFmtId="0" fontId="0" fillId="9" borderId="4" xfId="0" applyBorder="true" applyFill="true"/>
-    <xf numFmtId="0" fontId="0" fillId="11" borderId="4" xfId="0" applyBorder="true" applyFill="true"/>
-    <xf numFmtId="0" fontId="0" fillId="11" borderId="4" xfId="0" applyBorder="true" applyFill="true"/>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="4" xfId="0" applyBorder="true" applyFill="true"/>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="4" xfId="0" applyBorder="true" applyFill="true"/>
     <xf numFmtId="0" fontId="0" fillId="11" borderId="4" xfId="0" applyBorder="true" applyFill="true"/>
     <xf numFmtId="0" fontId="0" fillId="13" borderId="4" xfId="0" applyBorder="true" applyFill="true"/>
     <xf numFmtId="0" fontId="0" fillId="13" borderId="4" xfId="0" applyBorder="true" applyFill="true"/>
@@ -2807,25 +2428,10 @@
     <xf numFmtId="0" fontId="0" fillId="13" borderId="4" xfId="0" applyBorder="true" applyFill="true"/>
     <xf numFmtId="0" fontId="0" fillId="13" borderId="4" xfId="0" applyBorder="true" applyFill="true"/>
     <xf numFmtId="0" fontId="0" fillId="13" borderId="4" xfId="0" applyBorder="true" applyFill="true"/>
-    <xf numFmtId="0" fontId="0" fillId="13" borderId="4" xfId="0" applyBorder="true" applyFill="true"/>
-    <xf numFmtId="0" fontId="0" fillId="11" borderId="4" xfId="0" applyBorder="true" applyFill="true"/>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="4" xfId="0" applyBorder="true" applyFill="true"/>
     <xf numFmtId="0" fontId="0" fillId="13" borderId="4" xfId="0" applyBorder="true" applyFill="true"/>
     <xf numFmtId="0" fontId="0" fillId="13" borderId="4" xfId="0" applyBorder="true" applyFill="true"/>
     <xf numFmtId="0" fontId="0" fillId="11" borderId="4" xfId="0" applyBorder="true" applyFill="true"/>
-    <xf numFmtId="0" fontId="0" fillId="13" borderId="4" xfId="0" applyBorder="true" applyFill="true"/>
-    <xf numFmtId="0" fontId="0" fillId="13" borderId="4" xfId="0" applyBorder="true" applyFill="true"/>
-    <xf numFmtId="0" fontId="0" fillId="13" borderId="4" xfId="0" applyBorder="true" applyFill="true"/>
-    <xf numFmtId="0" fontId="0" fillId="13" borderId="4" xfId="0" applyBorder="true" applyFill="true"/>
-    <xf numFmtId="0" fontId="0" fillId="13" borderId="4" xfId="0" applyBorder="true" applyFill="true"/>
-    <xf numFmtId="0" fontId="0" fillId="13" borderId="4" xfId="0" applyBorder="true" applyFill="true"/>
-    <xf numFmtId="0" fontId="0" fillId="13" borderId="4" xfId="0" applyBorder="true" applyFill="true"/>
-    <xf numFmtId="0" fontId="0" fillId="13" borderId="4" xfId="0" applyBorder="true" applyFill="true"/>
-    <xf numFmtId="0" fontId="0" fillId="13" borderId="4" xfId="0" applyBorder="true" applyFill="true"/>
-    <xf numFmtId="0" fontId="0" fillId="11" borderId="4" xfId="0" applyBorder="true" applyFill="true"/>
-    <xf numFmtId="0" fontId="0" fillId="13" borderId="4" xfId="0" applyBorder="true" applyFill="true"/>
-    <xf numFmtId="0" fontId="0" fillId="13" borderId="4" xfId="0" applyBorder="true" applyFill="true"/>
-    <xf numFmtId="0" fontId="0" fillId="13" borderId="4" xfId="0" applyBorder="true" applyFill="true"/>
-    <xf numFmtId="0" fontId="0" fillId="13" borderId="4" xfId="0" applyBorder="true" applyFill="true"/>
     <xf numFmtId="0" fontId="0" fillId="13" borderId="4" xfId="0" applyBorder="true" applyFill="true"/>
     <xf numFmtId="0" fontId="0" fillId="13" borderId="4" xfId="0" applyBorder="true" applyFill="true"/>
     <xf numFmtId="0" fontId="0" fillId="13" borderId="4" xfId="0" applyBorder="true" applyFill="true"/>
@@ -2873,7 +2479,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:Z104"/>
+  <dimension ref="A1:Z89"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="9.765625" customWidth="true"/>
@@ -3826,10 +3432,10 @@
         <v>157</v>
       </c>
       <c r="X15" t="s" s="15">
-        <v>158</v>
+        <v>33</v>
       </c>
       <c r="Y15" t="s" s="15">
-        <v>158</v>
+        <v>33</v>
       </c>
     </row>
     <row r="16">
@@ -3837,19 +3443,19 @@
         <v>107</v>
       </c>
       <c r="B16" t="s" s="16">
+        <v>158</v>
+      </c>
+      <c r="C16" t="s" s="16">
+        <v>28</v>
+      </c>
+      <c r="D16" t="s" s="16">
         <v>159</v>
       </c>
-      <c r="C16" t="s" s="16">
-        <v>28</v>
-      </c>
-      <c r="D16" t="s" s="16">
+      <c r="E16" t="s" s="16">
         <v>160</v>
       </c>
-      <c r="E16" t="s" s="16">
+      <c r="F16" t="s" s="16">
         <v>161</v>
-      </c>
-      <c r="F16" t="s" s="16">
-        <v>162</v>
       </c>
       <c r="G16" t="s" s="16">
         <v>53</v>
@@ -3858,25 +3464,25 @@
         <v>33</v>
       </c>
       <c r="I16" t="s" s="16">
+        <v>162</v>
+      </c>
+      <c r="J16" t="s" s="16">
         <v>163</v>
       </c>
-      <c r="J16" t="s" s="16">
+      <c r="K16" t="s" s="16">
         <v>164</v>
       </c>
-      <c r="K16" t="s" s="16">
+      <c r="L16" t="s" s="16">
+        <v>28</v>
+      </c>
+      <c r="M16" t="s" s="16">
+        <v>28</v>
+      </c>
+      <c r="N16" t="s" s="16">
         <v>165</v>
       </c>
-      <c r="L16" t="s" s="16">
-        <v>28</v>
-      </c>
-      <c r="M16" t="s" s="16">
-        <v>28</v>
-      </c>
-      <c r="N16" t="s" s="16">
-        <v>166</v>
-      </c>
       <c r="O16" t="s" s="16">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="P16" t="s" s="16">
         <v>40</v>
@@ -3897,16 +3503,16 @@
         <v>44</v>
       </c>
       <c r="V16" t="s" s="16">
+        <v>166</v>
+      </c>
+      <c r="W16" t="s" s="16">
         <v>167</v>
       </c>
-      <c r="W16" t="s" s="16">
+      <c r="X16" t="s" s="16">
         <v>168</v>
       </c>
-      <c r="X16" t="s" s="16">
-        <v>33</v>
-      </c>
       <c r="Y16" t="s" s="16">
-        <v>33</v>
+        <v>168</v>
       </c>
     </row>
     <row r="17">
@@ -4000,10 +3606,10 @@
         <v>177</v>
       </c>
       <c r="E18" t="s" s="18">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="F18" t="s" s="18">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="G18" t="s" s="18">
         <v>53</v>
@@ -4012,13 +3618,13 @@
         <v>33</v>
       </c>
       <c r="I18" t="s" s="18">
-        <v>134</v>
+        <v>180</v>
       </c>
       <c r="J18" t="s" s="18">
-        <v>135</v>
+        <v>181</v>
       </c>
       <c r="K18" t="s" s="18">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="L18" t="s" s="18">
         <v>28</v>
@@ -4027,10 +3633,10 @@
         <v>28</v>
       </c>
       <c r="N18" t="s" s="18">
-        <v>180</v>
+        <v>183</v>
       </c>
       <c r="O18" t="s" s="18">
-        <v>180</v>
+        <v>183</v>
       </c>
       <c r="P18" t="s" s="18">
         <v>40</v>
@@ -4042,25 +3648,25 @@
         <v>41</v>
       </c>
       <c r="S18" t="s" s="18">
-        <v>42</v>
+        <v>83</v>
       </c>
       <c r="T18" t="s" s="18">
-        <v>43</v>
+        <v>84</v>
       </c>
       <c r="U18" t="s" s="18">
-        <v>28</v>
+        <v>44</v>
       </c>
       <c r="V18" t="s" s="18">
-        <v>181</v>
+        <v>45</v>
       </c>
       <c r="W18" t="s" s="18">
-        <v>61</v>
+        <v>184</v>
       </c>
       <c r="X18" t="s" s="18">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="Y18" t="s" s="18">
-        <v>47</v>
+        <v>45</v>
       </c>
     </row>
     <row r="19">
@@ -4068,31 +3674,31 @@
         <v>107</v>
       </c>
       <c r="B19" t="s" s="19">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="C19" t="s" s="19">
-        <v>183</v>
+        <v>28</v>
       </c>
       <c r="D19" t="s" s="19">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="E19" t="s" s="19">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="F19" t="s" s="19">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="G19" t="s" s="19">
-        <v>32</v>
+        <v>53</v>
       </c>
       <c r="H19" t="s" s="19">
         <v>33</v>
       </c>
       <c r="I19" t="s" s="19">
-        <v>186</v>
+        <v>134</v>
       </c>
       <c r="J19" t="s" s="19">
-        <v>187</v>
+        <v>135</v>
       </c>
       <c r="K19" t="s" s="19">
         <v>188</v>
@@ -4119,25 +3725,25 @@
         <v>41</v>
       </c>
       <c r="S19" t="s" s="19">
+        <v>42</v>
+      </c>
+      <c r="T19" t="s" s="19">
+        <v>43</v>
+      </c>
+      <c r="U19" t="s" s="19">
+        <v>28</v>
+      </c>
+      <c r="V19" t="s" s="19">
         <v>190</v>
       </c>
-      <c r="T19" t="s" s="19">
-        <v>191</v>
-      </c>
-      <c r="U19" t="s" s="19">
-        <v>44</v>
-      </c>
-      <c r="V19" t="s" s="19">
-        <v>192</v>
-      </c>
       <c r="W19" t="s" s="19">
-        <v>193</v>
+        <v>61</v>
       </c>
       <c r="X19" t="s" s="19">
-        <v>194</v>
+        <v>47</v>
       </c>
       <c r="Y19" t="s" s="19">
-        <v>194</v>
+        <v>47</v>
       </c>
     </row>
     <row r="20">
@@ -4145,19 +3751,19 @@
         <v>107</v>
       </c>
       <c r="B20" t="s" s="20">
-        <v>195</v>
+        <v>191</v>
       </c>
       <c r="C20" t="s" s="20">
-        <v>196</v>
+        <v>192</v>
       </c>
       <c r="D20" t="s" s="20">
-        <v>197</v>
+        <v>193</v>
       </c>
       <c r="E20" t="s" s="20">
-        <v>198</v>
+        <v>193</v>
       </c>
       <c r="F20" t="s" s="20">
-        <v>199</v>
+        <v>194</v>
       </c>
       <c r="G20" t="s" s="20">
         <v>32</v>
@@ -4166,25 +3772,25 @@
         <v>33</v>
       </c>
       <c r="I20" t="s" s="20">
-        <v>200</v>
+        <v>195</v>
       </c>
       <c r="J20" t="s" s="20">
-        <v>201</v>
+        <v>196</v>
       </c>
       <c r="K20" t="s" s="20">
-        <v>202</v>
+        <v>197</v>
       </c>
       <c r="L20" t="s" s="20">
-        <v>124</v>
+        <v>28</v>
       </c>
       <c r="M20" t="s" s="20">
-        <v>203</v>
+        <v>28</v>
       </c>
       <c r="N20" t="s" s="20">
-        <v>204</v>
+        <v>198</v>
       </c>
       <c r="O20" t="s" s="20">
-        <v>204</v>
+        <v>198</v>
       </c>
       <c r="P20" t="s" s="20">
         <v>40</v>
@@ -4196,25 +3802,25 @@
         <v>41</v>
       </c>
       <c r="S20" t="s" s="20">
-        <v>42</v>
+        <v>199</v>
       </c>
       <c r="T20" t="s" s="20">
-        <v>43</v>
+        <v>200</v>
       </c>
       <c r="U20" t="s" s="20">
         <v>44</v>
       </c>
       <c r="V20" t="s" s="20">
-        <v>205</v>
+        <v>201</v>
       </c>
       <c r="W20" t="s" s="20">
-        <v>206</v>
+        <v>202</v>
       </c>
       <c r="X20" t="s" s="20">
-        <v>207</v>
+        <v>203</v>
       </c>
       <c r="Y20" t="s" s="20">
-        <v>207</v>
+        <v>203</v>
       </c>
     </row>
     <row r="21">
@@ -4222,19 +3828,19 @@
         <v>107</v>
       </c>
       <c r="B21" t="s" s="21">
+        <v>204</v>
+      </c>
+      <c r="C21" t="s" s="21">
+        <v>205</v>
+      </c>
+      <c r="D21" t="s" s="21">
+        <v>206</v>
+      </c>
+      <c r="E21" t="s" s="21">
+        <v>207</v>
+      </c>
+      <c r="F21" t="s" s="21">
         <v>208</v>
-      </c>
-      <c r="C21" t="s" s="21">
-        <v>209</v>
-      </c>
-      <c r="D21" t="s" s="21">
-        <v>210</v>
-      </c>
-      <c r="E21" t="s" s="21">
-        <v>210</v>
-      </c>
-      <c r="F21" t="s" s="21">
-        <v>199</v>
       </c>
       <c r="G21" t="s" s="21">
         <v>32</v>
@@ -4243,25 +3849,25 @@
         <v>33</v>
       </c>
       <c r="I21" t="s" s="21">
+        <v>209</v>
+      </c>
+      <c r="J21" t="s" s="21">
+        <v>210</v>
+      </c>
+      <c r="K21" t="s" s="21">
         <v>211</v>
       </c>
-      <c r="J21" t="s" s="21">
+      <c r="L21" t="s" s="21">
+        <v>124</v>
+      </c>
+      <c r="M21" t="s" s="21">
         <v>212</v>
       </c>
-      <c r="K21" t="s" s="21">
+      <c r="N21" t="s" s="21">
         <v>213</v>
       </c>
-      <c r="L21" t="s" s="21">
-        <v>92</v>
-      </c>
-      <c r="M21" t="s" s="21">
-        <v>214</v>
-      </c>
-      <c r="N21" t="s" s="21">
-        <v>215</v>
-      </c>
       <c r="O21" t="s" s="21">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="P21" t="s" s="21">
         <v>40</v>
@@ -4273,25 +3879,25 @@
         <v>41</v>
       </c>
       <c r="S21" t="s" s="21">
-        <v>216</v>
+        <v>42</v>
       </c>
       <c r="T21" t="s" s="21">
-        <v>217</v>
+        <v>43</v>
       </c>
       <c r="U21" t="s" s="21">
         <v>44</v>
       </c>
       <c r="V21" t="s" s="21">
-        <v>158</v>
+        <v>106</v>
       </c>
       <c r="W21" t="s" s="21">
-        <v>206</v>
+        <v>214</v>
       </c>
       <c r="X21" t="s" s="21">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="Y21" t="s" s="21">
-        <v>218</v>
+        <v>215</v>
       </c>
     </row>
     <row r="22">
@@ -4299,46 +3905,46 @@
         <v>107</v>
       </c>
       <c r="B22" t="s" s="22">
+        <v>216</v>
+      </c>
+      <c r="C22" t="s" s="22">
+        <v>217</v>
+      </c>
+      <c r="D22" t="s" s="22">
+        <v>218</v>
+      </c>
+      <c r="E22" t="s" s="22">
+        <v>218</v>
+      </c>
+      <c r="F22" t="s" s="22">
+        <v>208</v>
+      </c>
+      <c r="G22" t="s" s="22">
+        <v>32</v>
+      </c>
+      <c r="H22" t="s" s="22">
+        <v>33</v>
+      </c>
+      <c r="I22" t="s" s="22">
         <v>219</v>
       </c>
-      <c r="C22" t="s" s="22">
-        <v>28</v>
-      </c>
-      <c r="D22" t="s" s="22">
+      <c r="J22" t="s" s="22">
         <v>220</v>
       </c>
-      <c r="E22" t="s" s="22">
+      <c r="K22" t="s" s="22">
         <v>221</v>
       </c>
-      <c r="F22" t="s" s="22">
+      <c r="L22" t="s" s="22">
+        <v>92</v>
+      </c>
+      <c r="M22" t="s" s="22">
         <v>222</v>
       </c>
-      <c r="G22" t="s" s="22">
+      <c r="N22" t="s" s="22">
         <v>223</v>
       </c>
-      <c r="H22" t="s" s="22">
-        <v>33</v>
-      </c>
-      <c r="I22" t="s" s="22">
-        <v>224</v>
-      </c>
-      <c r="J22" t="s" s="22">
-        <v>225</v>
-      </c>
-      <c r="K22" t="s" s="22">
-        <v>226</v>
-      </c>
-      <c r="L22" t="s" s="22">
-        <v>69</v>
-      </c>
-      <c r="M22" t="s" s="22">
-        <v>227</v>
-      </c>
-      <c r="N22" t="s" s="22">
-        <v>228</v>
-      </c>
       <c r="O22" t="s" s="22">
-        <v>228</v>
+        <v>223</v>
       </c>
       <c r="P22" t="s" s="22">
         <v>40</v>
@@ -4350,25 +3956,25 @@
         <v>41</v>
       </c>
       <c r="S22" t="s" s="22">
-        <v>127</v>
+        <v>224</v>
       </c>
       <c r="T22" t="s" s="22">
-        <v>128</v>
+        <v>225</v>
       </c>
       <c r="U22" t="s" s="22">
         <v>44</v>
       </c>
       <c r="V22" t="s" s="22">
-        <v>45</v>
+        <v>226</v>
       </c>
       <c r="W22" t="s" s="22">
-        <v>218</v>
+        <v>214</v>
       </c>
       <c r="X22" t="s" s="22">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="Y22" t="s" s="22">
-        <v>229</v>
+        <v>227</v>
       </c>
     </row>
     <row r="23">
@@ -4376,46 +3982,46 @@
         <v>107</v>
       </c>
       <c r="B23" t="s" s="23">
+        <v>228</v>
+      </c>
+      <c r="C23" t="s" s="23">
+        <v>28</v>
+      </c>
+      <c r="D23" t="s" s="23">
+        <v>229</v>
+      </c>
+      <c r="E23" t="s" s="23">
         <v>230</v>
       </c>
-      <c r="C23" t="s" s="23">
-        <v>28</v>
-      </c>
-      <c r="D23" t="s" s="23">
+      <c r="F23" t="s" s="23">
         <v>231</v>
       </c>
-      <c r="E23" t="s" s="23">
+      <c r="G23" t="s" s="23">
         <v>232</v>
       </c>
-      <c r="F23" t="s" s="23">
-        <v>185</v>
-      </c>
-      <c r="G23" t="s" s="23">
-        <v>32</v>
-      </c>
       <c r="H23" t="s" s="23">
         <v>33</v>
       </c>
       <c r="I23" t="s" s="23">
-        <v>100</v>
+        <v>233</v>
       </c>
       <c r="J23" t="s" s="23">
-        <v>101</v>
+        <v>234</v>
       </c>
       <c r="K23" t="s" s="23">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="L23" t="s" s="23">
-        <v>92</v>
+        <v>69</v>
       </c>
       <c r="M23" t="s" s="23">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="N23" t="s" s="23">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="O23" t="s" s="23">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="P23" t="s" s="23">
         <v>40</v>
@@ -4427,10 +4033,10 @@
         <v>41</v>
       </c>
       <c r="S23" t="s" s="23">
-        <v>138</v>
+        <v>127</v>
       </c>
       <c r="T23" t="s" s="23">
-        <v>139</v>
+        <v>128</v>
       </c>
       <c r="U23" t="s" s="23">
         <v>44</v>
@@ -4439,13 +4045,13 @@
         <v>45</v>
       </c>
       <c r="W23" t="s" s="23">
-        <v>207</v>
+        <v>227</v>
       </c>
       <c r="X23" t="s" s="23">
-        <v>45</v>
+        <v>238</v>
       </c>
       <c r="Y23" t="s" s="23">
-        <v>45</v>
+        <v>238</v>
       </c>
     </row>
     <row r="24">
@@ -4453,19 +4059,19 @@
         <v>107</v>
       </c>
       <c r="B24" t="s" s="24">
-        <v>236</v>
+        <v>239</v>
       </c>
       <c r="C24" t="s" s="24">
-        <v>237</v>
+        <v>28</v>
       </c>
       <c r="D24" t="s" s="24">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="E24" t="s" s="24">
-        <v>238</v>
+        <v>241</v>
       </c>
       <c r="F24" t="s" s="24">
-        <v>239</v>
+        <v>194</v>
       </c>
       <c r="G24" t="s" s="24">
         <v>32</v>
@@ -4474,25 +4080,25 @@
         <v>33</v>
       </c>
       <c r="I24" t="s" s="24">
-        <v>121</v>
+        <v>100</v>
       </c>
       <c r="J24" t="s" s="24">
-        <v>122</v>
+        <v>101</v>
       </c>
       <c r="K24" t="s" s="24">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="L24" t="s" s="24">
-        <v>124</v>
+        <v>92</v>
       </c>
       <c r="M24" t="s" s="24">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="N24" t="s" s="24">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="O24" t="s" s="24">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="P24" t="s" s="24">
         <v>40</v>
@@ -4504,25 +4110,25 @@
         <v>41</v>
       </c>
       <c r="S24" t="s" s="24">
-        <v>58</v>
+        <v>138</v>
       </c>
       <c r="T24" t="s" s="24">
-        <v>59</v>
+        <v>139</v>
       </c>
       <c r="U24" t="s" s="24">
         <v>44</v>
       </c>
       <c r="V24" t="s" s="24">
-        <v>158</v>
+        <v>45</v>
       </c>
       <c r="W24" t="s" s="24">
-        <v>243</v>
+        <v>215</v>
       </c>
       <c r="X24" t="s" s="24">
-        <v>33</v>
+        <v>245</v>
       </c>
       <c r="Y24" t="s" s="24">
-        <v>33</v>
+        <v>245</v>
       </c>
     </row>
     <row r="25">
@@ -4530,49 +4136,49 @@
         <v>107</v>
       </c>
       <c r="B25" t="s" s="25">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="C25" t="s" s="25">
-        <v>28</v>
+        <v>247</v>
       </c>
       <c r="D25" t="s" s="25">
-        <v>245</v>
+        <v>248</v>
       </c>
       <c r="E25" t="s" s="25">
-        <v>245</v>
+        <v>248</v>
       </c>
       <c r="F25" t="s" s="25">
-        <v>246</v>
+        <v>249</v>
       </c>
       <c r="G25" t="s" s="25">
-        <v>53</v>
+        <v>32</v>
       </c>
       <c r="H25" t="s" s="25">
         <v>33</v>
       </c>
       <c r="I25" t="s" s="25">
-        <v>247</v>
+        <v>121</v>
       </c>
       <c r="J25" t="s" s="25">
-        <v>248</v>
+        <v>122</v>
       </c>
       <c r="K25" t="s" s="25">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="L25" t="s" s="25">
-        <v>28</v>
+        <v>124</v>
       </c>
       <c r="M25" t="s" s="25">
-        <v>28</v>
+        <v>251</v>
       </c>
       <c r="N25" t="s" s="25">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="O25" t="s" s="25">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="P25" t="s" s="25">
-        <v>251</v>
+        <v>40</v>
       </c>
       <c r="Q25" t="s" s="25">
         <v>41</v>
@@ -4581,25 +4187,25 @@
         <v>41</v>
       </c>
       <c r="S25" t="s" s="25">
-        <v>252</v>
+        <v>58</v>
       </c>
       <c r="T25" t="s" s="25">
+        <v>59</v>
+      </c>
+      <c r="U25" t="s" s="25">
+        <v>44</v>
+      </c>
+      <c r="V25" t="s" s="25">
+        <v>226</v>
+      </c>
+      <c r="W25" t="s" s="25">
         <v>253</v>
       </c>
-      <c r="U25" t="s" s="25">
-        <v>28</v>
-      </c>
-      <c r="V25" t="s" s="25">
-        <v>254</v>
-      </c>
-      <c r="W25" t="s" s="25">
-        <v>33</v>
-      </c>
       <c r="X25" t="s" s="25">
-        <v>254</v>
+        <v>168</v>
       </c>
       <c r="Y25" t="s" s="25">
-        <v>254</v>
+        <v>168</v>
       </c>
     </row>
     <row r="26">
@@ -4607,19 +4213,19 @@
         <v>107</v>
       </c>
       <c r="B26" t="s" s="26">
+        <v>254</v>
+      </c>
+      <c r="C26" t="s" s="26">
         <v>255</v>
       </c>
-      <c r="C26" t="s" s="26">
+      <c r="D26" t="s" s="26">
         <v>256</v>
       </c>
-      <c r="D26" t="s" s="26">
+      <c r="E26" t="s" s="26">
+        <v>256</v>
+      </c>
+      <c r="F26" t="s" s="26">
         <v>257</v>
-      </c>
-      <c r="E26" t="s" s="26">
-        <v>257</v>
-      </c>
-      <c r="F26" t="s" s="26">
-        <v>246</v>
       </c>
       <c r="G26" t="s" s="26">
         <v>258</v>
@@ -4649,7 +4255,7 @@
         <v>263</v>
       </c>
       <c r="P26" t="s" s="26">
-        <v>251</v>
+        <v>40</v>
       </c>
       <c r="Q26" t="s" s="26">
         <v>41</v>
@@ -4658,25 +4264,25 @@
         <v>41</v>
       </c>
       <c r="S26" t="s" s="26">
-        <v>252</v>
+        <v>264</v>
       </c>
       <c r="T26" t="s" s="26">
-        <v>253</v>
+        <v>265</v>
       </c>
       <c r="U26" t="s" s="26">
         <v>44</v>
       </c>
       <c r="V26" t="s" s="26">
-        <v>158</v>
+        <v>226</v>
       </c>
       <c r="W26" t="s" s="26">
-        <v>33</v>
+        <v>168</v>
       </c>
       <c r="X26" t="s" s="26">
-        <v>158</v>
+        <v>33</v>
       </c>
       <c r="Y26" t="s" s="26">
-        <v>158</v>
+        <v>33</v>
       </c>
     </row>
     <row r="27">
@@ -4684,19 +4290,19 @@
         <v>107</v>
       </c>
       <c r="B27" t="s" s="27">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="C27" t="s" s="27">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="D27" t="s" s="27">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="E27" t="s" s="27">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="F27" t="s" s="27">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="G27" t="s" s="27">
         <v>32</v>
@@ -4705,28 +4311,28 @@
         <v>33</v>
       </c>
       <c r="I27" t="s" s="27">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="J27" t="s" s="27">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="K27" t="s" s="27">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="L27" t="s" s="27">
         <v>124</v>
       </c>
       <c r="M27" t="s" s="27">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="N27" t="s" s="27">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="O27" t="s" s="27">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="P27" t="s" s="27">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="Q27" t="s" s="27">
         <v>41</v>
@@ -4744,16 +4350,16 @@
         <v>44</v>
       </c>
       <c r="V27" t="s" s="27">
-        <v>274</v>
+        <v>203</v>
       </c>
       <c r="W27" t="s" s="27">
-        <v>149</v>
+        <v>276</v>
       </c>
       <c r="X27" t="s" s="27">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="Y27" t="s" s="27">
-        <v>275</v>
+        <v>277</v>
       </c>
     </row>
     <row r="28">
@@ -4761,19 +4367,19 @@
         <v>107</v>
       </c>
       <c r="B28" t="s" s="28">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="C28" t="s" s="28">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="D28" t="s" s="28">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="E28" t="s" s="28">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="F28" t="s" s="28">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="G28" t="s" s="28">
         <v>32</v>
@@ -4782,28 +4388,28 @@
         <v>33</v>
       </c>
       <c r="I28" t="s" s="28">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="J28" t="s" s="28">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="K28" t="s" s="28">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="L28" t="s" s="28">
         <v>81</v>
       </c>
       <c r="M28" t="s" s="28">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="N28" t="s" s="28">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="O28" t="s" s="28">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="P28" t="s" s="28">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="Q28" t="s" s="28">
         <v>41</v>
@@ -4812,19 +4418,19 @@
         <v>41</v>
       </c>
       <c r="S28" t="s" s="28">
-        <v>252</v>
+        <v>264</v>
       </c>
       <c r="T28" t="s" s="28">
-        <v>253</v>
+        <v>265</v>
       </c>
       <c r="U28" t="s" s="28">
         <v>44</v>
       </c>
       <c r="V28" t="s" s="28">
-        <v>205</v>
+        <v>106</v>
       </c>
       <c r="W28" t="s" s="28">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="X28" t="s" s="28">
         <v>117</v>
@@ -4838,19 +4444,19 @@
         <v>107</v>
       </c>
       <c r="B29" t="s" s="29">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="C29" t="s" s="29">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="D29" t="s" s="29">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="E29" t="s" s="29">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="F29" t="s" s="29">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="G29" t="s" s="29">
         <v>32</v>
@@ -4859,28 +4465,28 @@
         <v>33</v>
       </c>
       <c r="I29" t="s" s="29">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="J29" t="s" s="29">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="K29" t="s" s="29">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="L29" t="s" s="29">
         <v>92</v>
       </c>
       <c r="M29" t="s" s="29">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="N29" t="s" s="29">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="O29" t="s" s="29">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="P29" t="s" s="29">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="Q29" t="s" s="29">
         <v>41</v>
@@ -4889,25 +4495,25 @@
         <v>41</v>
       </c>
       <c r="S29" t="s" s="29">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="T29" t="s" s="29">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="U29" t="s" s="29">
         <v>44</v>
       </c>
       <c r="V29" t="s" s="29">
-        <v>297</v>
+        <v>277</v>
       </c>
       <c r="W29" t="s" s="29">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="X29" t="s" s="29">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="Y29" t="s" s="29">
-        <v>298</v>
+        <v>299</v>
       </c>
     </row>
     <row r="30">
@@ -4915,46 +4521,46 @@
         <v>107</v>
       </c>
       <c r="B30" t="s" s="30">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="C30" t="s" s="30">
         <v>28</v>
       </c>
       <c r="D30" t="s" s="30">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="E30" t="s" s="30">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="F30" t="s" s="30">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="G30" t="s" s="30">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="H30" t="s" s="30">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="I30" t="s" s="30">
-        <v>224</v>
+        <v>233</v>
       </c>
       <c r="J30" t="s" s="30">
-        <v>225</v>
+        <v>234</v>
       </c>
       <c r="K30" t="s" s="30">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="L30" t="s" s="30">
         <v>69</v>
       </c>
       <c r="M30" t="s" s="30">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="N30" t="s" s="30">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="O30" t="s" s="30">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="P30" t="s" s="30">
         <v>40</v>
@@ -4966,10 +4572,10 @@
         <v>41</v>
       </c>
       <c r="S30" t="s" s="30">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="T30" t="s" s="30">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="U30" t="s" s="30">
         <v>44</v>
@@ -4981,10 +4587,10 @@
         <v>117</v>
       </c>
       <c r="X30" t="s" s="30">
-        <v>192</v>
+        <v>166</v>
       </c>
       <c r="Y30" t="s" s="30">
-        <v>192</v>
+        <v>166</v>
       </c>
     </row>
     <row r="31">
@@ -4992,13 +4598,13 @@
         <v>107</v>
       </c>
       <c r="B31" t="s" s="31">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="C31" t="s" s="31">
         <v>28</v>
       </c>
       <c r="D31" t="s" s="31">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="E31" t="s" s="31">
         <v>312</v>
@@ -5013,28 +4619,28 @@
         <v>33</v>
       </c>
       <c r="I31" t="s" s="31">
+        <v>134</v>
+      </c>
+      <c r="J31" t="s" s="31">
+        <v>135</v>
+      </c>
+      <c r="K31" t="s" s="31">
         <v>314</v>
       </c>
-      <c r="J31" t="s" s="31">
-        <v>315</v>
-      </c>
-      <c r="K31" t="s" s="31">
-        <v>316</v>
-      </c>
       <c r="L31" t="s" s="31">
-        <v>81</v>
+        <v>28</v>
       </c>
       <c r="M31" t="s" s="31">
-        <v>317</v>
+        <v>28</v>
       </c>
       <c r="N31" t="s" s="31">
-        <v>318</v>
+        <v>312</v>
       </c>
       <c r="O31" t="s" s="31">
-        <v>318</v>
+        <v>312</v>
       </c>
       <c r="P31" t="s" s="31">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="Q31" t="s" s="31">
         <v>41</v>
@@ -5043,25 +4649,25 @@
         <v>41</v>
       </c>
       <c r="S31" t="s" s="31">
-        <v>252</v>
+        <v>173</v>
       </c>
       <c r="T31" t="s" s="31">
-        <v>253</v>
+        <v>174</v>
       </c>
       <c r="U31" t="s" s="31">
         <v>44</v>
       </c>
       <c r="V31" t="s" s="31">
-        <v>319</v>
+        <v>33</v>
       </c>
       <c r="W31" t="s" s="31">
         <v>117</v>
       </c>
       <c r="X31" t="s" s="31">
-        <v>304</v>
+        <v>117</v>
       </c>
       <c r="Y31" t="s" s="31">
-        <v>304</v>
+        <v>117</v>
       </c>
     </row>
     <row r="32">
@@ -5069,49 +4675,49 @@
         <v>107</v>
       </c>
       <c r="B32" t="s" s="32">
+        <v>315</v>
+      </c>
+      <c r="C32" t="s" s="32">
+        <v>316</v>
+      </c>
+      <c r="D32" t="s" s="32">
+        <v>317</v>
+      </c>
+      <c r="E32" t="s" s="32">
+        <v>317</v>
+      </c>
+      <c r="F32" t="s" s="32">
+        <v>318</v>
+      </c>
+      <c r="G32" t="s" s="32">
+        <v>32</v>
+      </c>
+      <c r="H32" t="s" s="32">
+        <v>33</v>
+      </c>
+      <c r="I32" t="s" s="32">
+        <v>319</v>
+      </c>
+      <c r="J32" t="s" s="32">
         <v>320</v>
       </c>
-      <c r="C32" t="s" s="32">
-        <v>28</v>
-      </c>
-      <c r="D32" t="s" s="32">
+      <c r="K32" t="s" s="32">
         <v>321</v>
       </c>
-      <c r="E32" t="s" s="32">
-        <v>321</v>
-      </c>
-      <c r="F32" t="s" s="32">
-        <v>313</v>
-      </c>
-      <c r="G32" t="s" s="32">
-        <v>53</v>
-      </c>
-      <c r="H32" t="s" s="32">
-        <v>33</v>
-      </c>
-      <c r="I32" t="s" s="32">
-        <v>134</v>
-      </c>
-      <c r="J32" t="s" s="32">
-        <v>135</v>
-      </c>
-      <c r="K32" t="s" s="32">
+      <c r="L32" t="s" s="32">
+        <v>92</v>
+      </c>
+      <c r="M32" t="s" s="32">
+        <v>45</v>
+      </c>
+      <c r="N32" t="s" s="32">
         <v>322</v>
       </c>
-      <c r="L32" t="s" s="32">
-        <v>28</v>
-      </c>
-      <c r="M32" t="s" s="32">
-        <v>28</v>
-      </c>
-      <c r="N32" t="s" s="32">
-        <v>321</v>
-      </c>
       <c r="O32" t="s" s="32">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="P32" t="s" s="32">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="Q32" t="s" s="32">
         <v>41</v>
@@ -5120,25 +4726,25 @@
         <v>41</v>
       </c>
       <c r="S32" t="s" s="32">
-        <v>173</v>
+        <v>199</v>
       </c>
       <c r="T32" t="s" s="32">
-        <v>174</v>
+        <v>200</v>
       </c>
       <c r="U32" t="s" s="32">
         <v>44</v>
       </c>
       <c r="V32" t="s" s="32">
-        <v>33</v>
+        <v>226</v>
       </c>
       <c r="W32" t="s" s="32">
-        <v>117</v>
+        <v>323</v>
       </c>
       <c r="X32" t="s" s="32">
-        <v>117</v>
+        <v>324</v>
       </c>
       <c r="Y32" t="s" s="32">
-        <v>117</v>
+        <v>324</v>
       </c>
     </row>
     <row r="33">
@@ -5146,49 +4752,49 @@
         <v>107</v>
       </c>
       <c r="B33" t="s" s="33">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="C33" t="s" s="33">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="D33" t="s" s="33">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="E33" t="s" s="33">
-        <v>325</v>
+        <v>328</v>
       </c>
       <c r="F33" t="s" s="33">
-        <v>326</v>
+        <v>329</v>
       </c>
       <c r="G33" t="s" s="33">
-        <v>32</v>
+        <v>232</v>
       </c>
       <c r="H33" t="s" s="33">
         <v>33</v>
       </c>
       <c r="I33" t="s" s="33">
-        <v>327</v>
+        <v>330</v>
       </c>
       <c r="J33" t="s" s="33">
-        <v>328</v>
+        <v>331</v>
       </c>
       <c r="K33" t="s" s="33">
-        <v>329</v>
+        <v>332</v>
       </c>
       <c r="L33" t="s" s="33">
-        <v>92</v>
+        <v>69</v>
       </c>
       <c r="M33" t="s" s="33">
         <v>45</v>
       </c>
       <c r="N33" t="s" s="33">
-        <v>330</v>
+        <v>333</v>
       </c>
       <c r="O33" t="s" s="33">
-        <v>330</v>
+        <v>333</v>
       </c>
       <c r="P33" t="s" s="33">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="Q33" t="s" s="33">
         <v>41</v>
@@ -5197,25 +4803,25 @@
         <v>41</v>
       </c>
       <c r="S33" t="s" s="33">
-        <v>190</v>
+        <v>138</v>
       </c>
       <c r="T33" t="s" s="33">
-        <v>191</v>
+        <v>139</v>
       </c>
       <c r="U33" t="s" s="33">
         <v>44</v>
       </c>
       <c r="V33" t="s" s="33">
-        <v>158</v>
+        <v>334</v>
       </c>
       <c r="W33" t="s" s="33">
-        <v>331</v>
+        <v>324</v>
       </c>
       <c r="X33" t="s" s="33">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="Y33" t="s" s="33">
-        <v>332</v>
+        <v>335</v>
       </c>
     </row>
     <row r="34">
@@ -5223,76 +4829,76 @@
         <v>107</v>
       </c>
       <c r="B34" t="s" s="34">
-        <v>333</v>
+        <v>336</v>
       </c>
       <c r="C34" t="s" s="34">
-        <v>334</v>
+        <v>28</v>
       </c>
       <c r="D34" t="s" s="34">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="E34" t="s" s="34">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="F34" t="s" s="34">
-        <v>337</v>
+        <v>329</v>
       </c>
       <c r="G34" t="s" s="34">
-        <v>223</v>
+        <v>53</v>
       </c>
       <c r="H34" t="s" s="34">
         <v>33</v>
       </c>
       <c r="I34" t="s" s="34">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="J34" t="s" s="34">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="K34" t="s" s="34">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="L34" t="s" s="34">
-        <v>69</v>
+        <v>28</v>
       </c>
       <c r="M34" t="s" s="34">
-        <v>45</v>
+        <v>28</v>
       </c>
       <c r="N34" t="s" s="34">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="O34" t="s" s="34">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="P34" t="s" s="34">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="Q34" t="s" s="34">
-        <v>41</v>
+        <v>28</v>
       </c>
       <c r="R34" t="s" s="34">
         <v>41</v>
       </c>
       <c r="S34" t="s" s="34">
-        <v>138</v>
+        <v>343</v>
       </c>
       <c r="T34" t="s" s="34">
-        <v>139</v>
+        <v>344</v>
       </c>
       <c r="U34" t="s" s="34">
         <v>44</v>
       </c>
       <c r="V34" t="s" s="34">
-        <v>342</v>
+        <v>323</v>
       </c>
       <c r="W34" t="s" s="34">
-        <v>332</v>
+        <v>324</v>
       </c>
       <c r="X34" t="s" s="34">
-        <v>254</v>
+        <v>86</v>
       </c>
       <c r="Y34" t="s" s="34">
-        <v>254</v>
+        <v>86</v>
       </c>
     </row>
     <row r="35">
@@ -5300,76 +4906,76 @@
         <v>107</v>
       </c>
       <c r="B35" t="s" s="35">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="C35" t="s" s="35">
         <v>28</v>
       </c>
       <c r="D35" t="s" s="35">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="E35" t="s" s="35">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="F35" t="s" s="35">
-        <v>337</v>
+        <v>348</v>
       </c>
       <c r="G35" t="s" s="35">
-        <v>53</v>
+        <v>32</v>
       </c>
       <c r="H35" t="s" s="35">
         <v>33</v>
       </c>
       <c r="I35" t="s" s="35">
-        <v>346</v>
+        <v>349</v>
       </c>
       <c r="J35" t="s" s="35">
-        <v>347</v>
+        <v>350</v>
       </c>
       <c r="K35" t="s" s="35">
-        <v>348</v>
+        <v>351</v>
       </c>
       <c r="L35" t="s" s="35">
-        <v>28</v>
+        <v>37</v>
       </c>
       <c r="M35" t="s" s="35">
-        <v>28</v>
+        <v>352</v>
       </c>
       <c r="N35" t="s" s="35">
-        <v>349</v>
+        <v>353</v>
       </c>
       <c r="O35" t="s" s="35">
-        <v>349</v>
+        <v>353</v>
       </c>
       <c r="P35" t="s" s="35">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="Q35" t="s" s="35">
-        <v>28</v>
+        <v>41</v>
       </c>
       <c r="R35" t="s" s="35">
         <v>41</v>
       </c>
       <c r="S35" t="s" s="35">
-        <v>350</v>
+        <v>58</v>
       </c>
       <c r="T35" t="s" s="35">
-        <v>351</v>
+        <v>59</v>
       </c>
       <c r="U35" t="s" s="35">
         <v>44</v>
       </c>
       <c r="V35" t="s" s="35">
-        <v>274</v>
+        <v>226</v>
       </c>
       <c r="W35" t="s" s="35">
-        <v>332</v>
+        <v>354</v>
       </c>
       <c r="X35" t="s" s="35">
-        <v>86</v>
+        <v>277</v>
       </c>
       <c r="Y35" t="s" s="35">
-        <v>86</v>
+        <v>277</v>
       </c>
     </row>
     <row r="36">
@@ -5377,49 +4983,49 @@
         <v>107</v>
       </c>
       <c r="B36" t="s" s="36">
-        <v>352</v>
+        <v>355</v>
       </c>
       <c r="C36" t="s" s="36">
         <v>28</v>
       </c>
       <c r="D36" t="s" s="36">
-        <v>353</v>
+        <v>356</v>
       </c>
       <c r="E36" t="s" s="36">
-        <v>354</v>
+        <v>357</v>
       </c>
       <c r="F36" t="s" s="36">
-        <v>355</v>
+        <v>358</v>
       </c>
       <c r="G36" t="s" s="36">
-        <v>32</v>
+        <v>53</v>
       </c>
       <c r="H36" t="s" s="36">
         <v>33</v>
       </c>
       <c r="I36" t="s" s="36">
-        <v>356</v>
+        <v>359</v>
       </c>
       <c r="J36" t="s" s="36">
-        <v>357</v>
+        <v>360</v>
       </c>
       <c r="K36" t="s" s="36">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="L36" t="s" s="36">
-        <v>37</v>
+        <v>28</v>
       </c>
       <c r="M36" t="s" s="36">
-        <v>359</v>
+        <v>28</v>
       </c>
       <c r="N36" t="s" s="36">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="O36" t="s" s="36">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="P36" t="s" s="36">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="Q36" t="s" s="36">
         <v>41</v>
@@ -5428,25 +5034,25 @@
         <v>41</v>
       </c>
       <c r="S36" t="s" s="36">
-        <v>58</v>
+        <v>264</v>
       </c>
       <c r="T36" t="s" s="36">
-        <v>59</v>
+        <v>265</v>
       </c>
       <c r="U36" t="s" s="36">
         <v>44</v>
       </c>
       <c r="V36" t="s" s="36">
-        <v>158</v>
+        <v>226</v>
       </c>
       <c r="W36" t="s" s="36">
-        <v>297</v>
+        <v>277</v>
       </c>
       <c r="X36" t="s" s="36">
-        <v>275</v>
+        <v>363</v>
       </c>
       <c r="Y36" t="s" s="36">
-        <v>275</v>
+        <v>363</v>
       </c>
     </row>
     <row r="37">
@@ -5454,49 +5060,49 @@
         <v>107</v>
       </c>
       <c r="B37" t="s" s="37">
-        <v>361</v>
+        <v>364</v>
       </c>
       <c r="C37" t="s" s="37">
         <v>28</v>
       </c>
       <c r="D37" t="s" s="37">
-        <v>362</v>
+        <v>365</v>
       </c>
       <c r="E37" t="s" s="37">
-        <v>362</v>
+        <v>366</v>
       </c>
       <c r="F37" t="s" s="37">
-        <v>363</v>
+        <v>358</v>
       </c>
       <c r="G37" t="s" s="37">
-        <v>53</v>
+        <v>32</v>
       </c>
       <c r="H37" t="s" s="37">
         <v>33</v>
       </c>
       <c r="I37" t="s" s="37">
-        <v>364</v>
+        <v>367</v>
       </c>
       <c r="J37" t="s" s="37">
-        <v>365</v>
+        <v>368</v>
       </c>
       <c r="K37" t="s" s="37">
-        <v>366</v>
+        <v>369</v>
       </c>
       <c r="L37" t="s" s="37">
-        <v>81</v>
+        <v>124</v>
       </c>
       <c r="M37" t="s" s="37">
-        <v>28</v>
+        <v>370</v>
       </c>
       <c r="N37" t="s" s="37">
-        <v>367</v>
+        <v>371</v>
       </c>
       <c r="O37" t="s" s="37">
-        <v>367</v>
+        <v>371</v>
       </c>
       <c r="P37" t="s" s="37">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="Q37" t="s" s="37">
         <v>41</v>
@@ -5505,25 +5111,25 @@
         <v>41</v>
       </c>
       <c r="S37" t="s" s="37">
-        <v>350</v>
+        <v>72</v>
       </c>
       <c r="T37" t="s" s="37">
-        <v>351</v>
+        <v>73</v>
       </c>
       <c r="U37" t="s" s="37">
         <v>44</v>
       </c>
       <c r="V37" t="s" s="37">
-        <v>117</v>
+        <v>334</v>
       </c>
       <c r="W37" t="s" s="37">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="X37" t="s" s="37">
-        <v>86</v>
+        <v>245</v>
       </c>
       <c r="Y37" t="s" s="37">
-        <v>86</v>
+        <v>245</v>
       </c>
     </row>
     <row r="38">
@@ -5531,19 +5137,19 @@
         <v>107</v>
       </c>
       <c r="B38" t="s" s="38">
-        <v>368</v>
+        <v>372</v>
       </c>
       <c r="C38" t="s" s="38">
         <v>28</v>
       </c>
       <c r="D38" t="s" s="38">
-        <v>369</v>
+        <v>373</v>
       </c>
       <c r="E38" t="s" s="38">
-        <v>370</v>
+        <v>374</v>
       </c>
       <c r="F38" t="s" s="38">
-        <v>363</v>
+        <v>375</v>
       </c>
       <c r="G38" t="s" s="38">
         <v>53</v>
@@ -5552,55 +5158,55 @@
         <v>33</v>
       </c>
       <c r="I38" t="s" s="38">
-        <v>371</v>
+        <v>376</v>
       </c>
       <c r="J38" t="s" s="38">
-        <v>372</v>
+        <v>377</v>
       </c>
       <c r="K38" t="s" s="38">
-        <v>373</v>
+        <v>378</v>
       </c>
       <c r="L38" t="s" s="38">
-        <v>28</v>
+        <v>379</v>
       </c>
       <c r="M38" t="s" s="38">
         <v>28</v>
       </c>
       <c r="N38" t="s" s="38">
-        <v>374</v>
+        <v>380</v>
       </c>
       <c r="O38" t="s" s="38">
-        <v>374</v>
+        <v>380</v>
       </c>
       <c r="P38" t="s" s="38">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="Q38" t="s" s="38">
-        <v>41</v>
+        <v>28</v>
       </c>
       <c r="R38" t="s" s="38">
         <v>41</v>
       </c>
       <c r="S38" t="s" s="38">
-        <v>252</v>
+        <v>173</v>
       </c>
       <c r="T38" t="s" s="38">
-        <v>253</v>
+        <v>174</v>
       </c>
       <c r="U38" t="s" s="38">
         <v>44</v>
       </c>
       <c r="V38" t="s" s="38">
-        <v>158</v>
+        <v>381</v>
       </c>
       <c r="W38" t="s" s="38">
-        <v>275</v>
+        <v>363</v>
       </c>
       <c r="X38" t="s" s="38">
-        <v>375</v>
+        <v>238</v>
       </c>
       <c r="Y38" t="s" s="38">
-        <v>375</v>
+        <v>238</v>
       </c>
     </row>
     <row r="39">
@@ -5608,49 +5214,49 @@
         <v>107</v>
       </c>
       <c r="B39" t="s" s="39">
-        <v>376</v>
+        <v>382</v>
       </c>
       <c r="C39" t="s" s="39">
         <v>28</v>
       </c>
       <c r="D39" t="s" s="39">
-        <v>377</v>
+        <v>383</v>
       </c>
       <c r="E39" t="s" s="39">
-        <v>378</v>
+        <v>383</v>
       </c>
       <c r="F39" t="s" s="39">
-        <v>363</v>
+        <v>375</v>
       </c>
       <c r="G39" t="s" s="39">
-        <v>32</v>
+        <v>53</v>
       </c>
       <c r="H39" t="s" s="39">
         <v>33</v>
       </c>
       <c r="I39" t="s" s="39">
-        <v>379</v>
+        <v>384</v>
       </c>
       <c r="J39" t="s" s="39">
-        <v>380</v>
+        <v>385</v>
       </c>
       <c r="K39" t="s" s="39">
-        <v>381</v>
+        <v>386</v>
       </c>
       <c r="L39" t="s" s="39">
-        <v>124</v>
+        <v>37</v>
       </c>
       <c r="M39" t="s" s="39">
-        <v>382</v>
+        <v>28</v>
       </c>
       <c r="N39" t="s" s="39">
-        <v>383</v>
+        <v>387</v>
       </c>
       <c r="O39" t="s" s="39">
-        <v>383</v>
+        <v>387</v>
       </c>
       <c r="P39" t="s" s="39">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="Q39" t="s" s="39">
         <v>41</v>
@@ -5659,25 +5265,25 @@
         <v>41</v>
       </c>
       <c r="S39" t="s" s="39">
-        <v>72</v>
+        <v>58</v>
       </c>
       <c r="T39" t="s" s="39">
-        <v>73</v>
+        <v>59</v>
       </c>
       <c r="U39" t="s" s="39">
         <v>44</v>
       </c>
       <c r="V39" t="s" s="39">
-        <v>342</v>
+        <v>190</v>
       </c>
       <c r="W39" t="s" s="39">
-        <v>275</v>
+        <v>363</v>
       </c>
       <c r="X39" t="s" s="39">
-        <v>45</v>
+        <v>201</v>
       </c>
       <c r="Y39" t="s" s="39">
-        <v>45</v>
+        <v>201</v>
       </c>
     </row>
     <row r="40">
@@ -5685,76 +5291,76 @@
         <v>107</v>
       </c>
       <c r="B40" t="s" s="40">
-        <v>384</v>
+        <v>388</v>
       </c>
       <c r="C40" t="s" s="40">
-        <v>28</v>
+        <v>389</v>
       </c>
       <c r="D40" t="s" s="40">
-        <v>385</v>
+        <v>390</v>
       </c>
       <c r="E40" t="s" s="40">
-        <v>386</v>
+        <v>390</v>
       </c>
       <c r="F40" t="s" s="40">
-        <v>387</v>
+        <v>391</v>
       </c>
       <c r="G40" t="s" s="40">
-        <v>53</v>
+        <v>32</v>
       </c>
       <c r="H40" t="s" s="40">
         <v>33</v>
       </c>
       <c r="I40" t="s" s="40">
-        <v>388</v>
+        <v>100</v>
       </c>
       <c r="J40" t="s" s="40">
-        <v>389</v>
+        <v>101</v>
       </c>
       <c r="K40" t="s" s="40">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="L40" t="s" s="40">
-        <v>391</v>
+        <v>92</v>
       </c>
       <c r="M40" t="s" s="40">
-        <v>28</v>
+        <v>393</v>
       </c>
       <c r="N40" t="s" s="40">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="O40" t="s" s="40">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="P40" t="s" s="40">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="Q40" t="s" s="40">
-        <v>28</v>
+        <v>41</v>
       </c>
       <c r="R40" t="s" s="40">
         <v>41</v>
       </c>
       <c r="S40" t="s" s="40">
-        <v>173</v>
+        <v>42</v>
       </c>
       <c r="T40" t="s" s="40">
-        <v>174</v>
+        <v>43</v>
       </c>
       <c r="U40" t="s" s="40">
         <v>44</v>
       </c>
       <c r="V40" t="s" s="40">
-        <v>285</v>
+        <v>33</v>
       </c>
       <c r="W40" t="s" s="40">
-        <v>375</v>
+        <v>363</v>
       </c>
       <c r="X40" t="s" s="40">
-        <v>229</v>
+        <v>203</v>
       </c>
       <c r="Y40" t="s" s="40">
-        <v>229</v>
+        <v>203</v>
       </c>
     </row>
     <row r="41">
@@ -5762,49 +5368,49 @@
         <v>107</v>
       </c>
       <c r="B41" t="s" s="41">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="C41" t="s" s="41">
-        <v>28</v>
+        <v>396</v>
       </c>
       <c r="D41" t="s" s="41">
-        <v>394</v>
+        <v>397</v>
       </c>
       <c r="E41" t="s" s="41">
-        <v>394</v>
+        <v>398</v>
       </c>
       <c r="F41" t="s" s="41">
-        <v>387</v>
+        <v>391</v>
       </c>
       <c r="G41" t="s" s="41">
-        <v>53</v>
+        <v>32</v>
       </c>
       <c r="H41" t="s" s="41">
         <v>33</v>
       </c>
       <c r="I41" t="s" s="41">
-        <v>395</v>
+        <v>292</v>
       </c>
       <c r="J41" t="s" s="41">
-        <v>396</v>
+        <v>293</v>
       </c>
       <c r="K41" t="s" s="41">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="L41" t="s" s="41">
-        <v>37</v>
+        <v>92</v>
       </c>
       <c r="M41" t="s" s="41">
-        <v>28</v>
+        <v>400</v>
       </c>
       <c r="N41" t="s" s="41">
-        <v>398</v>
+        <v>401</v>
       </c>
       <c r="O41" t="s" s="41">
-        <v>398</v>
+        <v>401</v>
       </c>
       <c r="P41" t="s" s="41">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="Q41" t="s" s="41">
         <v>41</v>
@@ -5813,25 +5419,25 @@
         <v>41</v>
       </c>
       <c r="S41" t="s" s="41">
-        <v>58</v>
+        <v>297</v>
       </c>
       <c r="T41" t="s" s="41">
-        <v>59</v>
+        <v>298</v>
       </c>
       <c r="U41" t="s" s="41">
         <v>44</v>
       </c>
       <c r="V41" t="s" s="41">
-        <v>181</v>
+        <v>226</v>
       </c>
       <c r="W41" t="s" s="41">
-        <v>375</v>
+        <v>203</v>
       </c>
       <c r="X41" t="s" s="41">
-        <v>399</v>
+        <v>402</v>
       </c>
       <c r="Y41" t="s" s="41">
-        <v>399</v>
+        <v>402</v>
       </c>
     </row>
     <row r="42">
@@ -5839,19 +5445,19 @@
         <v>107</v>
       </c>
       <c r="B42" t="s" s="42">
-        <v>400</v>
+        <v>403</v>
       </c>
       <c r="C42" t="s" s="42">
-        <v>401</v>
+        <v>404</v>
       </c>
       <c r="D42" t="s" s="42">
-        <v>402</v>
+        <v>405</v>
       </c>
       <c r="E42" t="s" s="42">
-        <v>402</v>
+        <v>405</v>
       </c>
       <c r="F42" t="s" s="42">
-        <v>403</v>
+        <v>391</v>
       </c>
       <c r="G42" t="s" s="42">
         <v>32</v>
@@ -5860,28 +5466,28 @@
         <v>33</v>
       </c>
       <c r="I42" t="s" s="42">
-        <v>100</v>
+        <v>406</v>
       </c>
       <c r="J42" t="s" s="42">
-        <v>101</v>
+        <v>407</v>
       </c>
       <c r="K42" t="s" s="42">
-        <v>404</v>
+        <v>408</v>
       </c>
       <c r="L42" t="s" s="42">
         <v>92</v>
       </c>
       <c r="M42" t="s" s="42">
-        <v>405</v>
+        <v>409</v>
       </c>
       <c r="N42" t="s" s="42">
-        <v>406</v>
+        <v>410</v>
       </c>
       <c r="O42" t="s" s="42">
-        <v>406</v>
+        <v>410</v>
       </c>
       <c r="P42" t="s" s="42">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="Q42" t="s" s="42">
         <v>41</v>
@@ -5890,25 +5496,25 @@
         <v>41</v>
       </c>
       <c r="S42" t="s" s="42">
-        <v>42</v>
+        <v>199</v>
       </c>
       <c r="T42" t="s" s="42">
-        <v>43</v>
+        <v>200</v>
       </c>
       <c r="U42" t="s" s="42">
         <v>44</v>
       </c>
       <c r="V42" t="s" s="42">
-        <v>33</v>
+        <v>226</v>
       </c>
       <c r="W42" t="s" s="42">
-        <v>375</v>
+        <v>203</v>
       </c>
       <c r="X42" t="s" s="42">
-        <v>194</v>
+        <v>402</v>
       </c>
       <c r="Y42" t="s" s="42">
-        <v>194</v>
+        <v>402</v>
       </c>
     </row>
     <row r="43">
@@ -5916,49 +5522,49 @@
         <v>107</v>
       </c>
       <c r="B43" t="s" s="43">
-        <v>407</v>
+        <v>411</v>
       </c>
       <c r="C43" t="s" s="43">
-        <v>408</v>
+        <v>28</v>
       </c>
       <c r="D43" t="s" s="43">
-        <v>409</v>
+        <v>412</v>
       </c>
       <c r="E43" t="s" s="43">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="F43" t="s" s="43">
-        <v>403</v>
+        <v>391</v>
       </c>
       <c r="G43" t="s" s="43">
-        <v>32</v>
+        <v>53</v>
       </c>
       <c r="H43" t="s" s="43">
         <v>33</v>
       </c>
       <c r="I43" t="s" s="43">
-        <v>290</v>
+        <v>134</v>
       </c>
       <c r="J43" t="s" s="43">
-        <v>291</v>
+        <v>135</v>
       </c>
       <c r="K43" t="s" s="43">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="L43" t="s" s="43">
-        <v>92</v>
+        <v>28</v>
       </c>
       <c r="M43" t="s" s="43">
-        <v>412</v>
+        <v>28</v>
       </c>
       <c r="N43" t="s" s="43">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="O43" t="s" s="43">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="P43" t="s" s="43">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="Q43" t="s" s="43">
         <v>41</v>
@@ -5967,25 +5573,25 @@
         <v>41</v>
       </c>
       <c r="S43" t="s" s="43">
-        <v>295</v>
+        <v>173</v>
       </c>
       <c r="T43" t="s" s="43">
-        <v>296</v>
+        <v>174</v>
       </c>
       <c r="U43" t="s" s="43">
         <v>44</v>
       </c>
       <c r="V43" t="s" s="43">
-        <v>158</v>
+        <v>415</v>
       </c>
       <c r="W43" t="s" s="43">
-        <v>194</v>
+        <v>203</v>
       </c>
       <c r="X43" t="s" s="43">
-        <v>304</v>
+        <v>45</v>
       </c>
       <c r="Y43" t="s" s="43">
-        <v>304</v>
+        <v>45</v>
       </c>
     </row>
     <row r="44">
@@ -5993,49 +5599,49 @@
         <v>107</v>
       </c>
       <c r="B44" t="s" s="44">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="C44" t="s" s="44">
-        <v>415</v>
+        <v>28</v>
       </c>
       <c r="D44" t="s" s="44">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="E44" t="s" s="44">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="F44" t="s" s="44">
-        <v>403</v>
+        <v>391</v>
       </c>
       <c r="G44" t="s" s="44">
-        <v>32</v>
+        <v>53</v>
       </c>
       <c r="H44" t="s" s="44">
         <v>33</v>
       </c>
       <c r="I44" t="s" s="44">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="J44" t="s" s="44">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="K44" t="s" s="44">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="L44" t="s" s="44">
-        <v>92</v>
+        <v>37</v>
       </c>
       <c r="M44" t="s" s="44">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="N44" t="s" s="44">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="O44" t="s" s="44">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="P44" t="s" s="44">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="Q44" t="s" s="44">
         <v>41</v>
@@ -6044,25 +5650,25 @@
         <v>41</v>
       </c>
       <c r="S44" t="s" s="44">
-        <v>190</v>
+        <v>264</v>
       </c>
       <c r="T44" t="s" s="44">
-        <v>191</v>
+        <v>265</v>
       </c>
       <c r="U44" t="s" s="44">
         <v>44</v>
       </c>
       <c r="V44" t="s" s="44">
-        <v>158</v>
+        <v>226</v>
       </c>
       <c r="W44" t="s" s="44">
-        <v>194</v>
+        <v>203</v>
       </c>
       <c r="X44" t="s" s="44">
-        <v>304</v>
+        <v>402</v>
       </c>
       <c r="Y44" t="s" s="44">
-        <v>304</v>
+        <v>402</v>
       </c>
     </row>
     <row r="45">
@@ -6070,49 +5676,49 @@
         <v>107</v>
       </c>
       <c r="B45" t="s" s="45">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="C45" t="s" s="45">
         <v>28</v>
       </c>
       <c r="D45" t="s" s="45">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="E45" t="s" s="45">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="F45" t="s" s="45">
-        <v>403</v>
+        <v>257</v>
       </c>
       <c r="G45" t="s" s="45">
-        <v>53</v>
+        <v>426</v>
       </c>
       <c r="H45" t="s" s="45">
-        <v>33</v>
+        <v>305</v>
       </c>
       <c r="I45" t="s" s="45">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="J45" t="s" s="45">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="K45" t="s" s="45">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="L45" t="s" s="45">
-        <v>37</v>
+        <v>69</v>
       </c>
       <c r="M45" t="s" s="45">
-        <v>428</v>
+        <v>28</v>
       </c>
       <c r="N45" t="s" s="45">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="O45" t="s" s="45">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="P45" t="s" s="45">
-        <v>273</v>
+        <v>40</v>
       </c>
       <c r="Q45" t="s" s="45">
         <v>41</v>
@@ -6121,25 +5727,25 @@
         <v>41</v>
       </c>
       <c r="S45" t="s" s="45">
-        <v>252</v>
+        <v>264</v>
       </c>
       <c r="T45" t="s" s="45">
-        <v>253</v>
+        <v>265</v>
       </c>
       <c r="U45" t="s" s="45">
         <v>44</v>
       </c>
       <c r="V45" t="s" s="45">
-        <v>158</v>
+        <v>238</v>
       </c>
       <c r="W45" t="s" s="45">
-        <v>194</v>
+        <v>402</v>
       </c>
       <c r="X45" t="s" s="45">
-        <v>304</v>
+        <v>431</v>
       </c>
       <c r="Y45" t="s" s="45">
-        <v>304</v>
+        <v>431</v>
       </c>
     </row>
     <row r="46">
@@ -6147,49 +5753,49 @@
         <v>107</v>
       </c>
       <c r="B46" t="s" s="46">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="C46" t="s" s="46">
         <v>28</v>
       </c>
       <c r="D46" t="s" s="46">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="E46" t="s" s="46">
-        <v>431</v>
+        <v>434</v>
       </c>
       <c r="F46" t="s" s="46">
-        <v>246</v>
+        <v>435</v>
       </c>
       <c r="G46" t="s" s="46">
-        <v>432</v>
+        <v>32</v>
       </c>
       <c r="H46" t="s" s="46">
-        <v>304</v>
+        <v>33</v>
       </c>
       <c r="I46" t="s" s="46">
-        <v>433</v>
+        <v>436</v>
       </c>
       <c r="J46" t="s" s="46">
-        <v>434</v>
+        <v>437</v>
       </c>
       <c r="K46" t="s" s="46">
-        <v>435</v>
+        <v>438</v>
       </c>
       <c r="L46" t="s" s="46">
-        <v>69</v>
+        <v>124</v>
       </c>
       <c r="M46" t="s" s="46">
-        <v>28</v>
+        <v>439</v>
       </c>
       <c r="N46" t="s" s="46">
-        <v>436</v>
+        <v>440</v>
       </c>
       <c r="O46" t="s" s="46">
-        <v>436</v>
+        <v>440</v>
       </c>
       <c r="P46" t="s" s="46">
-        <v>251</v>
+        <v>275</v>
       </c>
       <c r="Q46" t="s" s="46">
         <v>41</v>
@@ -6198,25 +5804,25 @@
         <v>41</v>
       </c>
       <c r="S46" t="s" s="46">
-        <v>252</v>
+        <v>58</v>
       </c>
       <c r="T46" t="s" s="46">
-        <v>253</v>
+        <v>59</v>
       </c>
       <c r="U46" t="s" s="46">
         <v>44</v>
       </c>
       <c r="V46" t="s" s="46">
-        <v>437</v>
+        <v>226</v>
       </c>
       <c r="W46" t="s" s="46">
-        <v>304</v>
+        <v>402</v>
       </c>
       <c r="X46" t="s" s="46">
-        <v>437</v>
+        <v>305</v>
       </c>
       <c r="Y46" t="s" s="46">
-        <v>437</v>
+        <v>305</v>
       </c>
     </row>
     <row r="47">
@@ -6224,19 +5830,19 @@
         <v>107</v>
       </c>
       <c r="B47" t="s" s="47">
-        <v>438</v>
+        <v>441</v>
       </c>
       <c r="C47" t="s" s="47">
-        <v>28</v>
+        <v>442</v>
       </c>
       <c r="D47" t="s" s="47">
-        <v>439</v>
+        <v>443</v>
       </c>
       <c r="E47" t="s" s="47">
-        <v>440</v>
+        <v>443</v>
       </c>
       <c r="F47" t="s" s="47">
-        <v>441</v>
+        <v>444</v>
       </c>
       <c r="G47" t="s" s="47">
         <v>32</v>
@@ -6245,28 +5851,28 @@
         <v>33</v>
       </c>
       <c r="I47" t="s" s="47">
-        <v>442</v>
+        <v>121</v>
       </c>
       <c r="J47" t="s" s="47">
-        <v>443</v>
+        <v>122</v>
       </c>
       <c r="K47" t="s" s="47">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="L47" t="s" s="47">
         <v>124</v>
       </c>
       <c r="M47" t="s" s="47">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="N47" t="s" s="47">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="O47" t="s" s="47">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="P47" t="s" s="47">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="Q47" t="s" s="47">
         <v>41</v>
@@ -6284,16 +5890,16 @@
         <v>44</v>
       </c>
       <c r="V47" t="s" s="47">
-        <v>158</v>
+        <v>33</v>
       </c>
       <c r="W47" t="s" s="47">
-        <v>304</v>
+        <v>402</v>
       </c>
       <c r="X47" t="s" s="47">
-        <v>167</v>
+        <v>305</v>
       </c>
       <c r="Y47" t="s" s="47">
-        <v>167</v>
+        <v>305</v>
       </c>
     </row>
     <row r="48">
@@ -6301,10 +5907,10 @@
         <v>107</v>
       </c>
       <c r="B48" t="s" s="48">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="C48" t="s" s="48">
-        <v>448</v>
+        <v>28</v>
       </c>
       <c r="D48" t="s" s="48">
         <v>449</v>
@@ -6316,35 +5922,35 @@
         <v>450</v>
       </c>
       <c r="G48" t="s" s="48">
-        <v>32</v>
+        <v>426</v>
       </c>
       <c r="H48" t="s" s="48">
-        <v>33</v>
+        <v>305</v>
       </c>
       <c r="I48" t="s" s="48">
-        <v>121</v>
+        <v>427</v>
       </c>
       <c r="J48" t="s" s="48">
-        <v>122</v>
+        <v>428</v>
       </c>
       <c r="K48" t="s" s="48">
         <v>451</v>
       </c>
       <c r="L48" t="s" s="48">
-        <v>124</v>
+        <v>69</v>
       </c>
       <c r="M48" t="s" s="48">
+        <v>28</v>
+      </c>
+      <c r="N48" t="s" s="48">
         <v>452</v>
       </c>
-      <c r="N48" t="s" s="48">
+      <c r="O48" t="s" s="48">
+        <v>452</v>
+      </c>
+      <c r="P48" t="s" s="48">
         <v>453</v>
       </c>
-      <c r="O48" t="s" s="48">
-        <v>453</v>
-      </c>
-      <c r="P48" t="s" s="48">
-        <v>273</v>
-      </c>
       <c r="Q48" t="s" s="48">
         <v>41</v>
       </c>
@@ -6352,25 +5958,25 @@
         <v>41</v>
       </c>
       <c r="S48" t="s" s="48">
-        <v>58</v>
+        <v>264</v>
       </c>
       <c r="T48" t="s" s="48">
-        <v>59</v>
+        <v>265</v>
       </c>
       <c r="U48" t="s" s="48">
         <v>44</v>
       </c>
       <c r="V48" t="s" s="48">
-        <v>33</v>
+        <v>238</v>
       </c>
       <c r="W48" t="s" s="48">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="X48" t="s" s="48">
-        <v>167</v>
+        <v>238</v>
       </c>
       <c r="Y48" t="s" s="48">
-        <v>167</v>
+        <v>238</v>
       </c>
     </row>
     <row r="49">
@@ -6381,46 +5987,46 @@
         <v>454</v>
       </c>
       <c r="C49" t="s" s="49">
-        <v>28</v>
+        <v>455</v>
       </c>
       <c r="D49" t="s" s="49">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="E49" t="s" s="49">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="F49" t="s" s="49">
-        <v>456</v>
+        <v>444</v>
       </c>
       <c r="G49" t="s" s="49">
-        <v>432</v>
+        <v>232</v>
       </c>
       <c r="H49" t="s" s="49">
-        <v>304</v>
+        <v>33</v>
       </c>
       <c r="I49" t="s" s="49">
-        <v>433</v>
+        <v>457</v>
       </c>
       <c r="J49" t="s" s="49">
-        <v>434</v>
+        <v>458</v>
       </c>
       <c r="K49" t="s" s="49">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="L49" t="s" s="49">
         <v>69</v>
       </c>
       <c r="M49" t="s" s="49">
-        <v>28</v>
+        <v>45</v>
       </c>
       <c r="N49" t="s" s="49">
-        <v>458</v>
+        <v>460</v>
       </c>
       <c r="O49" t="s" s="49">
-        <v>458</v>
+        <v>460</v>
       </c>
       <c r="P49" t="s" s="49">
-        <v>251</v>
+        <v>275</v>
       </c>
       <c r="Q49" t="s" s="49">
         <v>41</v>
@@ -6429,25 +6035,25 @@
         <v>41</v>
       </c>
       <c r="S49" t="s" s="49">
-        <v>252</v>
+        <v>72</v>
       </c>
       <c r="T49" t="s" s="49">
-        <v>253</v>
+        <v>73</v>
       </c>
       <c r="U49" t="s" s="49">
         <v>44</v>
       </c>
       <c r="V49" t="s" s="49">
-        <v>437</v>
+        <v>226</v>
       </c>
       <c r="W49" t="s" s="49">
-        <v>167</v>
+        <v>305</v>
       </c>
       <c r="X49" t="s" s="49">
-        <v>229</v>
+        <v>166</v>
       </c>
       <c r="Y49" t="s" s="49">
-        <v>229</v>
+        <v>166</v>
       </c>
     </row>
     <row r="50">
@@ -6455,49 +6061,49 @@
         <v>107</v>
       </c>
       <c r="B50" t="s" s="50">
-        <v>459</v>
+        <v>461</v>
       </c>
       <c r="C50" t="s" s="50">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="D50" t="s" s="50">
-        <v>461</v>
+        <v>463</v>
       </c>
       <c r="E50" t="s" s="50">
-        <v>461</v>
+        <v>463</v>
       </c>
       <c r="F50" t="s" s="50">
-        <v>450</v>
+        <v>444</v>
       </c>
       <c r="G50" t="s" s="50">
-        <v>223</v>
+        <v>232</v>
       </c>
       <c r="H50" t="s" s="50">
         <v>33</v>
       </c>
       <c r="I50" t="s" s="50">
-        <v>462</v>
+        <v>464</v>
       </c>
       <c r="J50" t="s" s="50">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="K50" t="s" s="50">
-        <v>464</v>
+        <v>466</v>
       </c>
       <c r="L50" t="s" s="50">
         <v>69</v>
       </c>
       <c r="M50" t="s" s="50">
-        <v>45</v>
+        <v>299</v>
       </c>
       <c r="N50" t="s" s="50">
-        <v>465</v>
+        <v>467</v>
       </c>
       <c r="O50" t="s" s="50">
-        <v>465</v>
+        <v>467</v>
       </c>
       <c r="P50" t="s" s="50">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="Q50" t="s" s="50">
         <v>41</v>
@@ -6515,16 +6121,16 @@
         <v>44</v>
       </c>
       <c r="V50" t="s" s="50">
-        <v>158</v>
+        <v>226</v>
       </c>
       <c r="W50" t="s" s="50">
-        <v>167</v>
+        <v>305</v>
       </c>
       <c r="X50" t="s" s="50">
-        <v>192</v>
+        <v>166</v>
       </c>
       <c r="Y50" t="s" s="50">
-        <v>192</v>
+        <v>166</v>
       </c>
     </row>
     <row r="51">
@@ -6532,49 +6138,49 @@
         <v>107</v>
       </c>
       <c r="B51" t="s" s="51">
-        <v>466</v>
+        <v>468</v>
       </c>
       <c r="C51" t="s" s="51">
-        <v>467</v>
+        <v>469</v>
       </c>
       <c r="D51" t="s" s="51">
-        <v>468</v>
+        <v>470</v>
       </c>
       <c r="E51" t="s" s="51">
-        <v>468</v>
+        <v>470</v>
       </c>
       <c r="F51" t="s" s="51">
-        <v>450</v>
+        <v>471</v>
       </c>
       <c r="G51" t="s" s="51">
-        <v>223</v>
+        <v>32</v>
       </c>
       <c r="H51" t="s" s="51">
         <v>33</v>
       </c>
       <c r="I51" t="s" s="51">
-        <v>469</v>
+        <v>121</v>
       </c>
       <c r="J51" t="s" s="51">
-        <v>470</v>
+        <v>122</v>
       </c>
       <c r="K51" t="s" s="51">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="L51" t="s" s="51">
-        <v>69</v>
+        <v>124</v>
       </c>
       <c r="M51" t="s" s="51">
-        <v>399</v>
+        <v>473</v>
       </c>
       <c r="N51" t="s" s="51">
-        <v>472</v>
+        <v>474</v>
       </c>
       <c r="O51" t="s" s="51">
-        <v>472</v>
+        <v>474</v>
       </c>
       <c r="P51" t="s" s="51">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="Q51" t="s" s="51">
         <v>41</v>
@@ -6583,25 +6189,25 @@
         <v>41</v>
       </c>
       <c r="S51" t="s" s="51">
-        <v>72</v>
+        <v>42</v>
       </c>
       <c r="T51" t="s" s="51">
-        <v>73</v>
+        <v>43</v>
       </c>
       <c r="U51" t="s" s="51">
         <v>44</v>
       </c>
       <c r="V51" t="s" s="51">
-        <v>158</v>
+        <v>276</v>
       </c>
       <c r="W51" t="s" s="51">
-        <v>167</v>
+        <v>305</v>
       </c>
       <c r="X51" t="s" s="51">
-        <v>192</v>
+        <v>431</v>
       </c>
       <c r="Y51" t="s" s="51">
-        <v>192</v>
+        <v>431</v>
       </c>
     </row>
     <row r="52">
@@ -6609,49 +6215,49 @@
         <v>107</v>
       </c>
       <c r="B52" t="s" s="52">
-        <v>473</v>
+        <v>475</v>
       </c>
       <c r="C52" t="s" s="52">
-        <v>474</v>
+        <v>476</v>
       </c>
       <c r="D52" t="s" s="52">
-        <v>475</v>
+        <v>477</v>
       </c>
       <c r="E52" t="s" s="52">
-        <v>475</v>
+        <v>477</v>
       </c>
       <c r="F52" t="s" s="52">
-        <v>476</v>
+        <v>444</v>
       </c>
       <c r="G52" t="s" s="52">
-        <v>32</v>
+        <v>232</v>
       </c>
       <c r="H52" t="s" s="52">
         <v>33</v>
       </c>
       <c r="I52" t="s" s="52">
-        <v>121</v>
+        <v>478</v>
       </c>
       <c r="J52" t="s" s="52">
-        <v>122</v>
+        <v>479</v>
       </c>
       <c r="K52" t="s" s="52">
-        <v>477</v>
+        <v>480</v>
       </c>
       <c r="L52" t="s" s="52">
-        <v>124</v>
+        <v>92</v>
       </c>
       <c r="M52" t="s" s="52">
-        <v>478</v>
+        <v>481</v>
       </c>
       <c r="N52" t="s" s="52">
-        <v>479</v>
+        <v>482</v>
       </c>
       <c r="O52" t="s" s="52">
-        <v>479</v>
+        <v>482</v>
       </c>
       <c r="P52" t="s" s="52">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="Q52" t="s" s="52">
         <v>41</v>
@@ -6660,25 +6266,25 @@
         <v>41</v>
       </c>
       <c r="S52" t="s" s="52">
-        <v>42</v>
+        <v>127</v>
       </c>
       <c r="T52" t="s" s="52">
-        <v>43</v>
+        <v>128</v>
       </c>
       <c r="U52" t="s" s="52">
         <v>44</v>
       </c>
       <c r="V52" t="s" s="52">
-        <v>106</v>
+        <v>226</v>
       </c>
       <c r="W52" t="s" s="52">
-        <v>167</v>
+        <v>305</v>
       </c>
       <c r="X52" t="s" s="52">
-        <v>437</v>
+        <v>166</v>
       </c>
       <c r="Y52" t="s" s="52">
-        <v>437</v>
+        <v>166</v>
       </c>
     </row>
     <row r="53">
@@ -6686,49 +6292,49 @@
         <v>107</v>
       </c>
       <c r="B53" t="s" s="53">
-        <v>480</v>
+        <v>483</v>
       </c>
       <c r="C53" t="s" s="53">
-        <v>481</v>
+        <v>484</v>
       </c>
       <c r="D53" t="s" s="53">
-        <v>482</v>
+        <v>485</v>
       </c>
       <c r="E53" t="s" s="53">
-        <v>482</v>
+        <v>485</v>
       </c>
       <c r="F53" t="s" s="53">
-        <v>450</v>
+        <v>444</v>
       </c>
       <c r="G53" t="s" s="53">
-        <v>223</v>
+        <v>32</v>
       </c>
       <c r="H53" t="s" s="53">
         <v>33</v>
       </c>
       <c r="I53" t="s" s="53">
-        <v>483</v>
+        <v>486</v>
       </c>
       <c r="J53" t="s" s="53">
-        <v>484</v>
+        <v>487</v>
       </c>
       <c r="K53" t="s" s="53">
-        <v>485</v>
+        <v>488</v>
       </c>
       <c r="L53" t="s" s="53">
         <v>92</v>
       </c>
       <c r="M53" t="s" s="53">
-        <v>486</v>
+        <v>489</v>
       </c>
       <c r="N53" t="s" s="53">
-        <v>487</v>
+        <v>490</v>
       </c>
       <c r="O53" t="s" s="53">
-        <v>487</v>
+        <v>490</v>
       </c>
       <c r="P53" t="s" s="53">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="Q53" t="s" s="53">
         <v>41</v>
@@ -6737,25 +6343,25 @@
         <v>41</v>
       </c>
       <c r="S53" t="s" s="53">
-        <v>127</v>
+        <v>297</v>
       </c>
       <c r="T53" t="s" s="53">
-        <v>128</v>
+        <v>298</v>
       </c>
       <c r="U53" t="s" s="53">
         <v>44</v>
       </c>
       <c r="V53" t="s" s="53">
-        <v>158</v>
+        <v>106</v>
       </c>
       <c r="W53" t="s" s="53">
-        <v>167</v>
+        <v>305</v>
       </c>
       <c r="X53" t="s" s="53">
-        <v>192</v>
+        <v>201</v>
       </c>
       <c r="Y53" t="s" s="53">
-        <v>192</v>
+        <v>201</v>
       </c>
     </row>
     <row r="54">
@@ -6763,49 +6369,49 @@
         <v>107</v>
       </c>
       <c r="B54" t="s" s="54">
-        <v>488</v>
+        <v>491</v>
       </c>
       <c r="C54" t="s" s="54">
-        <v>489</v>
+        <v>28</v>
       </c>
       <c r="D54" t="s" s="54">
-        <v>490</v>
+        <v>492</v>
       </c>
       <c r="E54" t="s" s="54">
-        <v>490</v>
+        <v>492</v>
       </c>
       <c r="F54" t="s" s="54">
-        <v>450</v>
+        <v>471</v>
       </c>
       <c r="G54" t="s" s="54">
-        <v>32</v>
+        <v>53</v>
       </c>
       <c r="H54" t="s" s="54">
         <v>33</v>
       </c>
       <c r="I54" t="s" s="54">
-        <v>491</v>
+        <v>493</v>
       </c>
       <c r="J54" t="s" s="54">
-        <v>492</v>
+        <v>494</v>
       </c>
       <c r="K54" t="s" s="54">
-        <v>493</v>
+        <v>495</v>
       </c>
       <c r="L54" t="s" s="54">
-        <v>92</v>
+        <v>28</v>
       </c>
       <c r="M54" t="s" s="54">
-        <v>494</v>
+        <v>28</v>
       </c>
       <c r="N54" t="s" s="54">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="O54" t="s" s="54">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="P54" t="s" s="54">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="Q54" t="s" s="54">
         <v>41</v>
@@ -6814,25 +6420,25 @@
         <v>41</v>
       </c>
       <c r="S54" t="s" s="54">
-        <v>295</v>
+        <v>58</v>
       </c>
       <c r="T54" t="s" s="54">
-        <v>296</v>
+        <v>59</v>
       </c>
       <c r="U54" t="s" s="54">
         <v>44</v>
       </c>
       <c r="V54" t="s" s="54">
-        <v>205</v>
+        <v>33</v>
       </c>
       <c r="W54" t="s" s="54">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="X54" t="s" s="54">
-        <v>399</v>
+        <v>166</v>
       </c>
       <c r="Y54" t="s" s="54">
-        <v>399</v>
+        <v>166</v>
       </c>
     </row>
     <row r="55">
@@ -6840,19 +6446,19 @@
         <v>107</v>
       </c>
       <c r="B55" t="s" s="55">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="C55" t="s" s="55">
         <v>28</v>
       </c>
       <c r="D55" t="s" s="55">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="E55" t="s" s="55">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="F55" t="s" s="55">
-        <v>476</v>
+        <v>471</v>
       </c>
       <c r="G55" t="s" s="55">
         <v>53</v>
@@ -6861,28 +6467,28 @@
         <v>33</v>
       </c>
       <c r="I55" t="s" s="55">
-        <v>499</v>
+        <v>359</v>
       </c>
       <c r="J55" t="s" s="55">
+        <v>360</v>
+      </c>
+      <c r="K55" t="s" s="55">
         <v>500</v>
       </c>
-      <c r="K55" t="s" s="55">
+      <c r="L55" t="s" s="55">
+        <v>28</v>
+      </c>
+      <c r="M55" t="s" s="55">
+        <v>28</v>
+      </c>
+      <c r="N55" t="s" s="55">
         <v>501</v>
       </c>
-      <c r="L55" t="s" s="55">
-        <v>37</v>
-      </c>
-      <c r="M55" t="s" s="55">
-        <v>502</v>
-      </c>
-      <c r="N55" t="s" s="55">
-        <v>503</v>
-      </c>
       <c r="O55" t="s" s="55">
-        <v>503</v>
+        <v>501</v>
       </c>
       <c r="P55" t="s" s="55">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="Q55" t="s" s="55">
         <v>41</v>
@@ -6891,25 +6497,25 @@
         <v>41</v>
       </c>
       <c r="S55" t="s" s="55">
-        <v>252</v>
+        <v>264</v>
       </c>
       <c r="T55" t="s" s="55">
-        <v>253</v>
+        <v>265</v>
       </c>
       <c r="U55" t="s" s="55">
-        <v>44</v>
+        <v>28</v>
       </c>
       <c r="V55" t="s" s="55">
-        <v>205</v>
+        <v>381</v>
       </c>
       <c r="W55" t="s" s="55">
-        <v>192</v>
+        <v>166</v>
       </c>
       <c r="X55" t="s" s="55">
-        <v>298</v>
+        <v>45</v>
       </c>
       <c r="Y55" t="s" s="55">
-        <v>298</v>
+        <v>45</v>
       </c>
     </row>
     <row r="56">
@@ -6917,40 +6523,40 @@
         <v>107</v>
       </c>
       <c r="B56" t="s" s="56">
+        <v>502</v>
+      </c>
+      <c r="C56" t="s" s="56">
+        <v>503</v>
+      </c>
+      <c r="D56" t="s" s="56">
         <v>504</v>
       </c>
-      <c r="C56" t="s" s="56">
-        <v>28</v>
-      </c>
-      <c r="D56" t="s" s="56">
+      <c r="E56" t="s" s="56">
+        <v>504</v>
+      </c>
+      <c r="F56" t="s" s="56">
+        <v>471</v>
+      </c>
+      <c r="G56" t="s" s="56">
+        <v>258</v>
+      </c>
+      <c r="H56" t="s" s="56">
+        <v>33</v>
+      </c>
+      <c r="I56" t="s" s="56">
         <v>505</v>
       </c>
-      <c r="E56" t="s" s="56">
-        <v>505</v>
-      </c>
-      <c r="F56" t="s" s="56">
-        <v>476</v>
-      </c>
-      <c r="G56" t="s" s="56">
-        <v>53</v>
-      </c>
-      <c r="H56" t="s" s="56">
-        <v>33</v>
-      </c>
-      <c r="I56" t="s" s="56">
+      <c r="J56" t="s" s="56">
         <v>506</v>
       </c>
-      <c r="J56" t="s" s="56">
+      <c r="K56" t="s" s="56">
         <v>507</v>
       </c>
-      <c r="K56" t="s" s="56">
+      <c r="L56" t="s" s="56">
+        <v>69</v>
+      </c>
+      <c r="M56" t="s" s="56">
         <v>508</v>
-      </c>
-      <c r="L56" t="s" s="56">
-        <v>28</v>
-      </c>
-      <c r="M56" t="s" s="56">
-        <v>28</v>
       </c>
       <c r="N56" t="s" s="56">
         <v>509</v>
@@ -6959,7 +6565,7 @@
         <v>509</v>
       </c>
       <c r="P56" t="s" s="56">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="Q56" t="s" s="56">
         <v>41</v>
@@ -6968,25 +6574,25 @@
         <v>41</v>
       </c>
       <c r="S56" t="s" s="56">
-        <v>58</v>
+        <v>72</v>
       </c>
       <c r="T56" t="s" s="56">
-        <v>59</v>
+        <v>73</v>
       </c>
       <c r="U56" t="s" s="56">
         <v>44</v>
       </c>
       <c r="V56" t="s" s="56">
-        <v>33</v>
+        <v>226</v>
       </c>
       <c r="W56" t="s" s="56">
-        <v>192</v>
+        <v>166</v>
       </c>
       <c r="X56" t="s" s="56">
-        <v>192</v>
+        <v>201</v>
       </c>
       <c r="Y56" t="s" s="56">
-        <v>192</v>
+        <v>201</v>
       </c>
     </row>
     <row r="57">
@@ -7006,37 +6612,37 @@
         <v>512</v>
       </c>
       <c r="F57" t="s" s="57">
-        <v>476</v>
+        <v>471</v>
       </c>
       <c r="G57" t="s" s="57">
-        <v>53</v>
+        <v>32</v>
       </c>
       <c r="H57" t="s" s="57">
         <v>33</v>
       </c>
       <c r="I57" t="s" s="57">
-        <v>371</v>
+        <v>513</v>
       </c>
       <c r="J57" t="s" s="57">
-        <v>372</v>
+        <v>514</v>
       </c>
       <c r="K57" t="s" s="57">
-        <v>513</v>
+        <v>515</v>
       </c>
       <c r="L57" t="s" s="57">
-        <v>28</v>
+        <v>124</v>
       </c>
       <c r="M57" t="s" s="57">
-        <v>28</v>
+        <v>516</v>
       </c>
       <c r="N57" t="s" s="57">
-        <v>514</v>
+        <v>517</v>
       </c>
       <c r="O57" t="s" s="57">
-        <v>514</v>
+        <v>517</v>
       </c>
       <c r="P57" t="s" s="57">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="Q57" t="s" s="57">
         <v>41</v>
@@ -7045,25 +6651,25 @@
         <v>41</v>
       </c>
       <c r="S57" t="s" s="57">
-        <v>252</v>
+        <v>518</v>
       </c>
       <c r="T57" t="s" s="57">
-        <v>253</v>
+        <v>519</v>
       </c>
       <c r="U57" t="s" s="57">
-        <v>28</v>
+        <v>44</v>
       </c>
       <c r="V57" t="s" s="57">
-        <v>515</v>
+        <v>276</v>
       </c>
       <c r="W57" t="s" s="57">
-        <v>192</v>
+        <v>305</v>
       </c>
       <c r="X57" t="s" s="57">
-        <v>86</v>
+        <v>431</v>
       </c>
       <c r="Y57" t="s" s="57">
-        <v>86</v>
+        <v>431</v>
       </c>
     </row>
     <row r="58">
@@ -7071,49 +6677,49 @@
         <v>107</v>
       </c>
       <c r="B58" t="s" s="58">
-        <v>516</v>
+        <v>520</v>
       </c>
       <c r="C58" t="s" s="58">
-        <v>517</v>
+        <v>28</v>
       </c>
       <c r="D58" t="s" s="58">
-        <v>518</v>
+        <v>521</v>
       </c>
       <c r="E58" t="s" s="58">
-        <v>518</v>
+        <v>521</v>
       </c>
       <c r="F58" t="s" s="58">
-        <v>476</v>
+        <v>522</v>
       </c>
       <c r="G58" t="s" s="58">
-        <v>258</v>
+        <v>53</v>
       </c>
       <c r="H58" t="s" s="58">
         <v>33</v>
       </c>
       <c r="I58" t="s" s="58">
-        <v>519</v>
+        <v>134</v>
       </c>
       <c r="J58" t="s" s="58">
-        <v>520</v>
+        <v>135</v>
       </c>
       <c r="K58" t="s" s="58">
+        <v>523</v>
+      </c>
+      <c r="L58" t="s" s="58">
+        <v>28</v>
+      </c>
+      <c r="M58" t="s" s="58">
+        <v>28</v>
+      </c>
+      <c r="N58" t="s" s="58">
         <v>521</v>
       </c>
-      <c r="L58" t="s" s="58">
-        <v>69</v>
-      </c>
-      <c r="M58" t="s" s="58">
-        <v>522</v>
-      </c>
-      <c r="N58" t="s" s="58">
-        <v>523</v>
-      </c>
       <c r="O58" t="s" s="58">
-        <v>523</v>
+        <v>521</v>
       </c>
       <c r="P58" t="s" s="58">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="Q58" t="s" s="58">
         <v>41</v>
@@ -7122,25 +6728,25 @@
         <v>41</v>
       </c>
       <c r="S58" t="s" s="58">
-        <v>72</v>
+        <v>173</v>
       </c>
       <c r="T58" t="s" s="58">
-        <v>73</v>
+        <v>174</v>
       </c>
       <c r="U58" t="s" s="58">
         <v>44</v>
       </c>
       <c r="V58" t="s" s="58">
-        <v>158</v>
+        <v>33</v>
       </c>
       <c r="W58" t="s" s="58">
-        <v>192</v>
+        <v>201</v>
       </c>
       <c r="X58" t="s" s="58">
-        <v>399</v>
+        <v>201</v>
       </c>
       <c r="Y58" t="s" s="58">
-        <v>399</v>
+        <v>201</v>
       </c>
     </row>
     <row r="59">
@@ -7160,37 +6766,37 @@
         <v>526</v>
       </c>
       <c r="F59" t="s" s="59">
+        <v>522</v>
+      </c>
+      <c r="G59" t="s" s="59">
+        <v>32</v>
+      </c>
+      <c r="H59" t="s" s="59">
+        <v>33</v>
+      </c>
+      <c r="I59" t="s" s="59">
         <v>527</v>
       </c>
-      <c r="G59" t="s" s="59">
+      <c r="J59" t="s" s="59">
         <v>528</v>
       </c>
-      <c r="H59" t="s" s="59">
-        <v>304</v>
-      </c>
-      <c r="I59" t="s" s="59">
+      <c r="K59" t="s" s="59">
         <v>529</v>
-      </c>
-      <c r="J59" t="s" s="59">
-        <v>530</v>
-      </c>
-      <c r="K59" t="s" s="59">
-        <v>531</v>
       </c>
       <c r="L59" t="s" s="59">
         <v>124</v>
       </c>
       <c r="M59" t="s" s="59">
-        <v>532</v>
+        <v>530</v>
       </c>
       <c r="N59" t="s" s="59">
-        <v>533</v>
+        <v>531</v>
       </c>
       <c r="O59" t="s" s="59">
-        <v>533</v>
+        <v>531</v>
       </c>
       <c r="P59" t="s" s="59">
-        <v>251</v>
+        <v>275</v>
       </c>
       <c r="Q59" t="s" s="59">
         <v>41</v>
@@ -7199,25 +6805,25 @@
         <v>41</v>
       </c>
       <c r="S59" t="s" s="59">
-        <v>138</v>
+        <v>72</v>
       </c>
       <c r="T59" t="s" s="59">
-        <v>139</v>
+        <v>73</v>
       </c>
       <c r="U59" t="s" s="59">
         <v>44</v>
       </c>
       <c r="V59" t="s" s="59">
-        <v>399</v>
+        <v>532</v>
       </c>
       <c r="W59" t="s" s="59">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="X59" t="s" s="59">
-        <v>437</v>
+        <v>245</v>
       </c>
       <c r="Y59" t="s" s="59">
-        <v>437</v>
+        <v>245</v>
       </c>
     </row>
     <row r="60">
@@ -7225,10 +6831,10 @@
         <v>107</v>
       </c>
       <c r="B60" t="s" s="60">
+        <v>533</v>
+      </c>
+      <c r="C60" t="s" s="60">
         <v>534</v>
-      </c>
-      <c r="C60" t="s" s="60">
-        <v>28</v>
       </c>
       <c r="D60" t="s" s="60">
         <v>535</v>
@@ -7237,37 +6843,37 @@
         <v>535</v>
       </c>
       <c r="F60" t="s" s="60">
-        <v>476</v>
+        <v>536</v>
       </c>
       <c r="G60" t="s" s="60">
-        <v>53</v>
+        <v>232</v>
       </c>
       <c r="H60" t="s" s="60">
         <v>33</v>
       </c>
       <c r="I60" t="s" s="60">
-        <v>134</v>
+        <v>537</v>
       </c>
       <c r="J60" t="s" s="60">
-        <v>135</v>
+        <v>538</v>
       </c>
       <c r="K60" t="s" s="60">
-        <v>536</v>
+        <v>539</v>
       </c>
       <c r="L60" t="s" s="60">
-        <v>28</v>
+        <v>92</v>
       </c>
       <c r="M60" t="s" s="60">
-        <v>28</v>
+        <v>335</v>
       </c>
       <c r="N60" t="s" s="60">
-        <v>537</v>
+        <v>540</v>
       </c>
       <c r="O60" t="s" s="60">
-        <v>537</v>
+        <v>540</v>
       </c>
       <c r="P60" t="s" s="60">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="Q60" t="s" s="60">
         <v>41</v>
@@ -7276,25 +6882,25 @@
         <v>41</v>
       </c>
       <c r="S60" t="s" s="60">
-        <v>350</v>
+        <v>297</v>
       </c>
       <c r="T60" t="s" s="60">
-        <v>351</v>
+        <v>298</v>
       </c>
       <c r="U60" t="s" s="60">
-        <v>28</v>
+        <v>44</v>
       </c>
       <c r="V60" t="s" s="60">
-        <v>149</v>
+        <v>226</v>
       </c>
       <c r="W60" t="s" s="60">
-        <v>192</v>
+        <v>201</v>
       </c>
       <c r="X60" t="s" s="60">
-        <v>229</v>
+        <v>431</v>
       </c>
       <c r="Y60" t="s" s="60">
-        <v>229</v>
+        <v>431</v>
       </c>
     </row>
     <row r="61">
@@ -7302,19 +6908,19 @@
         <v>107</v>
       </c>
       <c r="B61" t="s" s="61">
-        <v>538</v>
+        <v>541</v>
       </c>
       <c r="C61" t="s" s="61">
-        <v>28</v>
+        <v>542</v>
       </c>
       <c r="D61" t="s" s="61">
-        <v>539</v>
+        <v>543</v>
       </c>
       <c r="E61" t="s" s="61">
-        <v>526</v>
+        <v>543</v>
       </c>
       <c r="F61" t="s" s="61">
-        <v>476</v>
+        <v>536</v>
       </c>
       <c r="G61" t="s" s="61">
         <v>32</v>
@@ -7323,28 +6929,28 @@
         <v>33</v>
       </c>
       <c r="I61" t="s" s="61">
-        <v>529</v>
+        <v>121</v>
       </c>
       <c r="J61" t="s" s="61">
-        <v>530</v>
+        <v>122</v>
       </c>
       <c r="K61" t="s" s="61">
-        <v>540</v>
+        <v>544</v>
       </c>
       <c r="L61" t="s" s="61">
-        <v>124</v>
+        <v>81</v>
       </c>
       <c r="M61" t="s" s="61">
-        <v>541</v>
+        <v>545</v>
       </c>
       <c r="N61" t="s" s="61">
-        <v>542</v>
+        <v>546</v>
       </c>
       <c r="O61" t="s" s="61">
-        <v>542</v>
+        <v>546</v>
       </c>
       <c r="P61" t="s" s="61">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="Q61" t="s" s="61">
         <v>41</v>
@@ -7353,25 +6959,25 @@
         <v>41</v>
       </c>
       <c r="S61" t="s" s="61">
-        <v>543</v>
+        <v>42</v>
       </c>
       <c r="T61" t="s" s="61">
-        <v>544</v>
+        <v>43</v>
       </c>
       <c r="U61" t="s" s="61">
         <v>44</v>
       </c>
       <c r="V61" t="s" s="61">
-        <v>106</v>
+        <v>33</v>
       </c>
       <c r="W61" t="s" s="61">
-        <v>167</v>
+        <v>201</v>
       </c>
       <c r="X61" t="s" s="61">
-        <v>437</v>
+        <v>299</v>
       </c>
       <c r="Y61" t="s" s="61">
-        <v>437</v>
+        <v>299</v>
       </c>
     </row>
     <row r="62">
@@ -7379,19 +6985,19 @@
         <v>107</v>
       </c>
       <c r="B62" t="s" s="62">
-        <v>545</v>
+        <v>547</v>
       </c>
       <c r="C62" t="s" s="62">
         <v>28</v>
       </c>
       <c r="D62" t="s" s="62">
-        <v>546</v>
+        <v>548</v>
       </c>
       <c r="E62" t="s" s="62">
-        <v>546</v>
+        <v>548</v>
       </c>
       <c r="F62" t="s" s="62">
-        <v>547</v>
+        <v>536</v>
       </c>
       <c r="G62" t="s" s="62">
         <v>53</v>
@@ -7400,13 +7006,13 @@
         <v>33</v>
       </c>
       <c r="I62" t="s" s="62">
-        <v>134</v>
+        <v>549</v>
       </c>
       <c r="J62" t="s" s="62">
-        <v>135</v>
+        <v>550</v>
       </c>
       <c r="K62" t="s" s="62">
-        <v>548</v>
+        <v>551</v>
       </c>
       <c r="L62" t="s" s="62">
         <v>28</v>
@@ -7415,13 +7021,13 @@
         <v>28</v>
       </c>
       <c r="N62" t="s" s="62">
-        <v>546</v>
+        <v>552</v>
       </c>
       <c r="O62" t="s" s="62">
-        <v>546</v>
+        <v>552</v>
       </c>
       <c r="P62" t="s" s="62">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="Q62" t="s" s="62">
         <v>41</v>
@@ -7430,25 +7036,25 @@
         <v>41</v>
       </c>
       <c r="S62" t="s" s="62">
-        <v>173</v>
+        <v>264</v>
       </c>
       <c r="T62" t="s" s="62">
-        <v>174</v>
+        <v>265</v>
       </c>
       <c r="U62" t="s" s="62">
         <v>44</v>
       </c>
       <c r="V62" t="s" s="62">
-        <v>33</v>
+        <v>226</v>
       </c>
       <c r="W62" t="s" s="62">
-        <v>399</v>
+        <v>299</v>
       </c>
       <c r="X62" t="s" s="62">
-        <v>399</v>
+        <v>431</v>
       </c>
       <c r="Y62" t="s" s="62">
-        <v>399</v>
+        <v>431</v>
       </c>
     </row>
     <row r="63">
@@ -7456,49 +7062,49 @@
         <v>107</v>
       </c>
       <c r="B63" t="s" s="63">
-        <v>549</v>
+        <v>553</v>
       </c>
       <c r="C63" t="s" s="63">
-        <v>28</v>
+        <v>554</v>
       </c>
       <c r="D63" t="s" s="63">
-        <v>550</v>
+        <v>555</v>
       </c>
       <c r="E63" t="s" s="63">
-        <v>551</v>
+        <v>555</v>
       </c>
       <c r="F63" t="s" s="63">
-        <v>547</v>
+        <v>536</v>
       </c>
       <c r="G63" t="s" s="63">
-        <v>32</v>
+        <v>556</v>
       </c>
       <c r="H63" t="s" s="63">
         <v>33</v>
       </c>
       <c r="I63" t="s" s="63">
-        <v>552</v>
+        <v>557</v>
       </c>
       <c r="J63" t="s" s="63">
-        <v>553</v>
+        <v>558</v>
       </c>
       <c r="K63" t="s" s="63">
-        <v>554</v>
+        <v>559</v>
       </c>
       <c r="L63" t="s" s="63">
-        <v>124</v>
+        <v>69</v>
       </c>
       <c r="M63" t="s" s="63">
-        <v>555</v>
+        <v>560</v>
       </c>
       <c r="N63" t="s" s="63">
-        <v>556</v>
+        <v>561</v>
       </c>
       <c r="O63" t="s" s="63">
-        <v>556</v>
+        <v>561</v>
       </c>
       <c r="P63" t="s" s="63">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="Q63" t="s" s="63">
         <v>41</v>
@@ -7516,16 +7122,16 @@
         <v>44</v>
       </c>
       <c r="V63" t="s" s="63">
-        <v>515</v>
+        <v>226</v>
       </c>
       <c r="W63" t="s" s="63">
-        <v>192</v>
+        <v>299</v>
       </c>
       <c r="X63" t="s" s="63">
-        <v>45</v>
+        <v>431</v>
       </c>
       <c r="Y63" t="s" s="63">
-        <v>45</v>
+        <v>431</v>
       </c>
     </row>
     <row r="64">
@@ -7533,49 +7139,49 @@
         <v>107</v>
       </c>
       <c r="B64" t="s" s="64">
-        <v>557</v>
+        <v>562</v>
       </c>
       <c r="C64" t="s" s="64">
-        <v>558</v>
+        <v>563</v>
       </c>
       <c r="D64" t="s" s="64">
-        <v>559</v>
+        <v>564</v>
       </c>
       <c r="E64" t="s" s="64">
-        <v>559</v>
+        <v>564</v>
       </c>
       <c r="F64" t="s" s="64">
-        <v>560</v>
+        <v>536</v>
       </c>
       <c r="G64" t="s" s="64">
-        <v>223</v>
+        <v>32</v>
       </c>
       <c r="H64" t="s" s="64">
         <v>33</v>
       </c>
       <c r="I64" t="s" s="64">
-        <v>561</v>
+        <v>436</v>
       </c>
       <c r="J64" t="s" s="64">
-        <v>562</v>
+        <v>437</v>
       </c>
       <c r="K64" t="s" s="64">
-        <v>563</v>
+        <v>565</v>
       </c>
       <c r="L64" t="s" s="64">
         <v>92</v>
       </c>
       <c r="M64" t="s" s="64">
-        <v>229</v>
+        <v>566</v>
       </c>
       <c r="N64" t="s" s="64">
-        <v>564</v>
+        <v>567</v>
       </c>
       <c r="O64" t="s" s="64">
-        <v>564</v>
+        <v>567</v>
       </c>
       <c r="P64" t="s" s="64">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="Q64" t="s" s="64">
         <v>41</v>
@@ -7584,25 +7190,25 @@
         <v>41</v>
       </c>
       <c r="S64" t="s" s="64">
-        <v>295</v>
+        <v>58</v>
       </c>
       <c r="T64" t="s" s="64">
-        <v>296</v>
+        <v>59</v>
       </c>
       <c r="U64" t="s" s="64">
         <v>44</v>
       </c>
       <c r="V64" t="s" s="64">
-        <v>158</v>
+        <v>106</v>
       </c>
       <c r="W64" t="s" s="64">
-        <v>399</v>
+        <v>299</v>
       </c>
       <c r="X64" t="s" s="64">
-        <v>437</v>
+        <v>238</v>
       </c>
       <c r="Y64" t="s" s="64">
-        <v>437</v>
+        <v>238</v>
       </c>
     </row>
     <row r="65">
@@ -7610,19 +7216,19 @@
         <v>107</v>
       </c>
       <c r="B65" t="s" s="65">
-        <v>565</v>
+        <v>568</v>
       </c>
       <c r="C65" t="s" s="65">
-        <v>566</v>
+        <v>569</v>
       </c>
       <c r="D65" t="s" s="65">
-        <v>567</v>
+        <v>570</v>
       </c>
       <c r="E65" t="s" s="65">
-        <v>567</v>
+        <v>570</v>
       </c>
       <c r="F65" t="s" s="65">
-        <v>560</v>
+        <v>536</v>
       </c>
       <c r="G65" t="s" s="65">
         <v>32</v>
@@ -7631,55 +7237,55 @@
         <v>33</v>
       </c>
       <c r="I65" t="s" s="65">
-        <v>121</v>
+        <v>571</v>
       </c>
       <c r="J65" t="s" s="65">
-        <v>122</v>
+        <v>572</v>
       </c>
       <c r="K65" t="s" s="65">
-        <v>568</v>
+        <v>573</v>
       </c>
       <c r="L65" t="s" s="65">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="M65" t="s" s="65">
-        <v>569</v>
+        <v>45</v>
       </c>
       <c r="N65" t="s" s="65">
-        <v>570</v>
+        <v>574</v>
       </c>
       <c r="O65" t="s" s="65">
-        <v>570</v>
+        <v>574</v>
       </c>
       <c r="P65" t="s" s="65">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="Q65" t="s" s="65">
-        <v>41</v>
+        <v>28</v>
       </c>
       <c r="R65" t="s" s="65">
         <v>41</v>
       </c>
       <c r="S65" t="s" s="65">
-        <v>42</v>
+        <v>173</v>
       </c>
       <c r="T65" t="s" s="65">
-        <v>43</v>
+        <v>174</v>
       </c>
       <c r="U65" t="s" s="65">
         <v>44</v>
       </c>
       <c r="V65" t="s" s="65">
-        <v>33</v>
+        <v>532</v>
       </c>
       <c r="W65" t="s" s="65">
-        <v>399</v>
+        <v>299</v>
       </c>
       <c r="X65" t="s" s="65">
-        <v>298</v>
+        <v>45</v>
       </c>
       <c r="Y65" t="s" s="65">
-        <v>298</v>
+        <v>45</v>
       </c>
     </row>
     <row r="66">
@@ -7687,19 +7293,19 @@
         <v>107</v>
       </c>
       <c r="B66" t="s" s="66">
-        <v>571</v>
+        <v>575</v>
       </c>
       <c r="C66" t="s" s="66">
         <v>28</v>
       </c>
       <c r="D66" t="s" s="66">
-        <v>572</v>
+        <v>576</v>
       </c>
       <c r="E66" t="s" s="66">
-        <v>572</v>
+        <v>576</v>
       </c>
       <c r="F66" t="s" s="66">
-        <v>560</v>
+        <v>536</v>
       </c>
       <c r="G66" t="s" s="66">
         <v>53</v>
@@ -7708,13 +7314,13 @@
         <v>33</v>
       </c>
       <c r="I66" t="s" s="66">
-        <v>573</v>
+        <v>577</v>
       </c>
       <c r="J66" t="s" s="66">
-        <v>574</v>
+        <v>578</v>
       </c>
       <c r="K66" t="s" s="66">
-        <v>575</v>
+        <v>579</v>
       </c>
       <c r="L66" t="s" s="66">
         <v>28</v>
@@ -7723,40 +7329,40 @@
         <v>28</v>
       </c>
       <c r="N66" t="s" s="66">
-        <v>576</v>
+        <v>580</v>
       </c>
       <c r="O66" t="s" s="66">
-        <v>576</v>
+        <v>580</v>
       </c>
       <c r="P66" t="s" s="66">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="Q66" t="s" s="66">
-        <v>41</v>
+        <v>28</v>
       </c>
       <c r="R66" t="s" s="66">
         <v>41</v>
       </c>
       <c r="S66" t="s" s="66">
-        <v>252</v>
+        <v>297</v>
       </c>
       <c r="T66" t="s" s="66">
-        <v>253</v>
+        <v>298</v>
       </c>
       <c r="U66" t="s" s="66">
         <v>44</v>
       </c>
       <c r="V66" t="s" s="66">
-        <v>158</v>
+        <v>190</v>
       </c>
       <c r="W66" t="s" s="66">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="X66" t="s" s="66">
-        <v>437</v>
+        <v>245</v>
       </c>
       <c r="Y66" t="s" s="66">
-        <v>437</v>
+        <v>245</v>
       </c>
     </row>
     <row r="67">
@@ -7764,49 +7370,49 @@
         <v>107</v>
       </c>
       <c r="B67" t="s" s="67">
-        <v>577</v>
+        <v>581</v>
       </c>
       <c r="C67" t="s" s="67">
-        <v>578</v>
+        <v>28</v>
       </c>
       <c r="D67" t="s" s="67">
-        <v>579</v>
+        <v>582</v>
       </c>
       <c r="E67" t="s" s="67">
-        <v>579</v>
+        <v>583</v>
       </c>
       <c r="F67" t="s" s="67">
-        <v>560</v>
+        <v>584</v>
       </c>
       <c r="G67" t="s" s="67">
-        <v>580</v>
+        <v>32</v>
       </c>
       <c r="H67" t="s" s="67">
         <v>33</v>
       </c>
       <c r="I67" t="s" s="67">
-        <v>581</v>
+        <v>513</v>
       </c>
       <c r="J67" t="s" s="67">
-        <v>582</v>
+        <v>514</v>
       </c>
       <c r="K67" t="s" s="67">
-        <v>583</v>
+        <v>585</v>
       </c>
       <c r="L67" t="s" s="67">
-        <v>69</v>
+        <v>124</v>
       </c>
       <c r="M67" t="s" s="67">
-        <v>584</v>
+        <v>586</v>
       </c>
       <c r="N67" t="s" s="67">
-        <v>585</v>
+        <v>587</v>
       </c>
       <c r="O67" t="s" s="67">
-        <v>585</v>
+        <v>587</v>
       </c>
       <c r="P67" t="s" s="67">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="Q67" t="s" s="67">
         <v>41</v>
@@ -7815,25 +7421,25 @@
         <v>41</v>
       </c>
       <c r="S67" t="s" s="67">
-        <v>72</v>
+        <v>83</v>
       </c>
       <c r="T67" t="s" s="67">
-        <v>73</v>
+        <v>84</v>
       </c>
       <c r="U67" t="s" s="67">
         <v>44</v>
       </c>
       <c r="V67" t="s" s="67">
-        <v>158</v>
+        <v>226</v>
       </c>
       <c r="W67" t="s" s="67">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="X67" t="s" s="67">
-        <v>437</v>
+        <v>238</v>
       </c>
       <c r="Y67" t="s" s="67">
-        <v>437</v>
+        <v>238</v>
       </c>
     </row>
     <row r="68">
@@ -7841,49 +7447,49 @@
         <v>107</v>
       </c>
       <c r="B68" t="s" s="68">
-        <v>586</v>
+        <v>588</v>
       </c>
       <c r="C68" t="s" s="68">
-        <v>587</v>
+        <v>589</v>
       </c>
       <c r="D68" t="s" s="68">
-        <v>588</v>
+        <v>590</v>
       </c>
       <c r="E68" t="s" s="68">
-        <v>588</v>
+        <v>590</v>
       </c>
       <c r="F68" t="s" s="68">
-        <v>560</v>
+        <v>584</v>
       </c>
       <c r="G68" t="s" s="68">
-        <v>32</v>
+        <v>232</v>
       </c>
       <c r="H68" t="s" s="68">
         <v>33</v>
       </c>
       <c r="I68" t="s" s="68">
-        <v>442</v>
+        <v>591</v>
       </c>
       <c r="J68" t="s" s="68">
-        <v>443</v>
+        <v>592</v>
       </c>
       <c r="K68" t="s" s="68">
-        <v>589</v>
+        <v>593</v>
       </c>
       <c r="L68" t="s" s="68">
         <v>92</v>
       </c>
       <c r="M68" t="s" s="68">
-        <v>590</v>
+        <v>594</v>
       </c>
       <c r="N68" t="s" s="68">
-        <v>591</v>
+        <v>595</v>
       </c>
       <c r="O68" t="s" s="68">
-        <v>591</v>
+        <v>595</v>
       </c>
       <c r="P68" t="s" s="68">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="Q68" t="s" s="68">
         <v>41</v>
@@ -7892,25 +7498,25 @@
         <v>41</v>
       </c>
       <c r="S68" t="s" s="68">
-        <v>58</v>
+        <v>596</v>
       </c>
       <c r="T68" t="s" s="68">
-        <v>59</v>
+        <v>597</v>
       </c>
       <c r="U68" t="s" s="68">
         <v>44</v>
       </c>
       <c r="V68" t="s" s="68">
-        <v>205</v>
+        <v>33</v>
       </c>
       <c r="W68" t="s" s="68">
-        <v>298</v>
+        <v>431</v>
       </c>
       <c r="X68" t="s" s="68">
-        <v>229</v>
+        <v>431</v>
       </c>
       <c r="Y68" t="s" s="68">
-        <v>229</v>
+        <v>431</v>
       </c>
     </row>
     <row r="69">
@@ -7918,19 +7524,19 @@
         <v>107</v>
       </c>
       <c r="B69" t="s" s="69">
-        <v>592</v>
+        <v>598</v>
       </c>
       <c r="C69" t="s" s="69">
         <v>28</v>
       </c>
       <c r="D69" t="s" s="69">
-        <v>593</v>
+        <v>599</v>
       </c>
       <c r="E69" t="s" s="69">
-        <v>594</v>
+        <v>600</v>
       </c>
       <c r="F69" t="s" s="69">
-        <v>560</v>
+        <v>584</v>
       </c>
       <c r="G69" t="s" s="69">
         <v>53</v>
@@ -7939,55 +7545,55 @@
         <v>33</v>
       </c>
       <c r="I69" t="s" s="69">
-        <v>595</v>
+        <v>601</v>
       </c>
       <c r="J69" t="s" s="69">
-        <v>596</v>
+        <v>602</v>
       </c>
       <c r="K69" t="s" s="69">
-        <v>597</v>
+        <v>603</v>
       </c>
       <c r="L69" t="s" s="69">
-        <v>37</v>
+        <v>604</v>
       </c>
       <c r="M69" t="s" s="69">
-        <v>598</v>
+        <v>605</v>
       </c>
       <c r="N69" t="s" s="69">
-        <v>599</v>
+        <v>606</v>
       </c>
       <c r="O69" t="s" s="69">
-        <v>599</v>
+        <v>606</v>
       </c>
       <c r="P69" t="s" s="69">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="Q69" t="s" s="69">
-        <v>28</v>
+        <v>41</v>
       </c>
       <c r="R69" t="s" s="69">
         <v>41</v>
       </c>
       <c r="S69" t="s" s="69">
-        <v>173</v>
+        <v>72</v>
       </c>
       <c r="T69" t="s" s="69">
-        <v>174</v>
+        <v>73</v>
       </c>
       <c r="U69" t="s" s="69">
         <v>44</v>
       </c>
       <c r="V69" t="s" s="69">
-        <v>158</v>
+        <v>106</v>
       </c>
       <c r="W69" t="s" s="69">
-        <v>298</v>
+        <v>431</v>
       </c>
       <c r="X69" t="s" s="69">
-        <v>437</v>
+        <v>335</v>
       </c>
       <c r="Y69" t="s" s="69">
-        <v>437</v>
+        <v>335</v>
       </c>
     </row>
     <row r="70">
@@ -7995,76 +7601,76 @@
         <v>107</v>
       </c>
       <c r="B70" t="s" s="70">
-        <v>600</v>
+        <v>607</v>
       </c>
       <c r="C70" t="s" s="70">
-        <v>28</v>
+        <v>608</v>
       </c>
       <c r="D70" t="s" s="70">
-        <v>601</v>
+        <v>609</v>
       </c>
       <c r="E70" t="s" s="70">
-        <v>601</v>
+        <v>609</v>
       </c>
       <c r="F70" t="s" s="70">
-        <v>560</v>
+        <v>584</v>
       </c>
       <c r="G70" t="s" s="70">
-        <v>53</v>
+        <v>232</v>
       </c>
       <c r="H70" t="s" s="70">
         <v>33</v>
       </c>
       <c r="I70" t="s" s="70">
-        <v>602</v>
+        <v>610</v>
       </c>
       <c r="J70" t="s" s="70">
-        <v>603</v>
+        <v>611</v>
       </c>
       <c r="K70" t="s" s="70">
-        <v>604</v>
+        <v>612</v>
       </c>
       <c r="L70" t="s" s="70">
-        <v>28</v>
+        <v>69</v>
       </c>
       <c r="M70" t="s" s="70">
-        <v>28</v>
+        <v>190</v>
       </c>
       <c r="N70" t="s" s="70">
-        <v>605</v>
+        <v>613</v>
       </c>
       <c r="O70" t="s" s="70">
-        <v>605</v>
+        <v>613</v>
       </c>
       <c r="P70" t="s" s="70">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="Q70" t="s" s="70">
-        <v>28</v>
+        <v>41</v>
       </c>
       <c r="R70" t="s" s="70">
         <v>41</v>
       </c>
       <c r="S70" t="s" s="70">
-        <v>295</v>
+        <v>72</v>
       </c>
       <c r="T70" t="s" s="70">
-        <v>296</v>
+        <v>73</v>
       </c>
       <c r="U70" t="s" s="70">
         <v>44</v>
       </c>
       <c r="V70" t="s" s="70">
-        <v>181</v>
+        <v>226</v>
       </c>
       <c r="W70" t="s" s="70">
-        <v>298</v>
+        <v>431</v>
       </c>
       <c r="X70" t="s" s="70">
-        <v>45</v>
+        <v>238</v>
       </c>
       <c r="Y70" t="s" s="70">
-        <v>45</v>
+        <v>238</v>
       </c>
     </row>
     <row r="71">
@@ -8072,76 +7678,76 @@
         <v>107</v>
       </c>
       <c r="B71" t="s" s="71">
-        <v>606</v>
+        <v>614</v>
       </c>
       <c r="C71" t="s" s="71">
-        <v>28</v>
+        <v>615</v>
       </c>
       <c r="D71" t="s" s="71">
-        <v>607</v>
+        <v>616</v>
       </c>
       <c r="E71" t="s" s="71">
-        <v>608</v>
+        <v>616</v>
       </c>
       <c r="F71" t="s" s="71">
-        <v>609</v>
+        <v>617</v>
       </c>
       <c r="G71" t="s" s="71">
-        <v>32</v>
+        <v>53</v>
       </c>
       <c r="H71" t="s" s="71">
         <v>33</v>
       </c>
       <c r="I71" t="s" s="71">
-        <v>529</v>
+        <v>618</v>
       </c>
       <c r="J71" t="s" s="71">
-        <v>530</v>
+        <v>619</v>
       </c>
       <c r="K71" t="s" s="71">
-        <v>610</v>
+        <v>620</v>
       </c>
       <c r="L71" t="s" s="71">
         <v>124</v>
       </c>
       <c r="M71" t="s" s="71">
-        <v>611</v>
+        <v>621</v>
       </c>
       <c r="N71" t="s" s="71">
-        <v>612</v>
+        <v>622</v>
       </c>
       <c r="O71" t="s" s="71">
-        <v>612</v>
+        <v>622</v>
       </c>
       <c r="P71" t="s" s="71">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="Q71" t="s" s="71">
-        <v>41</v>
+        <v>28</v>
       </c>
       <c r="R71" t="s" s="71">
         <v>41</v>
       </c>
       <c r="S71" t="s" s="71">
-        <v>83</v>
+        <v>138</v>
       </c>
       <c r="T71" t="s" s="71">
-        <v>84</v>
+        <v>139</v>
       </c>
       <c r="U71" t="s" s="71">
         <v>44</v>
       </c>
       <c r="V71" t="s" s="71">
-        <v>158</v>
+        <v>299</v>
       </c>
       <c r="W71" t="s" s="71">
-        <v>298</v>
+        <v>431</v>
       </c>
       <c r="X71" t="s" s="71">
-        <v>229</v>
+        <v>45</v>
       </c>
       <c r="Y71" t="s" s="71">
-        <v>229</v>
+        <v>45</v>
       </c>
     </row>
     <row r="72">
@@ -8149,49 +7755,49 @@
         <v>107</v>
       </c>
       <c r="B72" t="s" s="72">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="C72" t="s" s="72">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="D72" t="s" s="72">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="E72" t="s" s="72">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="F72" t="s" s="72">
-        <v>609</v>
+        <v>617</v>
       </c>
       <c r="G72" t="s" s="72">
-        <v>223</v>
+        <v>53</v>
       </c>
       <c r="H72" t="s" s="72">
         <v>33</v>
       </c>
       <c r="I72" t="s" s="72">
-        <v>616</v>
+        <v>618</v>
       </c>
       <c r="J72" t="s" s="72">
-        <v>617</v>
+        <v>619</v>
       </c>
       <c r="K72" t="s" s="72">
-        <v>618</v>
+        <v>620</v>
       </c>
       <c r="L72" t="s" s="72">
-        <v>92</v>
+        <v>124</v>
       </c>
       <c r="M72" t="s" s="72">
-        <v>619</v>
+        <v>621</v>
       </c>
       <c r="N72" t="s" s="72">
-        <v>620</v>
+        <v>623</v>
       </c>
       <c r="O72" t="s" s="72">
-        <v>620</v>
+        <v>623</v>
       </c>
       <c r="P72" t="s" s="72">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="Q72" t="s" s="72">
         <v>41</v>
@@ -8200,25 +7806,25 @@
         <v>41</v>
       </c>
       <c r="S72" t="s" s="72">
-        <v>621</v>
+        <v>173</v>
       </c>
       <c r="T72" t="s" s="72">
-        <v>622</v>
+        <v>174</v>
       </c>
       <c r="U72" t="s" s="72">
         <v>44</v>
       </c>
       <c r="V72" t="s" s="72">
-        <v>33</v>
+        <v>190</v>
       </c>
       <c r="W72" t="s" s="72">
-        <v>437</v>
+        <v>431</v>
       </c>
       <c r="X72" t="s" s="72">
-        <v>437</v>
+        <v>45</v>
       </c>
       <c r="Y72" t="s" s="72">
-        <v>437</v>
+        <v>45</v>
       </c>
     </row>
     <row r="73">
@@ -8226,49 +7832,49 @@
         <v>107</v>
       </c>
       <c r="B73" t="s" s="73">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="C73" t="s" s="73">
-        <v>28</v>
+        <v>625</v>
       </c>
       <c r="D73" t="s" s="73">
-        <v>624</v>
+        <v>626</v>
       </c>
       <c r="E73" t="s" s="73">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="F73" t="s" s="73">
-        <v>609</v>
+        <v>627</v>
       </c>
       <c r="G73" t="s" s="73">
-        <v>53</v>
+        <v>32</v>
       </c>
       <c r="H73" t="s" s="73">
         <v>33</v>
       </c>
       <c r="I73" t="s" s="73">
-        <v>626</v>
+        <v>436</v>
       </c>
       <c r="J73" t="s" s="73">
-        <v>627</v>
+        <v>437</v>
       </c>
       <c r="K73" t="s" s="73">
         <v>628</v>
       </c>
       <c r="L73" t="s" s="73">
+        <v>379</v>
+      </c>
+      <c r="M73" t="s" s="73">
         <v>629</v>
       </c>
-      <c r="M73" t="s" s="73">
+      <c r="N73" t="s" s="73">
         <v>630</v>
       </c>
-      <c r="N73" t="s" s="73">
-        <v>631</v>
-      </c>
       <c r="O73" t="s" s="73">
-        <v>631</v>
+        <v>630</v>
       </c>
       <c r="P73" t="s" s="73">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="Q73" t="s" s="73">
         <v>41</v>
@@ -8277,25 +7883,25 @@
         <v>41</v>
       </c>
       <c r="S73" t="s" s="73">
-        <v>72</v>
+        <v>58</v>
       </c>
       <c r="T73" t="s" s="73">
-        <v>73</v>
+        <v>59</v>
       </c>
       <c r="U73" t="s" s="73">
         <v>44</v>
       </c>
       <c r="V73" t="s" s="73">
-        <v>205</v>
+        <v>226</v>
       </c>
       <c r="W73" t="s" s="73">
-        <v>437</v>
+        <v>238</v>
       </c>
       <c r="X73" t="s" s="73">
-        <v>254</v>
+        <v>335</v>
       </c>
       <c r="Y73" t="s" s="73">
-        <v>254</v>
+        <v>335</v>
       </c>
     </row>
     <row r="74">
@@ -8303,49 +7909,49 @@
         <v>107</v>
       </c>
       <c r="B74" t="s" s="74">
+        <v>631</v>
+      </c>
+      <c r="C74" t="s" s="74">
         <v>632</v>
       </c>
-      <c r="C74" t="s" s="74">
+      <c r="D74" t="s" s="74">
         <v>633</v>
       </c>
-      <c r="D74" t="s" s="74">
+      <c r="E74" t="s" s="74">
+        <v>633</v>
+      </c>
+      <c r="F74" t="s" s="74">
         <v>634</v>
       </c>
-      <c r="E74" t="s" s="74">
-        <v>634</v>
-      </c>
-      <c r="F74" t="s" s="74">
-        <v>609</v>
-      </c>
       <c r="G74" t="s" s="74">
-        <v>223</v>
+        <v>32</v>
       </c>
       <c r="H74" t="s" s="74">
         <v>33</v>
       </c>
       <c r="I74" t="s" s="74">
+        <v>121</v>
+      </c>
+      <c r="J74" t="s" s="74">
+        <v>122</v>
+      </c>
+      <c r="K74" t="s" s="74">
         <v>635</v>
       </c>
-      <c r="J74" t="s" s="74">
+      <c r="L74" t="s" s="74">
+        <v>124</v>
+      </c>
+      <c r="M74" t="s" s="74">
         <v>636</v>
       </c>
-      <c r="K74" t="s" s="74">
+      <c r="N74" t="s" s="74">
         <v>637</v>
       </c>
-      <c r="L74" t="s" s="74">
-        <v>69</v>
-      </c>
-      <c r="M74" t="s" s="74">
-        <v>181</v>
-      </c>
-      <c r="N74" t="s" s="74">
-        <v>638</v>
-      </c>
       <c r="O74" t="s" s="74">
-        <v>638</v>
+        <v>637</v>
       </c>
       <c r="P74" t="s" s="74">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="Q74" t="s" s="74">
         <v>41</v>
@@ -8363,16 +7969,16 @@
         <v>44</v>
       </c>
       <c r="V74" t="s" s="74">
-        <v>158</v>
+        <v>106</v>
       </c>
       <c r="W74" t="s" s="74">
-        <v>437</v>
+        <v>335</v>
       </c>
       <c r="X74" t="s" s="74">
-        <v>229</v>
+        <v>245</v>
       </c>
       <c r="Y74" t="s" s="74">
-        <v>229</v>
+        <v>245</v>
       </c>
     </row>
     <row r="75">
@@ -8380,19 +7986,19 @@
         <v>107</v>
       </c>
       <c r="B75" t="s" s="75">
+        <v>638</v>
+      </c>
+      <c r="C75" t="s" s="75">
+        <v>28</v>
+      </c>
+      <c r="D75" t="s" s="75">
         <v>639</v>
       </c>
-      <c r="C75" t="s" s="75">
-        <v>640</v>
-      </c>
-      <c r="D75" t="s" s="75">
-        <v>641</v>
-      </c>
       <c r="E75" t="s" s="75">
-        <v>641</v>
+        <v>639</v>
       </c>
       <c r="F75" t="s" s="75">
-        <v>609</v>
+        <v>634</v>
       </c>
       <c r="G75" t="s" s="75">
         <v>53</v>
@@ -8401,28 +8007,28 @@
         <v>33</v>
       </c>
       <c r="I75" t="s" s="75">
-        <v>642</v>
+        <v>134</v>
       </c>
       <c r="J75" t="s" s="75">
-        <v>643</v>
+        <v>135</v>
       </c>
       <c r="K75" t="s" s="75">
-        <v>644</v>
+        <v>640</v>
       </c>
       <c r="L75" t="s" s="75">
-        <v>124</v>
+        <v>28</v>
       </c>
       <c r="M75" t="s" s="75">
-        <v>645</v>
+        <v>28</v>
       </c>
       <c r="N75" t="s" s="75">
-        <v>646</v>
+        <v>641</v>
       </c>
       <c r="O75" t="s" s="75">
-        <v>646</v>
+        <v>641</v>
       </c>
       <c r="P75" t="s" s="75">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="Q75" t="s" s="75">
         <v>41</v>
@@ -8431,25 +8037,25 @@
         <v>41</v>
       </c>
       <c r="S75" t="s" s="75">
-        <v>83</v>
+        <v>42</v>
       </c>
       <c r="T75" t="s" s="75">
-        <v>84</v>
+        <v>43</v>
       </c>
       <c r="U75" t="s" s="75">
         <v>44</v>
       </c>
       <c r="V75" t="s" s="75">
-        <v>149</v>
+        <v>106</v>
       </c>
       <c r="W75" t="s" s="75">
-        <v>437</v>
+        <v>335</v>
       </c>
       <c r="X75" t="s" s="75">
-        <v>45</v>
+        <v>245</v>
       </c>
       <c r="Y75" t="s" s="75">
-        <v>45</v>
+        <v>245</v>
       </c>
     </row>
     <row r="76">
@@ -8457,49 +8063,49 @@
         <v>107</v>
       </c>
       <c r="B76" t="s" s="76">
+        <v>642</v>
+      </c>
+      <c r="C76" t="s" s="76">
+        <v>643</v>
+      </c>
+      <c r="D76" t="s" s="76">
+        <v>644</v>
+      </c>
+      <c r="E76" t="s" s="76">
+        <v>644</v>
+      </c>
+      <c r="F76" t="s" s="76">
+        <v>645</v>
+      </c>
+      <c r="G76" t="s" s="76">
+        <v>232</v>
+      </c>
+      <c r="H76" t="s" s="76">
+        <v>33</v>
+      </c>
+      <c r="I76" t="s" s="76">
+        <v>646</v>
+      </c>
+      <c r="J76" t="s" s="76">
         <v>647</v>
       </c>
-      <c r="C76" t="s" s="76">
+      <c r="K76" t="s" s="76">
         <v>648</v>
       </c>
-      <c r="D76" t="s" s="76">
+      <c r="L76" t="s" s="76">
+        <v>69</v>
+      </c>
+      <c r="M76" t="s" s="76">
         <v>649</v>
       </c>
-      <c r="E76" t="s" s="76">
-        <v>649</v>
-      </c>
-      <c r="F76" t="s" s="76">
+      <c r="N76" t="s" s="76">
         <v>650</v>
       </c>
-      <c r="G76" t="s" s="76">
-        <v>258</v>
-      </c>
-      <c r="H76" t="s" s="76">
-        <v>33</v>
-      </c>
-      <c r="I76" t="s" s="76">
-        <v>651</v>
-      </c>
-      <c r="J76" t="s" s="76">
-        <v>652</v>
-      </c>
-      <c r="K76" t="s" s="76">
-        <v>653</v>
-      </c>
-      <c r="L76" t="s" s="76">
-        <v>124</v>
-      </c>
-      <c r="M76" t="s" s="76">
-        <v>654</v>
-      </c>
-      <c r="N76" t="s" s="76">
-        <v>655</v>
-      </c>
       <c r="O76" t="s" s="76">
-        <v>655</v>
+        <v>650</v>
       </c>
       <c r="P76" t="s" s="76">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="Q76" t="s" s="76">
         <v>41</v>
@@ -8508,25 +8114,25 @@
         <v>41</v>
       </c>
       <c r="S76" t="s" s="76">
-        <v>252</v>
+        <v>72</v>
       </c>
       <c r="T76" t="s" s="76">
-        <v>253</v>
+        <v>73</v>
       </c>
       <c r="U76" t="s" s="76">
         <v>44</v>
       </c>
       <c r="V76" t="s" s="76">
-        <v>158</v>
+        <v>226</v>
       </c>
       <c r="W76" t="s" s="76">
-        <v>229</v>
+        <v>86</v>
       </c>
       <c r="X76" t="s" s="76">
-        <v>254</v>
+        <v>245</v>
       </c>
       <c r="Y76" t="s" s="76">
-        <v>254</v>
+        <v>245</v>
       </c>
     </row>
     <row r="77">
@@ -8534,76 +8140,76 @@
         <v>107</v>
       </c>
       <c r="B77" t="s" s="77">
+        <v>651</v>
+      </c>
+      <c r="C77" t="s" s="77">
+        <v>652</v>
+      </c>
+      <c r="D77" t="s" s="77">
+        <v>653</v>
+      </c>
+      <c r="E77" t="s" s="77">
+        <v>653</v>
+      </c>
+      <c r="F77" t="s" s="77">
+        <v>645</v>
+      </c>
+      <c r="G77" t="s" s="77">
+        <v>32</v>
+      </c>
+      <c r="H77" t="s" s="77">
+        <v>33</v>
+      </c>
+      <c r="I77" t="s" s="77">
+        <v>121</v>
+      </c>
+      <c r="J77" t="s" s="77">
+        <v>122</v>
+      </c>
+      <c r="K77" t="s" s="77">
+        <v>654</v>
+      </c>
+      <c r="L77" t="s" s="77">
+        <v>124</v>
+      </c>
+      <c r="M77" t="s" s="77">
+        <v>655</v>
+      </c>
+      <c r="N77" t="s" s="77">
         <v>656</v>
       </c>
-      <c r="C77" t="s" s="77">
-        <v>28</v>
-      </c>
-      <c r="D77" t="s" s="77">
-        <v>657</v>
-      </c>
-      <c r="E77" t="s" s="77">
-        <v>658</v>
-      </c>
-      <c r="F77" t="s" s="77">
-        <v>650</v>
-      </c>
-      <c r="G77" t="s" s="77">
-        <v>53</v>
-      </c>
-      <c r="H77" t="s" s="77">
-        <v>33</v>
-      </c>
-      <c r="I77" t="s" s="77">
-        <v>659</v>
-      </c>
-      <c r="J77" t="s" s="77">
-        <v>660</v>
-      </c>
-      <c r="K77" t="s" s="77">
-        <v>661</v>
-      </c>
-      <c r="L77" t="s" s="77">
-        <v>37</v>
-      </c>
-      <c r="M77" t="s" s="77">
-        <v>662</v>
-      </c>
-      <c r="N77" t="s" s="77">
-        <v>663</v>
-      </c>
       <c r="O77" t="s" s="77">
-        <v>663</v>
+        <v>656</v>
       </c>
       <c r="P77" t="s" s="77">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="Q77" t="s" s="77">
-        <v>28</v>
+        <v>41</v>
       </c>
       <c r="R77" t="s" s="77">
         <v>41</v>
       </c>
       <c r="S77" t="s" s="77">
-        <v>173</v>
+        <v>58</v>
       </c>
       <c r="T77" t="s" s="77">
-        <v>174</v>
+        <v>59</v>
       </c>
       <c r="U77" t="s" s="77">
         <v>44</v>
       </c>
       <c r="V77" t="s" s="77">
-        <v>33</v>
+        <v>106</v>
       </c>
       <c r="W77" t="s" s="77">
-        <v>229</v>
+        <v>86</v>
       </c>
       <c r="X77" t="s" s="77">
-        <v>229</v>
+        <v>45</v>
       </c>
       <c r="Y77" t="s" s="77">
-        <v>229</v>
+        <v>45</v>
       </c>
     </row>
     <row r="78">
@@ -8611,76 +8217,76 @@
         <v>107</v>
       </c>
       <c r="B78" t="s" s="78">
-        <v>664</v>
+        <v>657</v>
       </c>
       <c r="C78" t="s" s="78">
-        <v>665</v>
+        <v>28</v>
       </c>
       <c r="D78" t="s" s="78">
-        <v>666</v>
+        <v>658</v>
       </c>
       <c r="E78" t="s" s="78">
-        <v>666</v>
+        <v>659</v>
       </c>
       <c r="F78" t="s" s="78">
-        <v>650</v>
+        <v>645</v>
       </c>
       <c r="G78" t="s" s="78">
-        <v>32</v>
+        <v>53</v>
       </c>
       <c r="H78" t="s" s="78">
         <v>33</v>
       </c>
       <c r="I78" t="s" s="78">
-        <v>442</v>
+        <v>28</v>
       </c>
       <c r="J78" t="s" s="78">
-        <v>443</v>
+        <v>28</v>
       </c>
       <c r="K78" t="s" s="78">
-        <v>667</v>
+        <v>660</v>
       </c>
       <c r="L78" t="s" s="78">
-        <v>391</v>
+        <v>37</v>
       </c>
       <c r="M78" t="s" s="78">
-        <v>668</v>
+        <v>661</v>
       </c>
       <c r="N78" t="s" s="78">
-        <v>669</v>
+        <v>662</v>
       </c>
       <c r="O78" t="s" s="78">
-        <v>669</v>
+        <v>662</v>
       </c>
       <c r="P78" t="s" s="78">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="Q78" t="s" s="78">
-        <v>41</v>
+        <v>28</v>
       </c>
       <c r="R78" t="s" s="78">
         <v>41</v>
       </c>
       <c r="S78" t="s" s="78">
-        <v>58</v>
+        <v>173</v>
       </c>
       <c r="T78" t="s" s="78">
-        <v>59</v>
+        <v>174</v>
       </c>
       <c r="U78" t="s" s="78">
         <v>44</v>
       </c>
       <c r="V78" t="s" s="78">
-        <v>158</v>
+        <v>33</v>
       </c>
       <c r="W78" t="s" s="78">
-        <v>229</v>
+        <v>86</v>
       </c>
       <c r="X78" t="s" s="78">
-        <v>254</v>
+        <v>86</v>
       </c>
       <c r="Y78" t="s" s="78">
-        <v>254</v>
+        <v>86</v>
       </c>
     </row>
     <row r="79">
@@ -8688,19 +8294,19 @@
         <v>107</v>
       </c>
       <c r="B79" t="s" s="79">
-        <v>670</v>
+        <v>663</v>
       </c>
       <c r="C79" t="s" s="79">
-        <v>671</v>
+        <v>664</v>
       </c>
       <c r="D79" t="s" s="79">
-        <v>672</v>
+        <v>665</v>
       </c>
       <c r="E79" t="s" s="79">
-        <v>672</v>
+        <v>665</v>
       </c>
       <c r="F79" t="s" s="79">
-        <v>673</v>
+        <v>645</v>
       </c>
       <c r="G79" t="s" s="79">
         <v>32</v>
@@ -8709,28 +8315,28 @@
         <v>33</v>
       </c>
       <c r="I79" t="s" s="79">
-        <v>121</v>
+        <v>436</v>
       </c>
       <c r="J79" t="s" s="79">
-        <v>122</v>
+        <v>437</v>
       </c>
       <c r="K79" t="s" s="79">
-        <v>674</v>
+        <v>666</v>
       </c>
       <c r="L79" t="s" s="79">
-        <v>124</v>
+        <v>92</v>
       </c>
       <c r="M79" t="s" s="79">
-        <v>675</v>
+        <v>667</v>
       </c>
       <c r="N79" t="s" s="79">
-        <v>676</v>
+        <v>668</v>
       </c>
       <c r="O79" t="s" s="79">
-        <v>676</v>
+        <v>668</v>
       </c>
       <c r="P79" t="s" s="79">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="Q79" t="s" s="79">
         <v>41</v>
@@ -8739,25 +8345,25 @@
         <v>41</v>
       </c>
       <c r="S79" t="s" s="79">
-        <v>72</v>
+        <v>58</v>
       </c>
       <c r="T79" t="s" s="79">
-        <v>73</v>
+        <v>59</v>
       </c>
       <c r="U79" t="s" s="79">
-        <v>44</v>
+        <v>669</v>
       </c>
       <c r="V79" t="s" s="79">
-        <v>205</v>
+        <v>226</v>
       </c>
       <c r="W79" t="s" s="79">
-        <v>254</v>
+        <v>86</v>
       </c>
       <c r="X79" t="s" s="79">
-        <v>45</v>
+        <v>245</v>
       </c>
       <c r="Y79" t="s" s="79">
-        <v>45</v>
+        <v>245</v>
       </c>
     </row>
     <row r="80">
@@ -8765,49 +8371,49 @@
         <v>107</v>
       </c>
       <c r="B80" t="s" s="80">
+        <v>670</v>
+      </c>
+      <c r="C80" t="s" s="80">
+        <v>671</v>
+      </c>
+      <c r="D80" t="s" s="80">
+        <v>672</v>
+      </c>
+      <c r="E80" t="s" s="80">
+        <v>673</v>
+      </c>
+      <c r="F80" t="s" s="80">
+        <v>674</v>
+      </c>
+      <c r="G80" t="s" s="80">
+        <v>232</v>
+      </c>
+      <c r="H80" t="s" s="80">
+        <v>33</v>
+      </c>
+      <c r="I80" t="s" s="80">
+        <v>675</v>
+      </c>
+      <c r="J80" t="s" s="80">
+        <v>676</v>
+      </c>
+      <c r="K80" t="s" s="80">
         <v>677</v>
       </c>
-      <c r="C80" t="s" s="80">
-        <v>28</v>
-      </c>
-      <c r="D80" t="s" s="80">
+      <c r="L80" t="s" s="80">
+        <v>69</v>
+      </c>
+      <c r="M80" t="s" s="80">
+        <v>560</v>
+      </c>
+      <c r="N80" t="s" s="80">
         <v>678</v>
       </c>
-      <c r="E80" t="s" s="80">
+      <c r="O80" t="s" s="80">
         <v>678</v>
       </c>
-      <c r="F80" t="s" s="80">
-        <v>673</v>
-      </c>
-      <c r="G80" t="s" s="80">
-        <v>53</v>
-      </c>
-      <c r="H80" t="s" s="80">
-        <v>33</v>
-      </c>
-      <c r="I80" t="s" s="80">
-        <v>134</v>
-      </c>
-      <c r="J80" t="s" s="80">
-        <v>135</v>
-      </c>
-      <c r="K80" t="s" s="80">
-        <v>679</v>
-      </c>
-      <c r="L80" t="s" s="80">
-        <v>28</v>
-      </c>
-      <c r="M80" t="s" s="80">
-        <v>28</v>
-      </c>
-      <c r="N80" t="s" s="80">
-        <v>680</v>
-      </c>
-      <c r="O80" t="s" s="80">
-        <v>680</v>
-      </c>
       <c r="P80" t="s" s="80">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="Q80" t="s" s="80">
         <v>41</v>
@@ -8816,25 +8422,25 @@
         <v>41</v>
       </c>
       <c r="S80" t="s" s="80">
-        <v>42</v>
+        <v>72</v>
       </c>
       <c r="T80" t="s" s="80">
-        <v>43</v>
+        <v>73</v>
       </c>
       <c r="U80" t="s" s="80">
         <v>44</v>
       </c>
       <c r="V80" t="s" s="80">
-        <v>205</v>
+        <v>33</v>
       </c>
       <c r="W80" t="s" s="80">
-        <v>254</v>
+        <v>245</v>
       </c>
       <c r="X80" t="s" s="80">
-        <v>45</v>
+        <v>245</v>
       </c>
       <c r="Y80" t="s" s="80">
-        <v>45</v>
+        <v>245</v>
       </c>
     </row>
     <row r="81">
@@ -8842,19 +8448,19 @@
         <v>107</v>
       </c>
       <c r="B81" t="s" s="81">
+        <v>679</v>
+      </c>
+      <c r="C81" t="s" s="81">
+        <v>28</v>
+      </c>
+      <c r="D81" t="s" s="81">
+        <v>680</v>
+      </c>
+      <c r="E81" t="s" s="81">
         <v>681</v>
       </c>
-      <c r="C81" t="s" s="81">
-        <v>28</v>
-      </c>
-      <c r="D81" t="s" s="81">
-        <v>682</v>
-      </c>
-      <c r="E81" t="s" s="81">
-        <v>682</v>
-      </c>
       <c r="F81" t="s" s="81">
-        <v>683</v>
+        <v>674</v>
       </c>
       <c r="G81" t="s" s="81">
         <v>53</v>
@@ -8863,28 +8469,28 @@
         <v>33</v>
       </c>
       <c r="I81" t="s" s="81">
-        <v>134</v>
+        <v>682</v>
       </c>
       <c r="J81" t="s" s="81">
-        <v>135</v>
+        <v>683</v>
       </c>
       <c r="K81" t="s" s="81">
-        <v>322</v>
+        <v>684</v>
       </c>
       <c r="L81" t="s" s="81">
-        <v>28</v>
+        <v>604</v>
       </c>
       <c r="M81" t="s" s="81">
-        <v>28</v>
+        <v>685</v>
       </c>
       <c r="N81" t="s" s="81">
-        <v>684</v>
+        <v>686</v>
       </c>
       <c r="O81" t="s" s="81">
-        <v>684</v>
+        <v>686</v>
       </c>
       <c r="P81" t="s" s="81">
-        <v>685</v>
+        <v>275</v>
       </c>
       <c r="Q81" t="s" s="81">
         <v>41</v>
@@ -8893,19 +8499,19 @@
         <v>41</v>
       </c>
       <c r="S81" t="s" s="81">
-        <v>350</v>
+        <v>72</v>
       </c>
       <c r="T81" t="s" s="81">
-        <v>351</v>
+        <v>73</v>
       </c>
       <c r="U81" t="s" s="81">
-        <v>686</v>
+        <v>44</v>
       </c>
       <c r="V81" t="s" s="81">
-        <v>205</v>
+        <v>226</v>
       </c>
       <c r="W81" t="s" s="81">
-        <v>86</v>
+        <v>245</v>
       </c>
       <c r="X81" t="s" s="81">
         <v>45</v>
@@ -8922,46 +8528,46 @@
         <v>687</v>
       </c>
       <c r="C82" t="s" s="82">
+        <v>28</v>
+      </c>
+      <c r="D82" t="s" s="82">
         <v>688</v>
       </c>
-      <c r="D82" t="s" s="82">
-        <v>367</v>
-      </c>
       <c r="E82" t="s" s="82">
-        <v>367</v>
+        <v>688</v>
       </c>
       <c r="F82" t="s" s="82">
-        <v>683</v>
+        <v>674</v>
       </c>
       <c r="G82" t="s" s="82">
-        <v>223</v>
+        <v>53</v>
       </c>
       <c r="H82" t="s" s="82">
         <v>33</v>
       </c>
       <c r="I82" t="s" s="82">
+        <v>134</v>
+      </c>
+      <c r="J82" t="s" s="82">
+        <v>135</v>
+      </c>
+      <c r="K82" t="s" s="82">
         <v>689</v>
       </c>
-      <c r="J82" t="s" s="82">
-        <v>690</v>
-      </c>
-      <c r="K82" t="s" s="82">
-        <v>691</v>
-      </c>
       <c r="L82" t="s" s="82">
-        <v>69</v>
+        <v>28</v>
       </c>
       <c r="M82" t="s" s="82">
-        <v>692</v>
+        <v>28</v>
       </c>
       <c r="N82" t="s" s="82">
-        <v>693</v>
+        <v>688</v>
       </c>
       <c r="O82" t="s" s="82">
-        <v>693</v>
+        <v>688</v>
       </c>
       <c r="P82" t="s" s="82">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="Q82" t="s" s="82">
         <v>41</v>
@@ -8970,25 +8576,25 @@
         <v>41</v>
       </c>
       <c r="S82" t="s" s="82">
-        <v>72</v>
+        <v>173</v>
       </c>
       <c r="T82" t="s" s="82">
-        <v>73</v>
+        <v>174</v>
       </c>
       <c r="U82" t="s" s="82">
         <v>44</v>
       </c>
       <c r="V82" t="s" s="82">
-        <v>158</v>
+        <v>33</v>
       </c>
       <c r="W82" t="s" s="82">
-        <v>86</v>
+        <v>245</v>
       </c>
       <c r="X82" t="s" s="82">
-        <v>45</v>
+        <v>245</v>
       </c>
       <c r="Y82" t="s" s="82">
-        <v>45</v>
+        <v>245</v>
       </c>
     </row>
     <row r="83">
@@ -8996,19 +8602,19 @@
         <v>107</v>
       </c>
       <c r="B83" t="s" s="83">
-        <v>694</v>
+        <v>690</v>
       </c>
       <c r="C83" t="s" s="83">
-        <v>695</v>
+        <v>691</v>
       </c>
       <c r="D83" t="s" s="83">
-        <v>696</v>
+        <v>692</v>
       </c>
       <c r="E83" t="s" s="83">
-        <v>696</v>
+        <v>692</v>
       </c>
       <c r="F83" t="s" s="83">
-        <v>683</v>
+        <v>617</v>
       </c>
       <c r="G83" t="s" s="83">
         <v>32</v>
@@ -9017,28 +8623,28 @@
         <v>33</v>
       </c>
       <c r="I83" t="s" s="83">
-        <v>121</v>
+        <v>693</v>
       </c>
       <c r="J83" t="s" s="83">
-        <v>122</v>
+        <v>694</v>
       </c>
       <c r="K83" t="s" s="83">
-        <v>697</v>
+        <v>695</v>
       </c>
       <c r="L83" t="s" s="83">
         <v>124</v>
       </c>
       <c r="M83" t="s" s="83">
-        <v>698</v>
+        <v>696</v>
       </c>
       <c r="N83" t="s" s="83">
-        <v>699</v>
+        <v>697</v>
       </c>
       <c r="O83" t="s" s="83">
-        <v>699</v>
+        <v>697</v>
       </c>
       <c r="P83" t="s" s="83">
-        <v>685</v>
+        <v>275</v>
       </c>
       <c r="Q83" t="s" s="83">
         <v>41</v>
@@ -9047,19 +8653,19 @@
         <v>41</v>
       </c>
       <c r="S83" t="s" s="83">
-        <v>58</v>
+        <v>264</v>
       </c>
       <c r="T83" t="s" s="83">
-        <v>59</v>
+        <v>265</v>
       </c>
       <c r="U83" t="s" s="83">
         <v>44</v>
       </c>
       <c r="V83" t="s" s="83">
-        <v>205</v>
+        <v>33</v>
       </c>
       <c r="W83" t="s" s="83">
-        <v>86</v>
+        <v>45</v>
       </c>
       <c r="X83" t="s" s="83">
         <v>45</v>
@@ -9073,61 +8679,61 @@
         <v>107</v>
       </c>
       <c r="B84" t="s" s="84">
+        <v>698</v>
+      </c>
+      <c r="C84" t="s" s="84">
+        <v>28</v>
+      </c>
+      <c r="D84" t="s" s="84">
+        <v>699</v>
+      </c>
+      <c r="E84" t="s" s="84">
         <v>700</v>
       </c>
-      <c r="C84" t="s" s="84">
-        <v>28</v>
-      </c>
-      <c r="D84" t="s" s="84">
+      <c r="F84" t="s" s="84">
+        <v>617</v>
+      </c>
+      <c r="G84" t="s" s="84">
+        <v>32</v>
+      </c>
+      <c r="H84" t="s" s="84">
+        <v>33</v>
+      </c>
+      <c r="I84" t="s" s="84">
+        <v>527</v>
+      </c>
+      <c r="J84" t="s" s="84">
+        <v>528</v>
+      </c>
+      <c r="K84" t="s" s="84">
         <v>701</v>
       </c>
-      <c r="E84" t="s" s="84">
+      <c r="L84" t="s" s="84">
+        <v>124</v>
+      </c>
+      <c r="M84" t="s" s="84">
         <v>702</v>
       </c>
-      <c r="F84" t="s" s="84">
-        <v>683</v>
-      </c>
-      <c r="G84" t="s" s="84">
-        <v>53</v>
-      </c>
-      <c r="H84" t="s" s="84">
-        <v>33</v>
-      </c>
-      <c r="I84" t="s" s="84">
-        <v>28</v>
-      </c>
-      <c r="J84" t="s" s="84">
-        <v>28</v>
-      </c>
-      <c r="K84" t="s" s="84">
+      <c r="N84" t="s" s="84">
         <v>703</v>
       </c>
-      <c r="L84" t="s" s="84">
-        <v>81</v>
-      </c>
-      <c r="M84" t="s" s="84">
-        <v>704</v>
-      </c>
-      <c r="N84" t="s" s="84">
-        <v>705</v>
-      </c>
       <c r="O84" t="s" s="84">
-        <v>705</v>
+        <v>703</v>
       </c>
       <c r="P84" t="s" s="84">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="Q84" t="s" s="84">
-        <v>28</v>
+        <v>41</v>
       </c>
       <c r="R84" t="s" s="84">
         <v>41</v>
       </c>
       <c r="S84" t="s" s="84">
-        <v>173</v>
+        <v>264</v>
       </c>
       <c r="T84" t="s" s="84">
-        <v>174</v>
+        <v>265</v>
       </c>
       <c r="U84" t="s" s="84">
         <v>44</v>
@@ -9136,13 +8742,13 @@
         <v>33</v>
       </c>
       <c r="W84" t="s" s="84">
-        <v>86</v>
+        <v>245</v>
       </c>
       <c r="X84" t="s" s="84">
-        <v>86</v>
+        <v>45</v>
       </c>
       <c r="Y84" t="s" s="84">
-        <v>86</v>
+        <v>45</v>
       </c>
     </row>
     <row r="85">
@@ -9150,49 +8756,49 @@
         <v>107</v>
       </c>
       <c r="B85" t="s" s="85">
+        <v>704</v>
+      </c>
+      <c r="C85" t="s" s="85">
+        <v>28</v>
+      </c>
+      <c r="D85" t="s" s="85">
+        <v>705</v>
+      </c>
+      <c r="E85" t="s" s="85">
         <v>706</v>
       </c>
-      <c r="C85" t="s" s="85">
+      <c r="F85" t="s" s="85">
+        <v>617</v>
+      </c>
+      <c r="G85" t="s" s="85">
+        <v>32</v>
+      </c>
+      <c r="H85" t="s" s="85">
+        <v>33</v>
+      </c>
+      <c r="I85" t="s" s="85">
         <v>707</v>
       </c>
-      <c r="D85" t="s" s="85">
+      <c r="J85" t="s" s="85">
         <v>708</v>
       </c>
-      <c r="E85" t="s" s="85">
-        <v>708</v>
-      </c>
-      <c r="F85" t="s" s="85">
-        <v>289</v>
-      </c>
-      <c r="G85" t="s" s="85">
-        <v>528</v>
-      </c>
-      <c r="H85" t="s" s="85">
-        <v>304</v>
-      </c>
-      <c r="I85" t="s" s="85">
+      <c r="K85" t="s" s="85">
         <v>709</v>
       </c>
-      <c r="J85" t="s" s="85">
+      <c r="L85" t="s" s="85">
+        <v>92</v>
+      </c>
+      <c r="M85" t="s" s="85">
+        <v>307</v>
+      </c>
+      <c r="N85" t="s" s="85">
         <v>710</v>
       </c>
-      <c r="K85" t="s" s="85">
-        <v>711</v>
-      </c>
-      <c r="L85" t="s" s="85">
-        <v>124</v>
-      </c>
-      <c r="M85" t="s" s="85">
-        <v>712</v>
-      </c>
-      <c r="N85" t="s" s="85">
-        <v>713</v>
-      </c>
       <c r="O85" t="s" s="85">
-        <v>713</v>
+        <v>710</v>
       </c>
       <c r="P85" t="s" s="85">
-        <v>685</v>
+        <v>275</v>
       </c>
       <c r="Q85" t="s" s="85">
         <v>41</v>
@@ -9201,19 +8807,19 @@
         <v>41</v>
       </c>
       <c r="S85" t="s" s="85">
-        <v>252</v>
+        <v>83</v>
       </c>
       <c r="T85" t="s" s="85">
-        <v>253</v>
+        <v>84</v>
       </c>
       <c r="U85" t="s" s="85">
         <v>44</v>
       </c>
       <c r="V85" t="s" s="85">
-        <v>192</v>
+        <v>33</v>
       </c>
       <c r="W85" t="s" s="85">
-        <v>86</v>
+        <v>45</v>
       </c>
       <c r="X85" t="s" s="85">
         <v>45</v>
@@ -9227,49 +8833,49 @@
         <v>107</v>
       </c>
       <c r="B86" t="s" s="86">
+        <v>711</v>
+      </c>
+      <c r="C86" t="s" s="86">
+        <v>28</v>
+      </c>
+      <c r="D86" t="s" s="86">
+        <v>712</v>
+      </c>
+      <c r="E86" t="s" s="86">
+        <v>713</v>
+      </c>
+      <c r="F86" t="s" s="86">
+        <v>617</v>
+      </c>
+      <c r="G86" t="s" s="86">
+        <v>32</v>
+      </c>
+      <c r="H86" t="s" s="86">
+        <v>33</v>
+      </c>
+      <c r="I86" t="s" s="86">
+        <v>233</v>
+      </c>
+      <c r="J86" t="s" s="86">
+        <v>234</v>
+      </c>
+      <c r="K86" t="s" s="86">
         <v>714</v>
       </c>
-      <c r="C86" t="s" s="86">
+      <c r="L86" t="s" s="86">
+        <v>92</v>
+      </c>
+      <c r="M86" t="s" s="86">
+        <v>307</v>
+      </c>
+      <c r="N86" t="s" s="86">
         <v>715</v>
       </c>
-      <c r="D86" t="s" s="86">
-        <v>716</v>
-      </c>
-      <c r="E86" t="s" s="86">
-        <v>716</v>
-      </c>
-      <c r="F86" t="s" s="86">
-        <v>289</v>
-      </c>
-      <c r="G86" t="s" s="86">
-        <v>528</v>
-      </c>
-      <c r="H86" t="s" s="86">
-        <v>304</v>
-      </c>
-      <c r="I86" t="s" s="86">
-        <v>717</v>
-      </c>
-      <c r="J86" t="s" s="86">
-        <v>718</v>
-      </c>
-      <c r="K86" t="s" s="86">
-        <v>719</v>
-      </c>
-      <c r="L86" t="s" s="86">
-        <v>124</v>
-      </c>
-      <c r="M86" t="s" s="86">
-        <v>720</v>
-      </c>
-      <c r="N86" t="s" s="86">
-        <v>721</v>
-      </c>
       <c r="O86" t="s" s="86">
-        <v>721</v>
+        <v>715</v>
       </c>
       <c r="P86" t="s" s="86">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="Q86" t="s" s="86">
         <v>41</v>
@@ -9278,25 +8884,25 @@
         <v>41</v>
       </c>
       <c r="S86" t="s" s="86">
-        <v>252</v>
+        <v>127</v>
       </c>
       <c r="T86" t="s" s="86">
-        <v>253</v>
+        <v>128</v>
       </c>
       <c r="U86" t="s" s="86">
         <v>44</v>
       </c>
       <c r="V86" t="s" s="86">
-        <v>304</v>
+        <v>33</v>
       </c>
       <c r="W86" t="s" s="86">
-        <v>86</v>
+        <v>45</v>
       </c>
       <c r="X86" t="s" s="86">
-        <v>86</v>
+        <v>45</v>
       </c>
       <c r="Y86" t="s" s="86">
-        <v>86</v>
+        <v>45</v>
       </c>
     </row>
     <row r="87">
@@ -9304,19 +8910,19 @@
         <v>107</v>
       </c>
       <c r="B87" t="s" s="87">
-        <v>722</v>
+        <v>716</v>
       </c>
       <c r="C87" t="s" s="87">
-        <v>723</v>
+        <v>28</v>
       </c>
       <c r="D87" t="s" s="87">
-        <v>724</v>
+        <v>717</v>
       </c>
       <c r="E87" t="s" s="87">
-        <v>724</v>
+        <v>718</v>
       </c>
       <c r="F87" t="s" s="87">
-        <v>683</v>
+        <v>617</v>
       </c>
       <c r="G87" t="s" s="87">
         <v>32</v>
@@ -9325,28 +8931,28 @@
         <v>33</v>
       </c>
       <c r="I87" t="s" s="87">
-        <v>442</v>
+        <v>719</v>
       </c>
       <c r="J87" t="s" s="87">
-        <v>443</v>
+        <v>720</v>
       </c>
       <c r="K87" t="s" s="87">
-        <v>725</v>
+        <v>721</v>
       </c>
       <c r="L87" t="s" s="87">
-        <v>92</v>
+        <v>124</v>
       </c>
       <c r="M87" t="s" s="87">
-        <v>726</v>
+        <v>722</v>
       </c>
       <c r="N87" t="s" s="87">
-        <v>727</v>
+        <v>723</v>
       </c>
       <c r="O87" t="s" s="87">
-        <v>727</v>
+        <v>723</v>
       </c>
       <c r="P87" t="s" s="87">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="Q87" t="s" s="87">
         <v>41</v>
@@ -9355,19 +8961,19 @@
         <v>41</v>
       </c>
       <c r="S87" t="s" s="87">
-        <v>58</v>
+        <v>264</v>
       </c>
       <c r="T87" t="s" s="87">
-        <v>59</v>
+        <v>265</v>
       </c>
       <c r="U87" t="s" s="87">
-        <v>728</v>
+        <v>44</v>
       </c>
       <c r="V87" t="s" s="87">
-        <v>158</v>
+        <v>33</v>
       </c>
       <c r="W87" t="s" s="87">
-        <v>86</v>
+        <v>45</v>
       </c>
       <c r="X87" t="s" s="87">
         <v>45</v>
@@ -9381,49 +8987,49 @@
         <v>107</v>
       </c>
       <c r="B88" t="s" s="88">
+        <v>724</v>
+      </c>
+      <c r="C88" t="s" s="88">
+        <v>28</v>
+      </c>
+      <c r="D88" t="s" s="88">
+        <v>725</v>
+      </c>
+      <c r="E88" t="s" s="88">
+        <v>726</v>
+      </c>
+      <c r="F88" t="s" s="88">
+        <v>617</v>
+      </c>
+      <c r="G88" t="s" s="88">
+        <v>53</v>
+      </c>
+      <c r="H88" t="s" s="88">
+        <v>33</v>
+      </c>
+      <c r="I88" t="s" s="88">
+        <v>727</v>
+      </c>
+      <c r="J88" t="s" s="88">
+        <v>728</v>
+      </c>
+      <c r="K88" t="s" s="88">
+        <v>689</v>
+      </c>
+      <c r="L88" t="s" s="88">
+        <v>604</v>
+      </c>
+      <c r="M88" t="s" s="88">
         <v>729</v>
       </c>
-      <c r="C88" t="s" s="88">
-        <v>730</v>
-      </c>
-      <c r="D88" t="s" s="88">
-        <v>731</v>
-      </c>
-      <c r="E88" t="s" s="88">
-        <v>731</v>
-      </c>
-      <c r="F88" t="s" s="88">
-        <v>683</v>
-      </c>
-      <c r="G88" t="s" s="88">
-        <v>223</v>
-      </c>
-      <c r="H88" t="s" s="88">
-        <v>33</v>
-      </c>
-      <c r="I88" t="s" s="88">
-        <v>732</v>
-      </c>
-      <c r="J88" t="s" s="88">
-        <v>733</v>
-      </c>
-      <c r="K88" t="s" s="88">
-        <v>734</v>
-      </c>
-      <c r="L88" t="s" s="88">
-        <v>92</v>
-      </c>
-      <c r="M88" t="s" s="88">
-        <v>735</v>
-      </c>
       <c r="N88" t="s" s="88">
-        <v>736</v>
+        <v>725</v>
       </c>
       <c r="O88" t="s" s="88">
-        <v>736</v>
+        <v>725</v>
       </c>
       <c r="P88" t="s" s="88">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="Q88" t="s" s="88">
         <v>41</v>
@@ -9432,19 +9038,19 @@
         <v>41</v>
       </c>
       <c r="S88" t="s" s="88">
-        <v>350</v>
+        <v>173</v>
       </c>
       <c r="T88" t="s" s="88">
-        <v>351</v>
+        <v>174</v>
       </c>
       <c r="U88" t="s" s="88">
         <v>44</v>
       </c>
       <c r="V88" t="s" s="88">
-        <v>158</v>
+        <v>33</v>
       </c>
       <c r="W88" t="s" s="88">
-        <v>86</v>
+        <v>45</v>
       </c>
       <c r="X88" t="s" s="88">
         <v>45</v>
@@ -9458,49 +9064,49 @@
         <v>107</v>
       </c>
       <c r="B89" t="s" s="89">
-        <v>737</v>
+        <v>730</v>
       </c>
       <c r="C89" t="s" s="89">
-        <v>738</v>
+        <v>28</v>
       </c>
       <c r="D89" t="s" s="89">
-        <v>739</v>
+        <v>731</v>
       </c>
       <c r="E89" t="s" s="89">
-        <v>739</v>
+        <v>731</v>
       </c>
       <c r="F89" t="s" s="89">
-        <v>683</v>
+        <v>617</v>
       </c>
       <c r="G89" t="s" s="89">
-        <v>258</v>
+        <v>53</v>
       </c>
       <c r="H89" t="s" s="89">
         <v>33</v>
       </c>
       <c r="I89" t="s" s="89">
-        <v>740</v>
+        <v>493</v>
       </c>
       <c r="J89" t="s" s="89">
-        <v>741</v>
+        <v>494</v>
       </c>
       <c r="K89" t="s" s="89">
-        <v>742</v>
+        <v>732</v>
       </c>
       <c r="L89" t="s" s="89">
-        <v>92</v>
+        <v>28</v>
       </c>
       <c r="M89" t="s" s="89">
-        <v>743</v>
+        <v>28</v>
       </c>
       <c r="N89" t="s" s="89">
-        <v>744</v>
+        <v>733</v>
       </c>
       <c r="O89" t="s" s="89">
-        <v>744</v>
+        <v>733</v>
       </c>
       <c r="P89" t="s" s="89">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="Q89" t="s" s="89">
         <v>41</v>
@@ -9509,1179 +9115,24 @@
         <v>41</v>
       </c>
       <c r="S89" t="s" s="89">
-        <v>350</v>
+        <v>58</v>
       </c>
       <c r="T89" t="s" s="89">
-        <v>351</v>
+        <v>59</v>
       </c>
       <c r="U89" t="s" s="89">
         <v>44</v>
       </c>
       <c r="V89" t="s" s="89">
-        <v>158</v>
+        <v>33</v>
       </c>
       <c r="W89" t="s" s="89">
-        <v>86</v>
+        <v>45</v>
       </c>
       <c r="X89" t="s" s="89">
         <v>45</v>
       </c>
       <c r="Y89" t="s" s="89">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90" t="s" s="90">
-        <v>107</v>
-      </c>
-      <c r="B90" t="s" s="90">
-        <v>745</v>
-      </c>
-      <c r="C90" t="s" s="90">
-        <v>746</v>
-      </c>
-      <c r="D90" t="s" s="90">
-        <v>747</v>
-      </c>
-      <c r="E90" t="s" s="90">
-        <v>747</v>
-      </c>
-      <c r="F90" t="s" s="90">
-        <v>683</v>
-      </c>
-      <c r="G90" t="s" s="90">
-        <v>258</v>
-      </c>
-      <c r="H90" t="s" s="90">
-        <v>33</v>
-      </c>
-      <c r="I90" t="s" s="90">
-        <v>748</v>
-      </c>
-      <c r="J90" t="s" s="90">
-        <v>749</v>
-      </c>
-      <c r="K90" t="s" s="90">
-        <v>750</v>
-      </c>
-      <c r="L90" t="s" s="90">
-        <v>92</v>
-      </c>
-      <c r="M90" t="s" s="90">
-        <v>751</v>
-      </c>
-      <c r="N90" t="s" s="90">
-        <v>752</v>
-      </c>
-      <c r="O90" t="s" s="90">
-        <v>752</v>
-      </c>
-      <c r="P90" t="s" s="90">
-        <v>273</v>
-      </c>
-      <c r="Q90" t="s" s="90">
-        <v>41</v>
-      </c>
-      <c r="R90" t="s" s="90">
-        <v>41</v>
-      </c>
-      <c r="S90" t="s" s="90">
-        <v>350</v>
-      </c>
-      <c r="T90" t="s" s="90">
-        <v>351</v>
-      </c>
-      <c r="U90" t="s" s="90">
-        <v>44</v>
-      </c>
-      <c r="V90" t="s" s="90">
-        <v>158</v>
-      </c>
-      <c r="W90" t="s" s="90">
-        <v>86</v>
-      </c>
-      <c r="X90" t="s" s="90">
-        <v>45</v>
-      </c>
-      <c r="Y90" t="s" s="90">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="91">
-      <c r="A91" t="s" s="91">
-        <v>107</v>
-      </c>
-      <c r="B91" t="s" s="91">
-        <v>753</v>
-      </c>
-      <c r="C91" t="s" s="91">
-        <v>754</v>
-      </c>
-      <c r="D91" t="s" s="91">
-        <v>755</v>
-      </c>
-      <c r="E91" t="s" s="91">
-        <v>755</v>
-      </c>
-      <c r="F91" t="s" s="91">
-        <v>683</v>
-      </c>
-      <c r="G91" t="s" s="91">
-        <v>258</v>
-      </c>
-      <c r="H91" t="s" s="91">
-        <v>33</v>
-      </c>
-      <c r="I91" t="s" s="91">
-        <v>756</v>
-      </c>
-      <c r="J91" t="s" s="91">
-        <v>757</v>
-      </c>
-      <c r="K91" t="s" s="91">
-        <v>758</v>
-      </c>
-      <c r="L91" t="s" s="91">
-        <v>92</v>
-      </c>
-      <c r="M91" t="s" s="91">
-        <v>759</v>
-      </c>
-      <c r="N91" t="s" s="91">
-        <v>760</v>
-      </c>
-      <c r="O91" t="s" s="91">
-        <v>760</v>
-      </c>
-      <c r="P91" t="s" s="91">
-        <v>273</v>
-      </c>
-      <c r="Q91" t="s" s="91">
-        <v>41</v>
-      </c>
-      <c r="R91" t="s" s="91">
-        <v>41</v>
-      </c>
-      <c r="S91" t="s" s="91">
-        <v>350</v>
-      </c>
-      <c r="T91" t="s" s="91">
-        <v>351</v>
-      </c>
-      <c r="U91" t="s" s="91">
-        <v>44</v>
-      </c>
-      <c r="V91" t="s" s="91">
-        <v>158</v>
-      </c>
-      <c r="W91" t="s" s="91">
-        <v>86</v>
-      </c>
-      <c r="X91" t="s" s="91">
-        <v>45</v>
-      </c>
-      <c r="Y91" t="s" s="91">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="92">
-      <c r="A92" t="s" s="92">
-        <v>107</v>
-      </c>
-      <c r="B92" t="s" s="92">
-        <v>761</v>
-      </c>
-      <c r="C92" t="s" s="92">
-        <v>762</v>
-      </c>
-      <c r="D92" t="s" s="92">
-        <v>763</v>
-      </c>
-      <c r="E92" t="s" s="92">
-        <v>763</v>
-      </c>
-      <c r="F92" t="s" s="92">
-        <v>683</v>
-      </c>
-      <c r="G92" t="s" s="92">
-        <v>223</v>
-      </c>
-      <c r="H92" t="s" s="92">
-        <v>33</v>
-      </c>
-      <c r="I92" t="s" s="92">
-        <v>764</v>
-      </c>
-      <c r="J92" t="s" s="92">
-        <v>765</v>
-      </c>
-      <c r="K92" t="s" s="92">
-        <v>766</v>
-      </c>
-      <c r="L92" t="s" s="92">
-        <v>69</v>
-      </c>
-      <c r="M92" t="s" s="92">
-        <v>767</v>
-      </c>
-      <c r="N92" t="s" s="92">
-        <v>768</v>
-      </c>
-      <c r="O92" t="s" s="92">
-        <v>768</v>
-      </c>
-      <c r="P92" t="s" s="92">
-        <v>273</v>
-      </c>
-      <c r="Q92" t="s" s="92">
-        <v>28</v>
-      </c>
-      <c r="R92" t="s" s="92">
-        <v>41</v>
-      </c>
-      <c r="S92" t="s" s="92">
-        <v>173</v>
-      </c>
-      <c r="T92" t="s" s="92">
-        <v>174</v>
-      </c>
-      <c r="U92" t="s" s="92">
-        <v>44</v>
-      </c>
-      <c r="V92" t="s" s="92">
-        <v>158</v>
-      </c>
-      <c r="W92" t="s" s="92">
-        <v>86</v>
-      </c>
-      <c r="X92" t="s" s="92">
-        <v>45</v>
-      </c>
-      <c r="Y92" t="s" s="92">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="93">
-      <c r="A93" t="s" s="93">
-        <v>107</v>
-      </c>
-      <c r="B93" t="s" s="93">
-        <v>769</v>
-      </c>
-      <c r="C93" t="s" s="93">
-        <v>770</v>
-      </c>
-      <c r="D93" t="s" s="93">
-        <v>771</v>
-      </c>
-      <c r="E93" t="s" s="93">
-        <v>772</v>
-      </c>
-      <c r="F93" t="s" s="93">
-        <v>773</v>
-      </c>
-      <c r="G93" t="s" s="93">
-        <v>223</v>
-      </c>
-      <c r="H93" t="s" s="93">
-        <v>33</v>
-      </c>
-      <c r="I93" t="s" s="93">
-        <v>774</v>
-      </c>
-      <c r="J93" t="s" s="93">
-        <v>775</v>
-      </c>
-      <c r="K93" t="s" s="93">
-        <v>776</v>
-      </c>
-      <c r="L93" t="s" s="93">
-        <v>69</v>
-      </c>
-      <c r="M93" t="s" s="93">
-        <v>584</v>
-      </c>
-      <c r="N93" t="s" s="93">
-        <v>777</v>
-      </c>
-      <c r="O93" t="s" s="93">
-        <v>777</v>
-      </c>
-      <c r="P93" t="s" s="93">
-        <v>273</v>
-      </c>
-      <c r="Q93" t="s" s="93">
-        <v>41</v>
-      </c>
-      <c r="R93" t="s" s="93">
-        <v>41</v>
-      </c>
-      <c r="S93" t="s" s="93">
-        <v>72</v>
-      </c>
-      <c r="T93" t="s" s="93">
-        <v>73</v>
-      </c>
-      <c r="U93" t="s" s="93">
-        <v>44</v>
-      </c>
-      <c r="V93" t="s" s="93">
-        <v>33</v>
-      </c>
-      <c r="W93" t="s" s="93">
-        <v>45</v>
-      </c>
-      <c r="X93" t="s" s="93">
-        <v>45</v>
-      </c>
-      <c r="Y93" t="s" s="93">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="94">
-      <c r="A94" t="s" s="94">
-        <v>107</v>
-      </c>
-      <c r="B94" t="s" s="94">
-        <v>778</v>
-      </c>
-      <c r="C94" t="s" s="94">
-        <v>779</v>
-      </c>
-      <c r="D94" t="s" s="94">
-        <v>780</v>
-      </c>
-      <c r="E94" t="s" s="94">
-        <v>780</v>
-      </c>
-      <c r="F94" t="s" s="94">
-        <v>773</v>
-      </c>
-      <c r="G94" t="s" s="94">
-        <v>258</v>
-      </c>
-      <c r="H94" t="s" s="94">
-        <v>33</v>
-      </c>
-      <c r="I94" t="s" s="94">
-        <v>781</v>
-      </c>
-      <c r="J94" t="s" s="94">
-        <v>782</v>
-      </c>
-      <c r="K94" t="s" s="94">
-        <v>783</v>
-      </c>
-      <c r="L94" t="s" s="94">
-        <v>629</v>
-      </c>
-      <c r="M94" t="s" s="94">
-        <v>45</v>
-      </c>
-      <c r="N94" t="s" s="94">
-        <v>784</v>
-      </c>
-      <c r="O94" t="s" s="94">
-        <v>784</v>
-      </c>
-      <c r="P94" t="s" s="94">
-        <v>273</v>
-      </c>
-      <c r="Q94" t="s" s="94">
-        <v>41</v>
-      </c>
-      <c r="R94" t="s" s="94">
-        <v>41</v>
-      </c>
-      <c r="S94" t="s" s="94">
-        <v>350</v>
-      </c>
-      <c r="T94" t="s" s="94">
-        <v>351</v>
-      </c>
-      <c r="U94" t="s" s="94">
-        <v>44</v>
-      </c>
-      <c r="V94" t="s" s="94">
-        <v>33</v>
-      </c>
-      <c r="W94" t="s" s="94">
-        <v>45</v>
-      </c>
-      <c r="X94" t="s" s="94">
-        <v>45</v>
-      </c>
-      <c r="Y94" t="s" s="94">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="95">
-      <c r="A95" t="s" s="95">
-        <v>107</v>
-      </c>
-      <c r="B95" t="s" s="95">
-        <v>785</v>
-      </c>
-      <c r="C95" t="s" s="95">
-        <v>786</v>
-      </c>
-      <c r="D95" t="s" s="95">
-        <v>787</v>
-      </c>
-      <c r="E95" t="s" s="95">
-        <v>787</v>
-      </c>
-      <c r="F95" t="s" s="95">
-        <v>773</v>
-      </c>
-      <c r="G95" t="s" s="95">
-        <v>258</v>
-      </c>
-      <c r="H95" t="s" s="95">
-        <v>33</v>
-      </c>
-      <c r="I95" t="s" s="95">
-        <v>788</v>
-      </c>
-      <c r="J95" t="s" s="95">
-        <v>789</v>
-      </c>
-      <c r="K95" t="s" s="95">
-        <v>790</v>
-      </c>
-      <c r="L95" t="s" s="95">
-        <v>92</v>
-      </c>
-      <c r="M95" t="s" s="95">
-        <v>791</v>
-      </c>
-      <c r="N95" t="s" s="95">
-        <v>792</v>
-      </c>
-      <c r="O95" t="s" s="95">
-        <v>792</v>
-      </c>
-      <c r="P95" t="s" s="95">
-        <v>685</v>
-      </c>
-      <c r="Q95" t="s" s="95">
-        <v>41</v>
-      </c>
-      <c r="R95" t="s" s="95">
-        <v>41</v>
-      </c>
-      <c r="S95" t="s" s="95">
-        <v>350</v>
-      </c>
-      <c r="T95" t="s" s="95">
-        <v>351</v>
-      </c>
-      <c r="U95" t="s" s="95">
-        <v>44</v>
-      </c>
-      <c r="V95" t="s" s="95">
-        <v>158</v>
-      </c>
-      <c r="W95" t="s" s="95">
-        <v>45</v>
-      </c>
-      <c r="X95" t="s" s="95">
-        <v>45</v>
-      </c>
-      <c r="Y95" t="s" s="95">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="96">
-      <c r="A96" t="s" s="96">
-        <v>107</v>
-      </c>
-      <c r="B96" t="s" s="96">
-        <v>793</v>
-      </c>
-      <c r="C96" t="s" s="96">
-        <v>794</v>
-      </c>
-      <c r="D96" t="s" s="96">
-        <v>795</v>
-      </c>
-      <c r="E96" t="s" s="96">
-        <v>795</v>
-      </c>
-      <c r="F96" t="s" s="96">
-        <v>773</v>
-      </c>
-      <c r="G96" t="s" s="96">
-        <v>32</v>
-      </c>
-      <c r="H96" t="s" s="96">
-        <v>33</v>
-      </c>
-      <c r="I96" t="s" s="96">
-        <v>796</v>
-      </c>
-      <c r="J96" t="s" s="96">
-        <v>797</v>
-      </c>
-      <c r="K96" t="s" s="96">
-        <v>798</v>
-      </c>
-      <c r="L96" t="s" s="96">
-        <v>92</v>
-      </c>
-      <c r="M96" t="s" s="96">
-        <v>799</v>
-      </c>
-      <c r="N96" t="s" s="96">
-        <v>800</v>
-      </c>
-      <c r="O96" t="s" s="96">
-        <v>800</v>
-      </c>
-      <c r="P96" t="s" s="96">
-        <v>685</v>
-      </c>
-      <c r="Q96" t="s" s="96">
-        <v>41</v>
-      </c>
-      <c r="R96" t="s" s="96">
-        <v>41</v>
-      </c>
-      <c r="S96" t="s" s="96">
-        <v>350</v>
-      </c>
-      <c r="T96" t="s" s="96">
-        <v>351</v>
-      </c>
-      <c r="U96" t="s" s="96">
-        <v>44</v>
-      </c>
-      <c r="V96" t="s" s="96">
-        <v>158</v>
-      </c>
-      <c r="W96" t="s" s="96">
-        <v>45</v>
-      </c>
-      <c r="X96" t="s" s="96">
-        <v>45</v>
-      </c>
-      <c r="Y96" t="s" s="96">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="97">
-      <c r="A97" t="s" s="97">
-        <v>107</v>
-      </c>
-      <c r="B97" t="s" s="97">
-        <v>801</v>
-      </c>
-      <c r="C97" t="s" s="97">
-        <v>28</v>
-      </c>
-      <c r="D97" t="s" s="97">
-        <v>802</v>
-      </c>
-      <c r="E97" t="s" s="97">
-        <v>803</v>
-      </c>
-      <c r="F97" t="s" s="97">
-        <v>773</v>
-      </c>
-      <c r="G97" t="s" s="97">
-        <v>32</v>
-      </c>
-      <c r="H97" t="s" s="97">
-        <v>33</v>
-      </c>
-      <c r="I97" t="s" s="97">
-        <v>804</v>
-      </c>
-      <c r="J97" t="s" s="97">
-        <v>805</v>
-      </c>
-      <c r="K97" t="s" s="97">
-        <v>806</v>
-      </c>
-      <c r="L97" t="s" s="97">
-        <v>92</v>
-      </c>
-      <c r="M97" t="s" s="97">
-        <v>807</v>
-      </c>
-      <c r="N97" t="s" s="97">
-        <v>808</v>
-      </c>
-      <c r="O97" t="s" s="97">
-        <v>808</v>
-      </c>
-      <c r="P97" t="s" s="97">
-        <v>273</v>
-      </c>
-      <c r="Q97" t="s" s="97">
-        <v>41</v>
-      </c>
-      <c r="R97" t="s" s="97">
-        <v>41</v>
-      </c>
-      <c r="S97" t="s" s="97">
-        <v>350</v>
-      </c>
-      <c r="T97" t="s" s="97">
-        <v>351</v>
-      </c>
-      <c r="U97" t="s" s="97">
-        <v>44</v>
-      </c>
-      <c r="V97" t="s" s="97">
-        <v>33</v>
-      </c>
-      <c r="W97" t="s" s="97">
-        <v>45</v>
-      </c>
-      <c r="X97" t="s" s="97">
-        <v>45</v>
-      </c>
-      <c r="Y97" t="s" s="97">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="98">
-      <c r="A98" t="s" s="98">
-        <v>107</v>
-      </c>
-      <c r="B98" t="s" s="98">
-        <v>809</v>
-      </c>
-      <c r="C98" t="s" s="98">
-        <v>28</v>
-      </c>
-      <c r="D98" t="s" s="98">
-        <v>810</v>
-      </c>
-      <c r="E98" t="s" s="98">
-        <v>811</v>
-      </c>
-      <c r="F98" t="s" s="98">
-        <v>773</v>
-      </c>
-      <c r="G98" t="s" s="98">
-        <v>32</v>
-      </c>
-      <c r="H98" t="s" s="98">
-        <v>33</v>
-      </c>
-      <c r="I98" t="s" s="98">
-        <v>812</v>
-      </c>
-      <c r="J98" t="s" s="98">
-        <v>813</v>
-      </c>
-      <c r="K98" t="s" s="98">
-        <v>814</v>
-      </c>
-      <c r="L98" t="s" s="98">
-        <v>92</v>
-      </c>
-      <c r="M98" t="s" s="98">
-        <v>815</v>
-      </c>
-      <c r="N98" t="s" s="98">
-        <v>816</v>
-      </c>
-      <c r="O98" t="s" s="98">
-        <v>816</v>
-      </c>
-      <c r="P98" t="s" s="98">
-        <v>273</v>
-      </c>
-      <c r="Q98" t="s" s="98">
-        <v>41</v>
-      </c>
-      <c r="R98" t="s" s="98">
-        <v>41</v>
-      </c>
-      <c r="S98" t="s" s="98">
-        <v>350</v>
-      </c>
-      <c r="T98" t="s" s="98">
-        <v>351</v>
-      </c>
-      <c r="U98" t="s" s="98">
-        <v>44</v>
-      </c>
-      <c r="V98" t="s" s="98">
-        <v>33</v>
-      </c>
-      <c r="W98" t="s" s="98">
-        <v>45</v>
-      </c>
-      <c r="X98" t="s" s="98">
-        <v>45</v>
-      </c>
-      <c r="Y98" t="s" s="98">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="99">
-      <c r="A99" t="s" s="99">
-        <v>107</v>
-      </c>
-      <c r="B99" t="s" s="99">
-        <v>817</v>
-      </c>
-      <c r="C99" t="s" s="99">
-        <v>28</v>
-      </c>
-      <c r="D99" t="s" s="99">
-        <v>818</v>
-      </c>
-      <c r="E99" t="s" s="99">
-        <v>819</v>
-      </c>
-      <c r="F99" t="s" s="99">
-        <v>773</v>
-      </c>
-      <c r="G99" t="s" s="99">
-        <v>32</v>
-      </c>
-      <c r="H99" t="s" s="99">
-        <v>33</v>
-      </c>
-      <c r="I99" t="s" s="99">
-        <v>820</v>
-      </c>
-      <c r="J99" t="s" s="99">
-        <v>821</v>
-      </c>
-      <c r="K99" t="s" s="99">
-        <v>822</v>
-      </c>
-      <c r="L99" t="s" s="99">
-        <v>92</v>
-      </c>
-      <c r="M99" t="s" s="99">
-        <v>823</v>
-      </c>
-      <c r="N99" t="s" s="99">
-        <v>824</v>
-      </c>
-      <c r="O99" t="s" s="99">
-        <v>824</v>
-      </c>
-      <c r="P99" t="s" s="99">
-        <v>273</v>
-      </c>
-      <c r="Q99" t="s" s="99">
-        <v>41</v>
-      </c>
-      <c r="R99" t="s" s="99">
-        <v>41</v>
-      </c>
-      <c r="S99" t="s" s="99">
-        <v>350</v>
-      </c>
-      <c r="T99" t="s" s="99">
-        <v>351</v>
-      </c>
-      <c r="U99" t="s" s="99">
-        <v>44</v>
-      </c>
-      <c r="V99" t="s" s="99">
-        <v>33</v>
-      </c>
-      <c r="W99" t="s" s="99">
-        <v>45</v>
-      </c>
-      <c r="X99" t="s" s="99">
-        <v>45</v>
-      </c>
-      <c r="Y99" t="s" s="99">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="100">
-      <c r="A100" t="s" s="100">
-        <v>107</v>
-      </c>
-      <c r="B100" t="s" s="100">
-        <v>825</v>
-      </c>
-      <c r="C100" t="s" s="100">
-        <v>826</v>
-      </c>
-      <c r="D100" t="s" s="100">
-        <v>827</v>
-      </c>
-      <c r="E100" t="s" s="100">
-        <v>827</v>
-      </c>
-      <c r="F100" t="s" s="100">
-        <v>773</v>
-      </c>
-      <c r="G100" t="s" s="100">
-        <v>32</v>
-      </c>
-      <c r="H100" t="s" s="100">
-        <v>33</v>
-      </c>
-      <c r="I100" t="s" s="100">
-        <v>828</v>
-      </c>
-      <c r="J100" t="s" s="100">
-        <v>829</v>
-      </c>
-      <c r="K100" t="s" s="100">
-        <v>830</v>
-      </c>
-      <c r="L100" t="s" s="100">
-        <v>124</v>
-      </c>
-      <c r="M100" t="s" s="100">
-        <v>831</v>
-      </c>
-      <c r="N100" t="s" s="100">
-        <v>832</v>
-      </c>
-      <c r="O100" t="s" s="100">
-        <v>832</v>
-      </c>
-      <c r="P100" t="s" s="100">
-        <v>685</v>
-      </c>
-      <c r="Q100" t="s" s="100">
-        <v>41</v>
-      </c>
-      <c r="R100" t="s" s="100">
-        <v>41</v>
-      </c>
-      <c r="S100" t="s" s="100">
-        <v>252</v>
-      </c>
-      <c r="T100" t="s" s="100">
-        <v>253</v>
-      </c>
-      <c r="U100" t="s" s="100">
-        <v>44</v>
-      </c>
-      <c r="V100" t="s" s="100">
-        <v>158</v>
-      </c>
-      <c r="W100" t="s" s="100">
-        <v>45</v>
-      </c>
-      <c r="X100" t="s" s="100">
-        <v>45</v>
-      </c>
-      <c r="Y100" t="s" s="100">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101" t="s" s="101">
-        <v>107</v>
-      </c>
-      <c r="B101" t="s" s="101">
-        <v>833</v>
-      </c>
-      <c r="C101" t="s" s="101">
-        <v>28</v>
-      </c>
-      <c r="D101" t="s" s="101">
-        <v>834</v>
-      </c>
-      <c r="E101" t="s" s="101">
-        <v>835</v>
-      </c>
-      <c r="F101" t="s" s="101">
-        <v>773</v>
-      </c>
-      <c r="G101" t="s" s="101">
-        <v>32</v>
-      </c>
-      <c r="H101" t="s" s="101">
-        <v>33</v>
-      </c>
-      <c r="I101" t="s" s="101">
-        <v>836</v>
-      </c>
-      <c r="J101" t="s" s="101">
-        <v>837</v>
-      </c>
-      <c r="K101" t="s" s="101">
-        <v>838</v>
-      </c>
-      <c r="L101" t="s" s="101">
-        <v>92</v>
-      </c>
-      <c r="M101" t="s" s="101">
-        <v>839</v>
-      </c>
-      <c r="N101" t="s" s="101">
-        <v>840</v>
-      </c>
-      <c r="O101" t="s" s="101">
-        <v>840</v>
-      </c>
-      <c r="P101" t="s" s="101">
-        <v>273</v>
-      </c>
-      <c r="Q101" t="s" s="101">
-        <v>41</v>
-      </c>
-      <c r="R101" t="s" s="101">
-        <v>41</v>
-      </c>
-      <c r="S101" t="s" s="101">
-        <v>350</v>
-      </c>
-      <c r="T101" t="s" s="101">
-        <v>351</v>
-      </c>
-      <c r="U101" t="s" s="101">
-        <v>44</v>
-      </c>
-      <c r="V101" t="s" s="101">
-        <v>33</v>
-      </c>
-      <c r="W101" t="s" s="101">
-        <v>45</v>
-      </c>
-      <c r="X101" t="s" s="101">
-        <v>45</v>
-      </c>
-      <c r="Y101" t="s" s="101">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="102">
-      <c r="A102" t="s" s="102">
-        <v>107</v>
-      </c>
-      <c r="B102" t="s" s="102">
-        <v>841</v>
-      </c>
-      <c r="C102" t="s" s="102">
-        <v>28</v>
-      </c>
-      <c r="D102" t="s" s="102">
-        <v>842</v>
-      </c>
-      <c r="E102" t="s" s="102">
-        <v>843</v>
-      </c>
-      <c r="F102" t="s" s="102">
-        <v>773</v>
-      </c>
-      <c r="G102" t="s" s="102">
-        <v>53</v>
-      </c>
-      <c r="H102" t="s" s="102">
-        <v>33</v>
-      </c>
-      <c r="I102" t="s" s="102">
-        <v>844</v>
-      </c>
-      <c r="J102" t="s" s="102">
-        <v>845</v>
-      </c>
-      <c r="K102" t="s" s="102">
-        <v>846</v>
-      </c>
-      <c r="L102" t="s" s="102">
-        <v>629</v>
-      </c>
-      <c r="M102" t="s" s="102">
-        <v>847</v>
-      </c>
-      <c r="N102" t="s" s="102">
-        <v>848</v>
-      </c>
-      <c r="O102" t="s" s="102">
-        <v>848</v>
-      </c>
-      <c r="P102" t="s" s="102">
-        <v>685</v>
-      </c>
-      <c r="Q102" t="s" s="102">
-        <v>41</v>
-      </c>
-      <c r="R102" t="s" s="102">
-        <v>41</v>
-      </c>
-      <c r="S102" t="s" s="102">
-        <v>295</v>
-      </c>
-      <c r="T102" t="s" s="102">
-        <v>296</v>
-      </c>
-      <c r="U102" t="s" s="102">
-        <v>44</v>
-      </c>
-      <c r="V102" t="s" s="102">
-        <v>158</v>
-      </c>
-      <c r="W102" t="s" s="102">
-        <v>45</v>
-      </c>
-      <c r="X102" t="s" s="102">
-        <v>45</v>
-      </c>
-      <c r="Y102" t="s" s="102">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="103">
-      <c r="A103" t="s" s="103">
-        <v>107</v>
-      </c>
-      <c r="B103" t="s" s="103">
-        <v>849</v>
-      </c>
-      <c r="C103" t="s" s="103">
-        <v>28</v>
-      </c>
-      <c r="D103" t="s" s="103">
-        <v>850</v>
-      </c>
-      <c r="E103" t="s" s="103">
-        <v>851</v>
-      </c>
-      <c r="F103" t="s" s="103">
-        <v>773</v>
-      </c>
-      <c r="G103" t="s" s="103">
-        <v>53</v>
-      </c>
-      <c r="H103" t="s" s="103">
-        <v>33</v>
-      </c>
-      <c r="I103" t="s" s="103">
-        <v>134</v>
-      </c>
-      <c r="J103" t="s" s="103">
-        <v>135</v>
-      </c>
-      <c r="K103" t="s" s="103">
-        <v>852</v>
-      </c>
-      <c r="L103" t="s" s="103">
-        <v>28</v>
-      </c>
-      <c r="M103" t="s" s="103">
-        <v>28</v>
-      </c>
-      <c r="N103" t="s" s="103">
-        <v>850</v>
-      </c>
-      <c r="O103" t="s" s="103">
-        <v>850</v>
-      </c>
-      <c r="P103" t="s" s="103">
-        <v>273</v>
-      </c>
-      <c r="Q103" t="s" s="103">
-        <v>41</v>
-      </c>
-      <c r="R103" t="s" s="103">
-        <v>41</v>
-      </c>
-      <c r="S103" t="s" s="103">
-        <v>173</v>
-      </c>
-      <c r="T103" t="s" s="103">
-        <v>174</v>
-      </c>
-      <c r="U103" t="s" s="103">
-        <v>44</v>
-      </c>
-      <c r="V103" t="s" s="103">
-        <v>33</v>
-      </c>
-      <c r="W103" t="s" s="103">
-        <v>45</v>
-      </c>
-      <c r="X103" t="s" s="103">
-        <v>45</v>
-      </c>
-      <c r="Y103" t="s" s="103">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="104">
-      <c r="A104" t="s" s="104">
-        <v>107</v>
-      </c>
-      <c r="B104" t="s" s="104">
-        <v>853</v>
-      </c>
-      <c r="C104" t="s" s="104">
-        <v>28</v>
-      </c>
-      <c r="D104" t="s" s="104">
-        <v>854</v>
-      </c>
-      <c r="E104" t="s" s="104">
-        <v>854</v>
-      </c>
-      <c r="F104" t="s" s="104">
-        <v>773</v>
-      </c>
-      <c r="G104" t="s" s="104">
-        <v>53</v>
-      </c>
-      <c r="H104" t="s" s="104">
-        <v>33</v>
-      </c>
-      <c r="I104" t="s" s="104">
-        <v>134</v>
-      </c>
-      <c r="J104" t="s" s="104">
-        <v>135</v>
-      </c>
-      <c r="K104" t="s" s="104">
-        <v>855</v>
-      </c>
-      <c r="L104" t="s" s="104">
-        <v>28</v>
-      </c>
-      <c r="M104" t="s" s="104">
-        <v>28</v>
-      </c>
-      <c r="N104" t="s" s="104">
-        <v>854</v>
-      </c>
-      <c r="O104" t="s" s="104">
-        <v>854</v>
-      </c>
-      <c r="P104" t="s" s="104">
-        <v>273</v>
-      </c>
-      <c r="Q104" t="s" s="104">
-        <v>41</v>
-      </c>
-      <c r="R104" t="s" s="104">
-        <v>41</v>
-      </c>
-      <c r="S104" t="s" s="104">
-        <v>173</v>
-      </c>
-      <c r="T104" t="s" s="104">
-        <v>174</v>
-      </c>
-      <c r="U104" t="s" s="104">
-        <v>44</v>
-      </c>
-      <c r="V104" t="s" s="104">
-        <v>33</v>
-      </c>
-      <c r="W104" t="s" s="104">
-        <v>45</v>
-      </c>
-      <c r="X104" t="s" s="104">
-        <v>45</v>
-      </c>
-      <c r="Y104" t="s" s="104">
         <v>45</v>
       </c>
     </row>
